--- a/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
+++ b/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRSP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328D45C8-DBED-468F-869B-08D588F5465B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E77A537-30C2-4CBB-97F5-A6E08289232E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -2003,14 +2003,6 @@
   <dxfs count="30">
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2041,6 +2033,24 @@
         <strike val="0"/>
         <color theme="0"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2248,16 +2258,6 @@
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2600,15 +2600,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="6"/>
+    <col min="1" max="1" width="9.69140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="41.53515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>41</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>49</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>51</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>42</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>43</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>52</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>54</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
         <v>55</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
@@ -2797,19 +2797,19 @@
         <v>378</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46244.632315393515</v>
+        <v>46249.394488310187</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
         <v>382</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
         <v>384</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
         <v>385</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
         <v>57</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
         <v>58</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>59</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>60</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
         <v>376</v>
       </c>
@@ -2908,37 +2908,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <dimension ref="A1:AA100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.5703125" style="33" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="159.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.23046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.4609375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.4609375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.61328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.53515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.921875" style="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.15234375" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.84375" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.23046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="170.3046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="171.07421875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.23046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.07421875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.921875" style="33" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="36.84375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.61328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3" style="27" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="169.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3021,7 +3022,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="62">
         <v>2</v>
       </c>
@@ -3115,7 +3116,7 @@
         <v>Continent.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="62">
         <v>3</v>
       </c>
@@ -3207,7 +3208,7 @@
         <v>SubContinent.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="62">
         <v>4</v>
       </c>
@@ -3299,7 +3300,7 @@
         <v>Region that defines characteristics of life in the natural environment.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="62">
         <v>5</v>
       </c>
@@ -3392,7 +3393,7 @@
         <v>Country.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="62">
         <v>6</v>
       </c>
@@ -3484,7 +3485,7 @@
         <v>Nation</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="62">
         <v>7</v>
       </c>
@@ -3577,7 +3578,7 @@
         <v>Geographic Region of Brazil. of Brazil there are 5 main Geographic Regions.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="62">
         <v>8</v>
       </c>
@@ -3670,7 +3671,7 @@
         <v>Intermediate Geographic Region. Defined by the IBGE of Brazil, there are 133 Intermediate Geographic Regions, of a larger scale, which are articulated by regional capitals or large urban centers. Designed to organize the territory by articulating the Immediate Geographic Regions through a higher hierarchical pole differentiated from the flows of private and public management and the existence of urban functions of greater complexity.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="62">
         <v>9</v>
       </c>
@@ -3763,7 +3764,7 @@
         <v>Immediate geographic region. Defined by the IBGE of Brazil, there are 510 Geographic Regions of smaller scale, they are articulated by medium and small cities. It is in these centers that the population seeks what they need on a daily basis: buying products, looking for a job, accessing health and education services and solving issues in public agencies, such as the INSS, the Ministry of Labor and Justice.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="62">
         <v>10</v>
       </c>
@@ -3856,7 +3857,7 @@
         <v>State.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="62">
         <v>11</v>
       </c>
@@ -3948,7 +3949,7 @@
         <v>Federative Unit of Brazil.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="62">
         <v>12</v>
       </c>
@@ -4041,7 +4042,7 @@
         <v>Province.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="62">
         <v>13</v>
       </c>
@@ -4134,7 +4135,7 @@
         <v>Capital of a State in Brazil.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="62">
         <v>14</v>
       </c>
@@ -4228,7 +4229,7 @@
         <v>Capital City of a state located in the southern region of Brazil.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="62">
         <v>15</v>
       </c>
@@ -4322,7 +4323,7 @@
         <v>Capital City of a State located in the Southeast region of Brazil.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="62">
         <v>16</v>
       </c>
@@ -4416,7 +4417,7 @@
         <v>Capital City of a State located in the Northern region of Brazil.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="62">
         <v>17</v>
       </c>
@@ -4510,7 +4511,7 @@
         <v>Capital City of a state located in the Northeast region of Brazil.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="62">
         <v>18</v>
       </c>
@@ -4604,7 +4605,7 @@
         <v>Capital City of a state located in the Midwest region of Brazil.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="62">
         <v>19</v>
       </c>
@@ -4698,7 +4699,7 @@
         <v>City of Brazil.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="62">
         <v>20</v>
       </c>
@@ -4792,7 +4793,7 @@
         <v>City located in the southern region of Brazil.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="62">
         <v>21</v>
       </c>
@@ -4886,7 +4887,7 @@
         <v>City located in the Southeast region of Brazil.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="62">
         <v>22</v>
       </c>
@@ -4980,7 +4981,7 @@
         <v>City located in the North region of Brazil.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="62">
         <v>23</v>
       </c>
@@ -5074,7 +5075,7 @@
         <v>City located in the Northeast region of Brazil.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="62">
         <v>24</v>
       </c>
@@ -5168,7 +5169,7 @@
         <v>City located in the Midwest region of Brazil.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="62">
         <v>25</v>
       </c>
@@ -5261,7 +5262,7 @@
         <v>Metropolis.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="62">
         <v>26</v>
       </c>
@@ -5354,7 +5355,7 @@
         <v>Municipality.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="62">
         <v>27</v>
       </c>
@@ -5447,7 +5448,7 @@
         <v>Climatic region.</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="62">
         <v>28</v>
       </c>
@@ -5540,7 +5541,7 @@
         <v>Climate zone.</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="62">
         <v>29</v>
       </c>
@@ -5633,7 +5634,7 @@
         <v>Local climate zone (FTZ) according to Stewart and Oke's methodology for qualifying heat islands in urban areas.</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="62">
         <v>30</v>
       </c>
@@ -5725,7 +5726,7 @@
         <v>Ifcreferent defines a position at a specific offset along an alignment curve.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="62">
         <v>31</v>
       </c>
@@ -5817,7 +5818,7 @@
         <v>Represents where an administrative (city or state) or maintenance boundary (different companies or regionals) intersects the linear element (rails or roads) being measured.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="62">
         <v>32</v>
       </c>
@@ -5909,7 +5910,7 @@
         <v>It is the location of an intersection specified by the name of the referent. the intersection location of the intersection's street reference lines. it is not precise or deterministic.</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="62">
         <v>33</v>
       </c>
@@ -6001,7 +6002,7 @@
         <v>Used to completely describe a linearly referenced location, given by the line element.</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="62">
         <v>34</v>
       </c>
@@ -6093,7 +6094,7 @@
         <v>Point in kilometer.</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="62">
         <v>35</v>
       </c>
@@ -6185,7 +6186,7 @@
         <v>The reference is the location of a visible physical reference point in the field.</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="62">
         <v>36</v>
       </c>
@@ -6277,7 +6278,7 @@
         <v>Point in mile.</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="62">
         <v>37</v>
       </c>
@@ -6369,7 +6370,7 @@
         <v>A reference marker is a notation referent, located in the right-of-way of a highway, railroad or other transportation system spaced at uniform distances.</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="62">
         <v>38</v>
       </c>
@@ -6461,7 +6462,7 @@
         <v>Season.</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="62">
         <v>39</v>
       </c>
@@ -6553,7 +6554,7 @@
         <v>Specifies the superelevation (transverse slope) at a specific location along a road alignment, and the type of transition from the previous location.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="62">
         <v>40</v>
       </c>
@@ -6645,7 +6646,7 @@
         <v>Event type that specifies the width at a specific location along a road alignment.</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="62">
         <v>41</v>
       </c>
@@ -6737,7 +6738,7 @@
         <v>Elevation points positioned inside the land.</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="62">
         <v>42</v>
       </c>
@@ -6829,7 +6830,7 @@
         <v>Altimetric elevation points positioned on the perimeter of the land.</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="62">
         <v>43</v>
       </c>
@@ -6921,7 +6922,7 @@
         <v>Three-dimensional solid terrain. Revit models above 2024 use solid terrain models, while still maintaining the terrain mesh scheme.</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="62">
         <v>44</v>
       </c>
@@ -7013,7 +7014,7 @@
         <v>Three-dimensional maha of the terrain. Revit models prior to 2024 use surface terrain models.</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="62">
         <v>45</v>
       </c>
@@ -7105,7 +7106,7 @@
         <v>Three-dimensional terrain solid: core layer.</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="62">
         <v>46</v>
       </c>
@@ -7197,7 +7198,7 @@
         <v>Three-dimensional solid of the terrain: substrate layer.</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="62">
         <v>47</v>
       </c>
@@ -7289,7 +7290,7 @@
         <v>Three-dimensional solid of the terrain: membrane layer.</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="62">
         <v>48</v>
       </c>
@@ -7381,7 +7382,7 @@
         <v>Three-dimensional solid terrain: insulation layer.</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="62">
         <v>49</v>
       </c>
@@ -7473,7 +7474,7 @@
         <v>Three-dimensional solid of the terrain: surface layer.</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="62">
         <v>50</v>
       </c>
@@ -7565,7 +7566,7 @@
         <v>10-meter level curve.</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="62">
         <v>51</v>
       </c>
@@ -7657,7 +7658,7 @@
         <v>5 meter level curve.</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="62">
         <v>52</v>
       </c>
@@ -7749,7 +7750,7 @@
         <v>Level curve of 1 meter.</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="62">
         <v>53</v>
       </c>
@@ -7841,7 +7842,7 @@
         <v>Submetric contour line, its value must be less than 1m and can be 5 cm, 10 cm, 25 cm, etc. For adjustments of boxes or poles on the ground.</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="62">
         <v>54</v>
       </c>
@@ -7933,7 +7934,7 @@
         <v>Land polling point.</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="62">
         <v>55</v>
       </c>
@@ -8028,7 +8029,7 @@
         <v>AP stands for Planning Area.</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="62">
         <v>56</v>
       </c>
@@ -8122,7 +8123,7 @@
         <v>RA stands for Administrative Region.</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="62">
         <v>57</v>
       </c>
@@ -8214,7 +8215,7 @@
         <v>Area of Special Interest.</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="62">
         <v>58</v>
       </c>
@@ -8306,7 +8307,7 @@
         <v>Area with occupancy restrictions</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="62">
         <v>59</v>
       </c>
@@ -8398,7 +8399,7 @@
         <v>Areas of the city of Rio de Janeiro.</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="62">
         <v>60</v>
       </c>
@@ -8490,7 +8491,7 @@
         <v>City Neighborhood</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="62">
         <v>61</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>Zone of use of the municipal zoning of the city of Rio de Janeiro.</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="62">
         <v>62</v>
       </c>
@@ -8674,7 +8675,7 @@
         <v>City Neighborhood</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="62">
         <v>63</v>
       </c>
@@ -8766,7 +8767,7 @@
         <v>Block of a neighborhood.</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="62">
         <v>64</v>
       </c>
@@ -8858,7 +8859,7 @@
         <v>Large land that has not yet been subdivided.</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="62">
         <v>65</v>
       </c>
@@ -8950,7 +8951,7 @@
         <v>Urban allotment.</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="62">
         <v>66</v>
       </c>
@@ -9042,7 +9043,7 @@
         <v>Urban parcel.</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="62">
         <v>67</v>
       </c>
@@ -9134,7 +9135,7 @@
         <v>Urban lot.</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="62">
         <v>68</v>
       </c>
@@ -9227,7 +9228,7 @@
         <v>Building.</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="62">
         <v>69</v>
       </c>
@@ -9320,7 +9321,7 @@
         <v>Built block.</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="62">
         <v>70</v>
       </c>
@@ -9413,7 +9414,7 @@
         <v>Building.</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="62">
         <v>71</v>
       </c>
@@ -9506,7 +9507,7 @@
         <v>Home.</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="62">
         <v>72</v>
       </c>
@@ -9599,7 +9600,7 @@
         <v>Social Interest Housing.</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="62">
         <v>73</v>
       </c>
@@ -9691,7 +9692,7 @@
         <v>Shed.</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="62">
         <v>74</v>
       </c>
@@ -9783,7 +9784,7 @@
         <v>Edicule.</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="62">
         <v>75</v>
       </c>
@@ -9876,7 +9877,7 @@
         <v>Unity.</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="62">
         <v>76</v>
       </c>
@@ -9968,7 +9969,7 @@
         <v>Sector.</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="62">
         <v>77</v>
       </c>
@@ -10060,7 +10061,7 @@
         <v>Division.</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="62">
         <v>78</v>
       </c>
@@ -10152,7 +10153,7 @@
         <v>Department</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="62">
         <v>79</v>
       </c>
@@ -10244,7 +10245,7 @@
         <v>Environment.</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="62">
         <v>80</v>
       </c>
@@ -10336,7 +10337,7 @@
         <v>Apartment</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="62">
         <v>81</v>
       </c>
@@ -10428,7 +10429,7 @@
         <v>Circulation Center.</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="62">
         <v>82</v>
       </c>
@@ -10520,7 +10521,7 @@
         <v>National Hospital.</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="62">
         <v>83</v>
       </c>
@@ -10612,7 +10613,7 @@
         <v>State Hospital.</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="62">
         <v>84</v>
       </c>
@@ -10704,7 +10705,7 @@
         <v>Municipal Hospital.</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="62">
         <v>85</v>
       </c>
@@ -10796,7 +10797,7 @@
         <v>UBS Basic Health Unit. Primary and preventive health care offered by the SUS.</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="62">
         <v>86</v>
       </c>
@@ -10888,7 +10889,7 @@
         <v>UPA Emergency Health Care Unit. Urgencies and emergencies 24x7.</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="62">
         <v>87</v>
       </c>
@@ -10980,7 +10981,7 @@
         <v>Federal University.</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="62">
         <v>88</v>
       </c>
@@ -11072,7 +11073,7 @@
         <v>State University.</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="62">
         <v>89</v>
       </c>
@@ -11164,7 +11165,7 @@
         <v>State School.</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="62">
         <v>90</v>
       </c>
@@ -11256,7 +11257,7 @@
         <v>Municipal School.</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="62">
         <v>91</v>
       </c>
@@ -11348,7 +11349,7 @@
         <v>The application colleges are educational institutions linked to universities, with the mission of integrating theory and practice in the training of students and teachers.</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="62">
         <v>92</v>
       </c>
@@ -11440,7 +11441,7 @@
         <v>Military education institutions include military elementary and secondary education colleges as well as the vocational schools of the Armed Forces.</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="62">
         <v>93</v>
       </c>
@@ -11532,7 +11533,7 @@
         <v>Meteorological station managed by the National Institute of Meteorology (INMET) dependent on the Ministry of Agriculture and Livestock.</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="62">
         <v>94</v>
       </c>
@@ -11624,7 +11625,7 @@
         <v>Automatic meteorological station managed by the National Institute of Meteorology (INMET) dependent on the Ministry of Agriculture and Livestock.</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="62">
         <v>95</v>
       </c>
@@ -11716,7 +11717,7 @@
         <v>Conventional meteorological station managed by the National Institute of Meteorology (INMET) dependent on the Ministry of Agriculture and Livestock.</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="62">
         <v>96</v>
       </c>
@@ -11808,7 +11809,7 @@
         <v>IBGE Index - Number of inhabitants per square kilometer measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="62">
         <v>97</v>
       </c>
@@ -11900,7 +11901,7 @@
         <v>IBGE Index - Number of inhabitants per square kilometer measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="62">
         <v>98</v>
       </c>
@@ -11992,7 +11993,7 @@
         <v>IBGE Index - IDU (Urban Development Index) evaluates the quality of life and access to urban services measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="62">
         <v>99</v>
       </c>
@@ -12084,7 +12085,7 @@
         <v>IBGE Index - Proportion between urban and rural population measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="62">
         <v>100</v>
       </c>
@@ -12183,7 +12184,7 @@
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F101:F1048576 A1:D1 L1:Q1 S1:W1 AB1:XFD1 A101:D1048576 S101:W1048576 AA101:XFD1048576">
+  <conditionalFormatting sqref="F1 F101:F1048576 A1:D1 S1:W1 A101:D1048576 S101:W1048576 AA101:XFD1048576">
     <cfRule type="cellIs" dxfId="28" priority="454" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -12191,35 +12192,35 @@
   <conditionalFormatting sqref="F1">
     <cfRule type="duplicateValues" dxfId="27" priority="1492"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F96:F100 F2:F93">
-    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L2:Q6 S2:U28 AB2:XFD29 L7:O9 Q7:Q9 L10:Q29 S29:T29 U29:U40 O30:O40">
-    <cfRule type="cellIs" dxfId="25" priority="13" operator="equal">
+  <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AB1:XFD29 S2:U28 L7:O9 Q7:Q9 L10:Q29 S29:T29 U29:U40 O30:O40">
+    <cfRule type="cellIs" dxfId="26" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F93 F96:F100">
-    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F40">
-    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F40">
-    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
-    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F96:F100 F2:F93">
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101:F1048576 F1">
     <cfRule type="duplicateValues" dxfId="12" priority="157"/>
@@ -12231,8 +12232,8 @@
     <cfRule type="duplicateValues" dxfId="6" priority="986"/>
     <cfRule type="duplicateValues" dxfId="5" priority="990"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA100 V2:V100 A2:B100">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="AA1:AA100 A2:B100 V2:V100">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12243,15 +12244,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>22</v>
       </c>
@@ -12316,7 +12317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -12381,7 +12382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -12449,7 +12450,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12461,14 +12462,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="21">
         <v>1</v>
       </c>
@@ -12482,7 +12483,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13">
         <v>2</v>
       </c>
@@ -12496,7 +12497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>3</v>
       </c>
@@ -12510,7 +12511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>4</v>
       </c>
@@ -12524,7 +12525,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>5</v>
       </c>
@@ -12538,7 +12539,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>6</v>
       </c>
@@ -12554,7 +12555,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A6">
-    <cfRule type="cellIs" dxfId="3" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12565,68 +12566,68 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:BE10"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.84375" style="25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="32.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="7.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="16.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="5.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="5.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="9.7109375" style="48" bestFit="1" customWidth="1"/>
-    <col min="58" max="16384" width="9.140625" style="25"/>
+    <col min="15" max="15" width="32.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.84375" style="58" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.84375" style="58" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.84375" style="58" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="3.84375" style="58" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.84375" style="58" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="3.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="3.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.3046875" style="48" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.3828125" style="25" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="5.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16.3046875" style="48" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="5.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="5.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="9.69140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="58" max="16384" width="9.15234375" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="29" t="s">
         <v>74</v>
       </c>
@@ -12795,7 +12796,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="38">
         <v>2</v>
       </c>
@@ -12969,7 +12970,7 @@
         <v>"Continente"</v>
       </c>
     </row>
-    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="38">
         <v>3</v>
       </c>
@@ -13143,7 +13144,7 @@
         <v>"SubContinente"</v>
       </c>
     </row>
-    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="38">
         <v>4</v>
       </c>
@@ -13317,7 +13318,7 @@
         <v>"País"</v>
       </c>
     </row>
-    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="38">
         <v>5</v>
       </c>
@@ -13491,7 +13492,7 @@
         <v>"Região"</v>
       </c>
     </row>
-    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="38">
         <v>6</v>
       </c>
@@ -13665,7 +13666,7 @@
         <v>"Região"</v>
       </c>
     </row>
-    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="38">
         <v>7</v>
       </c>
@@ -13839,7 +13840,7 @@
         <v>"Estado"</v>
       </c>
     </row>
-    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="38">
         <v>8</v>
       </c>
@@ -14014,7 +14015,7 @@
         <v>"Capital"</v>
       </c>
     </row>
-    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="38">
         <v>9</v>
       </c>
@@ -14188,7 +14189,7 @@
         <v>"UF"</v>
       </c>
     </row>
-    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="38">
         <v>10</v>
       </c>
@@ -14365,13 +14366,13 @@
   </sheetData>
   <autoFilter ref="F1:F10" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B1048576 D1:F1048576 G2 G4:G5 G7 G9 H1:XFD1048576">
-    <cfRule type="cellIs" dxfId="2" priority="37" operator="equal">
+  <conditionalFormatting sqref="A1:B1048576 D1:F1048576 H1:XFD1048576 G2 G4:G5 G7 G9">
+    <cfRule type="cellIs" dxfId="1" priority="37" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
+++ b/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDEF7DB-5CEC-4516-A514-EC1DB6E0755A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFEF49C-1E31-4818-AD10-E711FDA3247F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="594">
   <si>
     <t>Key</t>
   </si>
@@ -1285,9 +1285,6 @@
     <t>[ OST_SpecialityEquipment ]</t>
   </si>
   <si>
-    <t>null ]</t>
-  </si>
-  <si>
     <t>[ IfcReferentBOUNDARY ]</t>
   </si>
   <si>
@@ -1339,9 +1336,6 @@
     <t>[ IfcBuildingElementProxy ]</t>
   </si>
   <si>
-    <t>[ null ]</t>
-  </si>
-  <si>
     <t>[ OST_ToposolidMembrane ]</t>
   </si>
   <si>
@@ -1838,6 +1832,30 @@
   </si>
   <si>
     <t>Atributo Ifc</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
   </si>
 </sst>
 </file>
@@ -1945,7 +1963,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2072,6 +2090,18 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE79D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -2124,7 +2154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2335,11 +2365,32 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="34">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2377,6 +2428,7 @@
       <font>
         <b val="0"/>
         <i/>
+        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -2387,6 +2439,23 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2989,7 +3058,7 @@
         <v>46</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C3" s="52" t="s">
         <v>378</v>
@@ -3145,7 +3214,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C17" s="52" t="s">
         <v>378</v>
@@ -3157,7 +3226,7 @@
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46253.650933101853</v>
+        <v>46258.60483715278</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>378</v>
@@ -3225,7 +3294,7 @@
         <v>59</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C24" s="52" t="s">
         <v>378</v>
@@ -3236,7 +3305,7 @@
         <v>60</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C25" s="52" t="s">
         <v>379</v>
@@ -3261,7 +3330,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
@@ -3370,13 +3439,13 @@
         <v>80</v>
       </c>
       <c r="Z1" s="26" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AA1" s="16" t="s">
         <v>79</v>
       </c>
       <c r="AB1" s="26" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AC1" s="26" t="s">
         <v>374</v>
@@ -3387,7 +3456,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C2" s="31" t="s">
         <v>255</v>
@@ -3441,7 +3510,7 @@
         <v>81</v>
       </c>
       <c r="R2" s="66" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="S2" s="66" t="s">
         <v>1</v>
@@ -3459,23 +3528,23 @@
         <v>Naturais</v>
       </c>
       <c r="W2" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X2" s="67" t="str">
-        <f t="shared" ref="X2:X61" si="2">CONCATENATE("Key-BRASIL-",A2)</f>
-        <v>Key-BRASIL-2</v>
+        <f>CONCATENATE("Key-BRASIL-SP-",A2)</f>
+        <v>Key-BRASIL-SP-2</v>
       </c>
       <c r="Y2" s="66" t="s">
         <v>1</v>
       </c>
       <c r="Z2" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AA2" s="66" t="s">
         <v>1</v>
       </c>
       <c r="AB2" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AC2" s="70" t="s">
         <v>1</v>
@@ -3486,7 +3555,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C3" s="31" t="s">
         <v>255</v>
@@ -3520,15 +3589,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M3" s="69" t="str">
-        <f t="shared" ref="M3:O57" si="3">_xlfn.CONCAT(SUBSTITUTE(D3,"."," "))</f>
+        <f t="shared" ref="M3:O57" si="2">_xlfn.CONCAT(SUBSTITUTE(D3,"."," "))</f>
         <v>Geográficas</v>
       </c>
       <c r="N3" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Naturais</v>
       </c>
       <c r="O3" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>SubContinente</v>
       </c>
       <c r="P3" s="69" t="s">
@@ -3538,7 +3607,7 @@
         <v>82</v>
       </c>
       <c r="R3" s="66" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="S3" s="66" t="s">
         <v>1</v>
@@ -3556,23 +3625,23 @@
         <v>Naturais</v>
       </c>
       <c r="W3" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X3" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-3</v>
+        <f t="shared" ref="X3:X66" si="3">CONCATENATE("Key-BRASIL-SP-",A3)</f>
+        <v>Key-BRASIL-SP-3</v>
       </c>
       <c r="Y3" s="66" t="s">
         <v>1</v>
       </c>
       <c r="Z3" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AA3" s="66" t="s">
         <v>1</v>
       </c>
       <c r="AB3" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AC3" s="70" t="s">
         <v>1</v>
@@ -3583,7 +3652,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C4" s="31" t="s">
         <v>255</v>
@@ -3617,15 +3686,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M4" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N4" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Naturais</v>
       </c>
       <c r="O4" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Bioma</v>
       </c>
       <c r="P4" s="69" t="s">
@@ -3635,7 +3704,7 @@
         <v>84</v>
       </c>
       <c r="R4" s="66" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="S4" s="66" t="s">
         <v>1</v>
@@ -3653,23 +3722,23 @@
         <v>Naturais</v>
       </c>
       <c r="W4" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X4" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-4</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-4</v>
       </c>
       <c r="Y4" s="66" t="s">
         <v>1</v>
       </c>
       <c r="Z4" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AA4" s="66" t="s">
         <v>1</v>
       </c>
       <c r="AB4" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AC4" s="70" t="s">
         <v>1</v>
@@ -3680,7 +3749,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>255</v>
@@ -3715,15 +3784,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M5" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N5" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O5" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>País</v>
       </c>
       <c r="P5" s="69" t="s">
@@ -3733,7 +3802,7 @@
         <v>85</v>
       </c>
       <c r="R5" s="66" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="S5" s="66" t="s">
         <v>1</v>
@@ -3751,23 +3820,23 @@
         <v>Políticas</v>
       </c>
       <c r="W5" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X5" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-5</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-5</v>
       </c>
       <c r="Y5" s="66" t="s">
         <v>1</v>
       </c>
       <c r="Z5" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AA5" s="66" t="s">
         <v>386</v>
       </c>
       <c r="AB5" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AC5" s="70" t="s">
         <v>1</v>
@@ -3778,7 +3847,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C6" s="31" t="s">
         <v>255</v>
@@ -3812,15 +3881,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M6" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N6" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O6" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Nação</v>
       </c>
       <c r="P6" s="69" t="s">
@@ -3830,7 +3899,7 @@
         <v>87</v>
       </c>
       <c r="R6" s="66" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="S6" s="66" t="s">
         <v>1</v>
@@ -3848,23 +3917,23 @@
         <v>Políticas</v>
       </c>
       <c r="W6" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X6" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-6</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-6</v>
       </c>
       <c r="Y6" s="66" t="s">
         <v>1</v>
       </c>
       <c r="Z6" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AA6" s="66" t="s">
         <v>386</v>
       </c>
       <c r="AB6" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AC6" s="70" t="s">
         <v>1</v>
@@ -3875,7 +3944,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>255</v>
@@ -3909,25 +3978,25 @@
         <v>Fronteiras</v>
       </c>
       <c r="M7" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N7" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O7" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Região</v>
       </c>
       <c r="P7" s="71" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Q7" s="69" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="R7" s="66" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="S7" s="66" t="s">
         <v>1</v>
@@ -3945,23 +4014,23 @@
         <v>Políticas</v>
       </c>
       <c r="W7" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X7" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-7</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-7</v>
       </c>
       <c r="Y7" s="66" t="s">
         <v>1</v>
       </c>
       <c r="Z7" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AA7" s="66" t="s">
         <v>386</v>
       </c>
       <c r="AB7" s="66" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AC7" s="70" t="s">
         <v>1</v>
@@ -3972,7 +4041,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>255</v>
@@ -3984,7 +4053,7 @@
         <v>257</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G8" s="68" t="s">
         <v>1</v>
@@ -4006,25 +4075,25 @@
         <v>Fronteiras</v>
       </c>
       <c r="M8" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N8" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O8" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Região Intermediária</v>
       </c>
       <c r="P8" s="71" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Q8" s="69" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="R8" s="66" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S8" s="66" t="s">
         <v>1</v>
@@ -4042,23 +4111,23 @@
         <v>Políticas</v>
       </c>
       <c r="W8" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X8" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-8</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-8</v>
       </c>
       <c r="Y8" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z8" s="66" t="s">
-        <v>586</v>
+      <c r="Z8" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA8" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB8" s="66" t="s">
-        <v>586</v>
+      <c r="AB8" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC8" s="70" t="s">
         <v>1</v>
@@ -4069,7 +4138,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>255</v>
@@ -4081,7 +4150,7 @@
         <v>257</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="G9" s="68" t="s">
         <v>1</v>
@@ -4103,25 +4172,25 @@
         <v>Fronteiras</v>
       </c>
       <c r="M9" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N9" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O9" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Região Imediata</v>
       </c>
       <c r="P9" s="71" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Q9" s="69" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="R9" s="66" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="S9" s="66" t="s">
         <v>1</v>
@@ -4139,23 +4208,23 @@
         <v>Políticas</v>
       </c>
       <c r="W9" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X9" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-9</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-9</v>
       </c>
       <c r="Y9" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z9" s="66" t="s">
-        <v>586</v>
+      <c r="Z9" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA9" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB9" s="66" t="s">
-        <v>586</v>
+      <c r="AB9" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC9" s="70" t="s">
         <v>1</v>
@@ -4166,7 +4235,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>255</v>
@@ -4201,15 +4270,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M10" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N10" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O10" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Estado</v>
       </c>
       <c r="P10" s="69" t="s">
@@ -4219,7 +4288,7 @@
         <v>90</v>
       </c>
       <c r="R10" s="66" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="S10" s="66" t="s">
         <v>1</v>
@@ -4237,23 +4306,23 @@
         <v>Políticas</v>
       </c>
       <c r="W10" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X10" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-10</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-10</v>
       </c>
       <c r="Y10" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z10" s="66" t="s">
-        <v>586</v>
+      <c r="Z10" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA10" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB10" s="66" t="s">
-        <v>586</v>
+      <c r="AB10" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC10" s="70" t="s">
         <v>1</v>
@@ -4264,7 +4333,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C11" s="31" t="s">
         <v>255</v>
@@ -4298,15 +4367,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M11" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N11" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O11" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>UF</v>
       </c>
       <c r="P11" s="69" t="s">
@@ -4316,7 +4385,7 @@
         <v>92</v>
       </c>
       <c r="R11" s="66" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="S11" s="66" t="s">
         <v>1</v>
@@ -4334,23 +4403,23 @@
         <v>Políticas</v>
       </c>
       <c r="W11" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X11" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-11</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-11</v>
       </c>
       <c r="Y11" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z11" s="66" t="s">
-        <v>586</v>
+      <c r="Z11" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA11" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB11" s="66" t="s">
-        <v>586</v>
+      <c r="AB11" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC11" s="70" t="s">
         <v>1</v>
@@ -4361,7 +4430,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>255</v>
@@ -4396,15 +4465,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M12" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N12" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O12" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Província</v>
       </c>
       <c r="P12" s="69" t="s">
@@ -4414,7 +4483,7 @@
         <v>94</v>
       </c>
       <c r="R12" s="66" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="S12" s="66" t="s">
         <v>1</v>
@@ -4432,23 +4501,23 @@
         <v>Políticas</v>
       </c>
       <c r="W12" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X12" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-12</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-12</v>
       </c>
       <c r="Y12" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z12" s="66" t="s">
-        <v>586</v>
+      <c r="Z12" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA12" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB12" s="66" t="s">
-        <v>586</v>
+      <c r="AB12" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC12" s="70" t="s">
         <v>1</v>
@@ -4459,7 +4528,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>255</v>
@@ -4494,25 +4563,25 @@
         <v>Fronteiras</v>
       </c>
       <c r="M13" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N13" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O13" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Capital</v>
       </c>
       <c r="P13" s="69" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="Q13" s="69" t="s">
         <v>95</v>
       </c>
       <c r="R13" s="66" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="S13" s="66" t="s">
         <v>1</v>
@@ -4530,23 +4599,23 @@
         <v>Políticas</v>
       </c>
       <c r="W13" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X13" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-13</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-13</v>
       </c>
       <c r="Y13" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z13" s="66" t="s">
-        <v>586</v>
+      <c r="Z13" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA13" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB13" s="66" t="s">
-        <v>586</v>
+      <c r="AB13" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC13" s="70" t="s">
         <v>1</v>
@@ -4557,7 +4626,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>255</v>
@@ -4569,7 +4638,7 @@
         <v>257</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="G14" s="68" t="s">
         <v>1</v>
@@ -4592,59 +4661,59 @@
         <v>Fronteiras</v>
       </c>
       <c r="M14" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="N14" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Políticas</v>
+      </c>
+      <c r="O14" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Capital do Sul</v>
+      </c>
+      <c r="P14" s="69" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q14" s="69" t="s">
+        <v>572</v>
+      </c>
+      <c r="R14" s="66" t="s">
+        <v>485</v>
+      </c>
+      <c r="S14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Fronteiras</v>
+      </c>
+      <c r="U14" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="V14" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Políticas</v>
+      </c>
+      <c r="W14" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X14" s="67" t="str">
         <f t="shared" si="3"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="N14" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Políticas</v>
-      </c>
-      <c r="O14" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Capital do Sul</v>
-      </c>
-      <c r="P14" s="69" t="s">
-        <v>448</v>
-      </c>
-      <c r="Q14" s="69" t="s">
-        <v>574</v>
-      </c>
-      <c r="R14" s="66" t="s">
-        <v>487</v>
-      </c>
-      <c r="S14" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T14" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Fronteiras</v>
-      </c>
-      <c r="U14" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="V14" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Políticas</v>
-      </c>
-      <c r="W14" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="X14" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-14</v>
+        <v>Key-BRASIL-SP-14</v>
       </c>
       <c r="Y14" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z14" s="66" t="s">
-        <v>586</v>
+      <c r="Z14" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA14" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB14" s="66" t="s">
-        <v>586</v>
+      <c r="AB14" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC14" s="70" t="s">
         <v>1</v>
@@ -4655,7 +4724,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>255</v>
@@ -4667,7 +4736,7 @@
         <v>257</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G15" s="68" t="s">
         <v>1</v>
@@ -4690,59 +4759,59 @@
         <v>Fronteiras</v>
       </c>
       <c r="M15" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="N15" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Políticas</v>
+      </c>
+      <c r="O15" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Capital do Sudeste</v>
+      </c>
+      <c r="P15" s="69" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q15" s="69" t="s">
+        <v>573</v>
+      </c>
+      <c r="R15" s="66" t="s">
+        <v>486</v>
+      </c>
+      <c r="S15" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Fronteiras</v>
+      </c>
+      <c r="U15" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="V15" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Políticas</v>
+      </c>
+      <c r="W15" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X15" s="67" t="str">
         <f t="shared" si="3"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="N15" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Políticas</v>
-      </c>
-      <c r="O15" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Capital do Sudeste</v>
-      </c>
-      <c r="P15" s="69" t="s">
-        <v>450</v>
-      </c>
-      <c r="Q15" s="69" t="s">
-        <v>575</v>
-      </c>
-      <c r="R15" s="66" t="s">
-        <v>488</v>
-      </c>
-      <c r="S15" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T15" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Fronteiras</v>
-      </c>
-      <c r="U15" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="V15" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Políticas</v>
-      </c>
-      <c r="W15" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="X15" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-15</v>
+        <v>Key-BRASIL-SP-15</v>
       </c>
       <c r="Y15" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z15" s="66" t="s">
-        <v>586</v>
+      <c r="Z15" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA15" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB15" s="66" t="s">
-        <v>586</v>
+      <c r="AB15" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC15" s="70" t="s">
         <v>1</v>
@@ -4753,7 +4822,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>255</v>
@@ -4765,7 +4834,7 @@
         <v>257</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G16" s="68" t="s">
         <v>1</v>
@@ -4788,59 +4857,59 @@
         <v>Fronteiras</v>
       </c>
       <c r="M16" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="N16" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Políticas</v>
+      </c>
+      <c r="O16" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Capital do Norte</v>
+      </c>
+      <c r="P16" s="69" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q16" s="69" t="s">
+        <v>574</v>
+      </c>
+      <c r="R16" s="66" t="s">
+        <v>487</v>
+      </c>
+      <c r="S16" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Fronteiras</v>
+      </c>
+      <c r="U16" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="V16" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Políticas</v>
+      </c>
+      <c r="W16" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X16" s="67" t="str">
         <f t="shared" si="3"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="N16" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Políticas</v>
-      </c>
-      <c r="O16" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Capital do Norte</v>
-      </c>
-      <c r="P16" s="69" t="s">
-        <v>452</v>
-      </c>
-      <c r="Q16" s="69" t="s">
-        <v>576</v>
-      </c>
-      <c r="R16" s="66" t="s">
-        <v>489</v>
-      </c>
-      <c r="S16" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T16" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Fronteiras</v>
-      </c>
-      <c r="U16" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="V16" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Políticas</v>
-      </c>
-      <c r="W16" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="X16" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-16</v>
+        <v>Key-BRASIL-SP-16</v>
       </c>
       <c r="Y16" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z16" s="66" t="s">
-        <v>586</v>
+      <c r="Z16" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA16" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB16" s="66" t="s">
-        <v>586</v>
+      <c r="AB16" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC16" s="70" t="s">
         <v>1</v>
@@ -4851,7 +4920,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>255</v>
@@ -4863,7 +4932,7 @@
         <v>257</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G17" s="68" t="s">
         <v>1</v>
@@ -4886,59 +4955,59 @@
         <v>Fronteiras</v>
       </c>
       <c r="M17" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="N17" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Políticas</v>
+      </c>
+      <c r="O17" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Capital do Nordeste</v>
+      </c>
+      <c r="P17" s="69" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q17" s="69" t="s">
+        <v>575</v>
+      </c>
+      <c r="R17" s="66" t="s">
+        <v>488</v>
+      </c>
+      <c r="S17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Fronteiras</v>
+      </c>
+      <c r="U17" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="V17" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Políticas</v>
+      </c>
+      <c r="W17" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X17" s="67" t="str">
         <f t="shared" si="3"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="N17" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Políticas</v>
-      </c>
-      <c r="O17" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Capital do Nordeste</v>
-      </c>
-      <c r="P17" s="69" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q17" s="69" t="s">
-        <v>577</v>
-      </c>
-      <c r="R17" s="66" t="s">
-        <v>490</v>
-      </c>
-      <c r="S17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T17" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Fronteiras</v>
-      </c>
-      <c r="U17" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="V17" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Políticas</v>
-      </c>
-      <c r="W17" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="X17" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-17</v>
+        <v>Key-BRASIL-SP-17</v>
       </c>
       <c r="Y17" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z17" s="66" t="s">
-        <v>586</v>
+      <c r="Z17" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA17" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB17" s="66" t="s">
-        <v>586</v>
+      <c r="AB17" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC17" s="70" t="s">
         <v>1</v>
@@ -4949,7 +5018,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>255</v>
@@ -4961,7 +5030,7 @@
         <v>257</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G18" s="68" t="s">
         <v>1</v>
@@ -4984,59 +5053,59 @@
         <v>Fronteiras</v>
       </c>
       <c r="M18" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="N18" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Políticas</v>
+      </c>
+      <c r="O18" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Capital do CentroOeste</v>
+      </c>
+      <c r="P18" s="69" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q18" s="69" t="s">
+        <v>576</v>
+      </c>
+      <c r="R18" s="66" t="s">
+        <v>489</v>
+      </c>
+      <c r="S18" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Fronteiras</v>
+      </c>
+      <c r="U18" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="V18" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Políticas</v>
+      </c>
+      <c r="W18" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X18" s="67" t="str">
         <f t="shared" si="3"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="N18" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Políticas</v>
-      </c>
-      <c r="O18" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Capital do CentroOeste</v>
-      </c>
-      <c r="P18" s="69" t="s">
-        <v>456</v>
-      </c>
-      <c r="Q18" s="69" t="s">
-        <v>578</v>
-      </c>
-      <c r="R18" s="66" t="s">
-        <v>491</v>
-      </c>
-      <c r="S18" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T18" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Fronteiras</v>
-      </c>
-      <c r="U18" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="V18" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Políticas</v>
-      </c>
-      <c r="W18" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="X18" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-18</v>
+        <v>Key-BRASIL-SP-18</v>
       </c>
       <c r="Y18" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z18" s="66" t="s">
-        <v>586</v>
+      <c r="Z18" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA18" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB18" s="66" t="s">
-        <v>586</v>
+      <c r="AB18" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC18" s="70" t="s">
         <v>1</v>
@@ -5047,7 +5116,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>255</v>
@@ -5082,59 +5151,59 @@
         <v>Fronteiras</v>
       </c>
       <c r="M19" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="N19" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Políticas</v>
+      </c>
+      <c r="O19" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Cidade</v>
+      </c>
+      <c r="P19" s="69" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q19" s="69" t="s">
+        <v>577</v>
+      </c>
+      <c r="R19" s="66" t="s">
+        <v>490</v>
+      </c>
+      <c r="S19" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Fronteiras</v>
+      </c>
+      <c r="U19" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="V19" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Políticas</v>
+      </c>
+      <c r="W19" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X19" s="67" t="str">
         <f t="shared" si="3"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="N19" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Políticas</v>
-      </c>
-      <c r="O19" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Cidade</v>
-      </c>
-      <c r="P19" s="69" t="s">
-        <v>457</v>
-      </c>
-      <c r="Q19" s="69" t="s">
-        <v>579</v>
-      </c>
-      <c r="R19" s="66" t="s">
-        <v>492</v>
-      </c>
-      <c r="S19" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T19" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Fronteiras</v>
-      </c>
-      <c r="U19" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="V19" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Políticas</v>
-      </c>
-      <c r="W19" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="X19" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-19</v>
+        <v>Key-BRASIL-SP-19</v>
       </c>
       <c r="Y19" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z19" s="66" t="s">
-        <v>586</v>
+      <c r="Z19" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA19" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB19" s="66" t="s">
-        <v>586</v>
+      <c r="AB19" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC19" s="70" t="s">
         <v>1</v>
@@ -5145,7 +5214,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>255</v>
@@ -5157,7 +5226,7 @@
         <v>257</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G20" s="68" t="s">
         <v>1</v>
@@ -5180,59 +5249,59 @@
         <v>Fronteiras</v>
       </c>
       <c r="M20" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="N20" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Políticas</v>
+      </c>
+      <c r="O20" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Cidade do Sul</v>
+      </c>
+      <c r="P20" s="69" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q20" s="69" t="s">
+        <v>578</v>
+      </c>
+      <c r="R20" s="66" t="s">
+        <v>491</v>
+      </c>
+      <c r="S20" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Fronteiras</v>
+      </c>
+      <c r="U20" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="V20" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Políticas</v>
+      </c>
+      <c r="W20" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X20" s="67" t="str">
         <f t="shared" si="3"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="N20" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Políticas</v>
-      </c>
-      <c r="O20" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Cidade do Sul</v>
-      </c>
-      <c r="P20" s="69" t="s">
-        <v>459</v>
-      </c>
-      <c r="Q20" s="69" t="s">
-        <v>580</v>
-      </c>
-      <c r="R20" s="66" t="s">
-        <v>493</v>
-      </c>
-      <c r="S20" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T20" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Fronteiras</v>
-      </c>
-      <c r="U20" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="V20" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Políticas</v>
-      </c>
-      <c r="W20" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="X20" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-20</v>
+        <v>Key-BRASIL-SP-20</v>
       </c>
       <c r="Y20" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z20" s="66" t="s">
-        <v>586</v>
+      <c r="Z20" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA20" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB20" s="66" t="s">
-        <v>586</v>
+      <c r="AB20" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC20" s="70" t="s">
         <v>1</v>
@@ -5243,7 +5312,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>255</v>
@@ -5255,7 +5324,7 @@
         <v>257</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G21" s="68" t="s">
         <v>1</v>
@@ -5278,59 +5347,59 @@
         <v>Fronteiras</v>
       </c>
       <c r="M21" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="N21" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Políticas</v>
+      </c>
+      <c r="O21" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Cidade do Sudeste</v>
+      </c>
+      <c r="P21" s="69" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q21" s="69" t="s">
+        <v>579</v>
+      </c>
+      <c r="R21" s="66" t="s">
+        <v>492</v>
+      </c>
+      <c r="S21" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Fronteiras</v>
+      </c>
+      <c r="U21" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="V21" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Políticas</v>
+      </c>
+      <c r="W21" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X21" s="67" t="str">
         <f t="shared" si="3"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="N21" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Políticas</v>
-      </c>
-      <c r="O21" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Cidade do Sudeste</v>
-      </c>
-      <c r="P21" s="69" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q21" s="69" t="s">
-        <v>581</v>
-      </c>
-      <c r="R21" s="66" t="s">
-        <v>494</v>
-      </c>
-      <c r="S21" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T21" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Fronteiras</v>
-      </c>
-      <c r="U21" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="V21" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Políticas</v>
-      </c>
-      <c r="W21" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="X21" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-21</v>
+        <v>Key-BRASIL-SP-21</v>
       </c>
       <c r="Y21" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z21" s="66" t="s">
-        <v>586</v>
+      <c r="Z21" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA21" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB21" s="66" t="s">
-        <v>586</v>
+      <c r="AB21" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC21" s="70" t="s">
         <v>1</v>
@@ -5341,7 +5410,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>255</v>
@@ -5353,7 +5422,7 @@
         <v>257</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G22" s="68" t="s">
         <v>1</v>
@@ -5376,59 +5445,59 @@
         <v>Fronteiras</v>
       </c>
       <c r="M22" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="N22" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Políticas</v>
+      </c>
+      <c r="O22" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Cidade do Norte</v>
+      </c>
+      <c r="P22" s="69" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q22" s="69" t="s">
+        <v>580</v>
+      </c>
+      <c r="R22" s="66" t="s">
+        <v>493</v>
+      </c>
+      <c r="S22" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Fronteiras</v>
+      </c>
+      <c r="U22" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="V22" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Políticas</v>
+      </c>
+      <c r="W22" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X22" s="67" t="str">
         <f t="shared" si="3"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="N22" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Políticas</v>
-      </c>
-      <c r="O22" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Cidade do Norte</v>
-      </c>
-      <c r="P22" s="69" t="s">
-        <v>463</v>
-      </c>
-      <c r="Q22" s="69" t="s">
-        <v>582</v>
-      </c>
-      <c r="R22" s="66" t="s">
-        <v>495</v>
-      </c>
-      <c r="S22" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T22" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Fronteiras</v>
-      </c>
-      <c r="U22" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="V22" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Políticas</v>
-      </c>
-      <c r="W22" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="X22" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-22</v>
+        <v>Key-BRASIL-SP-22</v>
       </c>
       <c r="Y22" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z22" s="66" t="s">
-        <v>586</v>
+      <c r="Z22" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA22" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB22" s="66" t="s">
-        <v>586</v>
+      <c r="AB22" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC22" s="70" t="s">
         <v>1</v>
@@ -5439,7 +5508,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C23" s="31" t="s">
         <v>255</v>
@@ -5451,7 +5520,7 @@
         <v>257</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G23" s="68" t="s">
         <v>1</v>
@@ -5474,59 +5543,59 @@
         <v>Fronteiras</v>
       </c>
       <c r="M23" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="N23" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Políticas</v>
+      </c>
+      <c r="O23" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Cidade do Nordeste</v>
+      </c>
+      <c r="P23" s="69" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q23" s="69" t="s">
+        <v>581</v>
+      </c>
+      <c r="R23" s="66" t="s">
+        <v>494</v>
+      </c>
+      <c r="S23" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T23" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Fronteiras</v>
+      </c>
+      <c r="U23" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="V23" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Políticas</v>
+      </c>
+      <c r="W23" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X23" s="67" t="str">
         <f t="shared" si="3"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="N23" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Políticas</v>
-      </c>
-      <c r="O23" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Cidade do Nordeste</v>
-      </c>
-      <c r="P23" s="69" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q23" s="69" t="s">
-        <v>583</v>
-      </c>
-      <c r="R23" s="66" t="s">
-        <v>496</v>
-      </c>
-      <c r="S23" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T23" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Fronteiras</v>
-      </c>
-      <c r="U23" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="V23" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Políticas</v>
-      </c>
-      <c r="W23" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="X23" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-23</v>
+        <v>Key-BRASIL-SP-23</v>
       </c>
       <c r="Y23" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z23" s="66" t="s">
-        <v>586</v>
+      <c r="Z23" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA23" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB23" s="66" t="s">
-        <v>586</v>
+      <c r="AB23" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC23" s="70" t="s">
         <v>1</v>
@@ -5537,7 +5606,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C24" s="31" t="s">
         <v>255</v>
@@ -5549,7 +5618,7 @@
         <v>257</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G24" s="68" t="s">
         <v>1</v>
@@ -5572,59 +5641,59 @@
         <v>Fronteiras</v>
       </c>
       <c r="M24" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="N24" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Políticas</v>
+      </c>
+      <c r="O24" s="69" t="str">
+        <f t="shared" si="2"/>
+        <v>Cidade do CentroOeste</v>
+      </c>
+      <c r="P24" s="69" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q24" s="69" t="s">
+        <v>582</v>
+      </c>
+      <c r="R24" s="66" t="s">
+        <v>495</v>
+      </c>
+      <c r="S24" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T24" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Fronteiras</v>
+      </c>
+      <c r="U24" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Geográficas</v>
+      </c>
+      <c r="V24" s="66" t="str">
+        <f t="shared" si="4"/>
+        <v>Políticas</v>
+      </c>
+      <c r="W24" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X24" s="67" t="str">
         <f t="shared" si="3"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="N24" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Políticas</v>
-      </c>
-      <c r="O24" s="69" t="str">
-        <f t="shared" si="3"/>
-        <v>Cidade do CentroOeste</v>
-      </c>
-      <c r="P24" s="69" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q24" s="69" t="s">
-        <v>584</v>
-      </c>
-      <c r="R24" s="66" t="s">
-        <v>497</v>
-      </c>
-      <c r="S24" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T24" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Fronteiras</v>
-      </c>
-      <c r="U24" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Geográficas</v>
-      </c>
-      <c r="V24" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v>Políticas</v>
-      </c>
-      <c r="W24" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="X24" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-24</v>
+        <v>Key-BRASIL-SP-24</v>
       </c>
       <c r="Y24" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z24" s="66" t="s">
-        <v>586</v>
+      <c r="Z24" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA24" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB24" s="66" t="s">
-        <v>586</v>
+      <c r="AB24" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC24" s="70" t="s">
         <v>1</v>
@@ -5635,7 +5704,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C25" s="31" t="s">
         <v>255</v>
@@ -5670,15 +5739,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M25" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N25" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O25" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Metrópoli</v>
       </c>
       <c r="P25" s="69" t="s">
@@ -5688,7 +5757,7 @@
         <v>96</v>
       </c>
       <c r="R25" s="66" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="S25" s="66" t="s">
         <v>1</v>
@@ -5706,23 +5775,23 @@
         <v>Políticas</v>
       </c>
       <c r="W25" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X25" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-25</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-25</v>
       </c>
       <c r="Y25" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z25" s="66" t="s">
-        <v>586</v>
+      <c r="Z25" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA25" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB25" s="66" t="s">
-        <v>586</v>
+      <c r="AB25" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC25" s="70" t="s">
         <v>1</v>
@@ -5733,7 +5802,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C26" s="31" t="s">
         <v>255</v>
@@ -5768,15 +5837,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M26" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N26" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O26" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Município</v>
       </c>
       <c r="P26" s="69" t="s">
@@ -5786,7 +5855,7 @@
         <v>98</v>
       </c>
       <c r="R26" s="66" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="S26" s="66" t="s">
         <v>1</v>
@@ -5804,23 +5873,23 @@
         <v>Políticas</v>
       </c>
       <c r="W26" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X26" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-26</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-26</v>
       </c>
       <c r="Y26" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z26" s="66" t="s">
-        <v>586</v>
+      <c r="Z26" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA26" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB26" s="66" t="s">
-        <v>586</v>
+      <c r="AB26" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC26" s="70" t="s">
         <v>1</v>
@@ -5831,7 +5900,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C27" s="31" t="s">
         <v>255</v>
@@ -5866,15 +5935,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M27" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Térmicas</v>
       </c>
       <c r="N27" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Bioclimáticas</v>
       </c>
       <c r="O27" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Região Climática</v>
       </c>
       <c r="P27" s="69" t="s">
@@ -5884,7 +5953,7 @@
         <v>100</v>
       </c>
       <c r="R27" s="66" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="S27" s="66" t="s">
         <v>1</v>
@@ -5902,23 +5971,23 @@
         <v>Bioclimáticas</v>
       </c>
       <c r="W27" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X27" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-27</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-27</v>
       </c>
       <c r="Y27" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z27" s="66" t="s">
-        <v>586</v>
+      <c r="Z27" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA27" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB27" s="66" t="s">
-        <v>586</v>
+      <c r="AB27" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC27" s="70" t="s">
         <v>1</v>
@@ -5929,7 +5998,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C28" s="31" t="s">
         <v>255</v>
@@ -5964,15 +6033,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M28" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Térmicas</v>
       </c>
       <c r="N28" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Bioclimáticas</v>
       </c>
       <c r="O28" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Zona Climática</v>
       </c>
       <c r="P28" s="69" t="s">
@@ -5982,7 +6051,7 @@
         <v>102</v>
       </c>
       <c r="R28" s="66" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="S28" s="66" t="s">
         <v>1</v>
@@ -6000,23 +6069,23 @@
         <v>Bioclimáticas</v>
       </c>
       <c r="W28" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X28" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-28</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-28</v>
       </c>
       <c r="Y28" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z28" s="66" t="s">
-        <v>586</v>
+      <c r="Z28" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA28" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB28" s="66" t="s">
-        <v>586</v>
+      <c r="AB28" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC28" s="70" t="s">
         <v>1</v>
@@ -6027,7 +6096,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C29" s="31" t="s">
         <v>255</v>
@@ -6062,15 +6131,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M29" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Térmicas</v>
       </c>
       <c r="N29" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Ilhas de Calor</v>
       </c>
       <c r="O29" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Zona Climática Local</v>
       </c>
       <c r="P29" s="69" t="s">
@@ -6080,7 +6149,7 @@
         <v>104</v>
       </c>
       <c r="R29" s="66" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="S29" s="66" t="s">
         <v>1</v>
@@ -6098,23 +6167,23 @@
         <v>Ilhas de Calor</v>
       </c>
       <c r="W29" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X29" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-29</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-29</v>
       </c>
       <c r="Y29" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z29" s="66" t="s">
-        <v>586</v>
+      <c r="Z29" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA29" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB29" s="66" t="s">
-        <v>586</v>
+      <c r="AB29" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC29" s="70" t="s">
         <v>1</v>
@@ -6125,7 +6194,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C30" s="31" t="s">
         <v>255</v>
@@ -6177,7 +6246,7 @@
         <v>225</v>
       </c>
       <c r="R30" s="66" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="S30" s="66" t="s">
         <v>1</v>
@@ -6195,23 +6264,23 @@
         <v>Marcos</v>
       </c>
       <c r="W30" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X30" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-30</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-30</v>
       </c>
       <c r="Y30" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z30" s="66" t="s">
-        <v>586</v>
+      <c r="Z30" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA30" s="70" t="s">
-        <v>404</v>
-      </c>
-      <c r="AB30" s="66" t="s">
-        <v>586</v>
+        <v>403</v>
+      </c>
+      <c r="AB30" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC30" s="70" t="s">
         <v>1</v>
@@ -6222,7 +6291,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C31" s="31" t="s">
         <v>255</v>
@@ -6274,7 +6343,7 @@
         <v>227</v>
       </c>
       <c r="R31" s="66" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S31" s="66" t="s">
         <v>1</v>
@@ -6292,23 +6361,23 @@
         <v>Marcos</v>
       </c>
       <c r="W31" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X31" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-31</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-31</v>
       </c>
       <c r="Y31" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z31" s="66" t="s">
-        <v>586</v>
+      <c r="Z31" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA31" s="70" t="s">
-        <v>405</v>
-      </c>
-      <c r="AB31" s="66" t="s">
-        <v>586</v>
+        <v>404</v>
+      </c>
+      <c r="AB31" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC31" s="70" t="s">
         <v>1</v>
@@ -6319,7 +6388,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C32" s="31" t="s">
         <v>255</v>
@@ -6371,7 +6440,7 @@
         <v>229</v>
       </c>
       <c r="R32" s="66" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="S32" s="66" t="s">
         <v>1</v>
@@ -6389,23 +6458,23 @@
         <v>Marcos</v>
       </c>
       <c r="W32" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X32" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-32</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-32</v>
       </c>
       <c r="Y32" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z32" s="66" t="s">
-        <v>586</v>
+      <c r="Z32" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA32" s="70" t="s">
-        <v>406</v>
-      </c>
-      <c r="AB32" s="66" t="s">
-        <v>586</v>
+        <v>405</v>
+      </c>
+      <c r="AB32" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC32" s="70" t="s">
         <v>1</v>
@@ -6416,7 +6485,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C33" s="31" t="s">
         <v>255</v>
@@ -6468,7 +6537,7 @@
         <v>237</v>
       </c>
       <c r="R33" s="66" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="S33" s="66" t="s">
         <v>1</v>
@@ -6486,23 +6555,23 @@
         <v>Marcos</v>
       </c>
       <c r="W33" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X33" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-33</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-33</v>
       </c>
       <c r="Y33" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z33" s="66" t="s">
-        <v>586</v>
+      <c r="Z33" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA33" s="70" t="s">
-        <v>407</v>
-      </c>
-      <c r="AB33" s="66" t="s">
-        <v>586</v>
+        <v>406</v>
+      </c>
+      <c r="AB33" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC33" s="70" t="s">
         <v>1</v>
@@ -6513,7 +6582,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C34" s="31" t="s">
         <v>255</v>
@@ -6565,7 +6634,7 @@
         <v>231</v>
       </c>
       <c r="R34" s="66" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="S34" s="66" t="s">
         <v>1</v>
@@ -6583,23 +6652,23 @@
         <v>Marcos</v>
       </c>
       <c r="W34" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X34" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-34</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-34</v>
       </c>
       <c r="Y34" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z34" s="66" t="s">
-        <v>586</v>
+      <c r="Z34" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA34" s="70" t="s">
-        <v>408</v>
-      </c>
-      <c r="AB34" s="66" t="s">
-        <v>586</v>
+        <v>407</v>
+      </c>
+      <c r="AB34" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC34" s="70" t="s">
         <v>1</v>
@@ -6610,7 +6679,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C35" s="31" t="s">
         <v>255</v>
@@ -6662,7 +6731,7 @@
         <v>233</v>
       </c>
       <c r="R35" s="66" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="S35" s="66" t="s">
         <v>1</v>
@@ -6680,23 +6749,23 @@
         <v>Marcos</v>
       </c>
       <c r="W35" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X35" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-35</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-35</v>
       </c>
       <c r="Y35" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z35" s="66" t="s">
-        <v>586</v>
+      <c r="Z35" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA35" s="70" t="s">
-        <v>409</v>
-      </c>
-      <c r="AB35" s="66" t="s">
-        <v>586</v>
+        <v>408</v>
+      </c>
+      <c r="AB35" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC35" s="70" t="s">
         <v>1</v>
@@ -6707,7 +6776,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C36" s="31" t="s">
         <v>255</v>
@@ -6759,7 +6828,7 @@
         <v>235</v>
       </c>
       <c r="R36" s="66" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="S36" s="66" t="s">
         <v>1</v>
@@ -6777,23 +6846,23 @@
         <v>Marcos</v>
       </c>
       <c r="W36" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X36" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-36</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-36</v>
       </c>
       <c r="Y36" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z36" s="66" t="s">
-        <v>586</v>
+      <c r="Z36" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA36" s="70" t="s">
-        <v>410</v>
-      </c>
-      <c r="AB36" s="66" t="s">
-        <v>586</v>
+        <v>409</v>
+      </c>
+      <c r="AB36" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC36" s="70" t="s">
         <v>1</v>
@@ -6804,7 +6873,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C37" s="31" t="s">
         <v>255</v>
@@ -6856,7 +6925,7 @@
         <v>239</v>
       </c>
       <c r="R37" s="66" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S37" s="66" t="s">
         <v>1</v>
@@ -6874,23 +6943,23 @@
         <v>Marcos</v>
       </c>
       <c r="W37" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X37" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-37</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-37</v>
       </c>
       <c r="Y37" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z37" s="66" t="s">
-        <v>586</v>
+      <c r="Z37" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA37" s="70" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB37" s="66" t="s">
-        <v>586</v>
+        <v>410</v>
+      </c>
+      <c r="AB37" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC37" s="70" t="s">
         <v>1</v>
@@ -6901,7 +6970,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C38" s="31" t="s">
         <v>255</v>
@@ -6953,7 +7022,7 @@
         <v>241</v>
       </c>
       <c r="R38" s="66" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="S38" s="66" t="s">
         <v>1</v>
@@ -6971,23 +7040,23 @@
         <v>Marcos</v>
       </c>
       <c r="W38" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X38" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-38</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-38</v>
       </c>
       <c r="Y38" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z38" s="66" t="s">
-        <v>586</v>
+      <c r="Z38" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA38" s="70" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB38" s="66" t="s">
-        <v>586</v>
+        <v>411</v>
+      </c>
+      <c r="AB38" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC38" s="70" t="s">
         <v>1</v>
@@ -6998,7 +7067,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C39" s="31" t="s">
         <v>255</v>
@@ -7050,7 +7119,7 @@
         <v>243</v>
       </c>
       <c r="R39" s="66" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="S39" s="66" t="s">
         <v>1</v>
@@ -7068,23 +7137,23 @@
         <v>Marcos</v>
       </c>
       <c r="W39" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X39" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-39</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-39</v>
       </c>
       <c r="Y39" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z39" s="66" t="s">
-        <v>586</v>
+      <c r="Z39" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA39" s="70" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB39" s="66" t="s">
-        <v>586</v>
+        <v>412</v>
+      </c>
+      <c r="AB39" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC39" s="70" t="s">
         <v>1</v>
@@ -7095,7 +7164,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C40" s="31" t="s">
         <v>255</v>
@@ -7147,7 +7216,7 @@
         <v>245</v>
       </c>
       <c r="R40" s="66" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S40" s="66" t="s">
         <v>1</v>
@@ -7165,23 +7234,23 @@
         <v>Marcos</v>
       </c>
       <c r="W40" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X40" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-40</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-40</v>
       </c>
       <c r="Y40" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z40" s="66" t="s">
-        <v>586</v>
+      <c r="Z40" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA40" s="70" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB40" s="66" t="s">
-        <v>586</v>
+        <v>413</v>
+      </c>
+      <c r="AB40" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC40" s="70" t="s">
         <v>1</v>
@@ -7192,10 +7261,10 @@
         <v>41</v>
       </c>
       <c r="B41" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D41" s="31" t="s">
         <v>275</v>
@@ -7244,7 +7313,7 @@
         <v>352</v>
       </c>
       <c r="R41" s="66" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S41" s="66" t="s">
         <v>1</v>
@@ -7262,23 +7331,23 @@
         <v>Pontos Cotados</v>
       </c>
       <c r="W41" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X41" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-41</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-41</v>
       </c>
       <c r="Y41" s="66" t="s">
         <v>388</v>
       </c>
-      <c r="Z41" s="66" t="s">
-        <v>586</v>
+      <c r="Z41" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA41" s="66" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB41" s="66" t="s">
-        <v>586</v>
+        <v>413</v>
+      </c>
+      <c r="AB41" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC41" s="70" t="s">
         <v>1</v>
@@ -7289,10 +7358,10 @@
         <v>42</v>
       </c>
       <c r="B42" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D42" s="31" t="s">
         <v>275</v>
@@ -7341,7 +7410,7 @@
         <v>353</v>
       </c>
       <c r="R42" s="66" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S42" s="66" t="s">
         <v>1</v>
@@ -7359,23 +7428,23 @@
         <v>Pontos Cotados</v>
       </c>
       <c r="W42" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X42" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-42</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-42</v>
       </c>
       <c r="Y42" s="66" t="s">
         <v>389</v>
       </c>
-      <c r="Z42" s="66" t="s">
-        <v>586</v>
+      <c r="Z42" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA42" s="66" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB42" s="66" t="s">
-        <v>586</v>
+        <v>414</v>
+      </c>
+      <c r="AB42" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC42" s="70" t="s">
         <v>1</v>
@@ -7386,10 +7455,10 @@
         <v>43</v>
       </c>
       <c r="B43" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D43" s="31" t="s">
         <v>275</v>
@@ -7438,7 +7507,7 @@
         <v>354</v>
       </c>
       <c r="R43" s="66" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="S43" s="66" t="s">
         <v>1</v>
@@ -7456,23 +7525,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W43" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X43" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-43</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-43</v>
       </c>
       <c r="Y43" s="66" t="s">
         <v>390</v>
       </c>
-      <c r="Z43" s="66" t="s">
-        <v>586</v>
+      <c r="Z43" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA43" s="66" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB43" s="66" t="s">
-        <v>586</v>
+        <v>414</v>
+      </c>
+      <c r="AB43" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC43" s="70" t="s">
         <v>1</v>
@@ -7483,10 +7552,10 @@
         <v>44</v>
       </c>
       <c r="B44" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D44" s="31" t="s">
         <v>275</v>
@@ -7517,11 +7586,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M44" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N44" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O44" s="69" t="str">
@@ -7535,7 +7604,7 @@
         <v>355</v>
       </c>
       <c r="R44" s="66" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="S44" s="66" t="s">
         <v>1</v>
@@ -7553,23 +7622,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W44" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X44" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-44</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-44</v>
       </c>
       <c r="Y44" s="66" t="s">
         <v>391</v>
       </c>
-      <c r="Z44" s="66" t="s">
-        <v>586</v>
+      <c r="Z44" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA44" s="66" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB44" s="66" t="s">
-        <v>586</v>
+        <v>414</v>
+      </c>
+      <c r="AB44" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC44" s="70" t="s">
         <v>1</v>
@@ -7580,10 +7649,10 @@
         <v>45</v>
       </c>
       <c r="B45" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D45" s="31" t="s">
         <v>275</v>
@@ -7614,11 +7683,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M45" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N45" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O45" s="69" t="str">
@@ -7632,7 +7701,7 @@
         <v>356</v>
       </c>
       <c r="R45" s="66" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="S45" s="66" t="s">
         <v>1</v>
@@ -7650,23 +7719,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W45" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X45" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-45</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-45</v>
       </c>
       <c r="Y45" s="66" t="s">
         <v>392</v>
       </c>
-      <c r="Z45" s="66" t="s">
-        <v>586</v>
+      <c r="Z45" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA45" s="66" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB45" s="66" t="s">
-        <v>586</v>
+        <v>414</v>
+      </c>
+      <c r="AB45" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC45" s="70" t="s">
         <v>1</v>
@@ -7677,10 +7746,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D46" s="31" t="s">
         <v>275</v>
@@ -7711,11 +7780,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M46" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N46" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O46" s="69" t="str">
@@ -7729,7 +7798,7 @@
         <v>357</v>
       </c>
       <c r="R46" s="66" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S46" s="66" t="s">
         <v>1</v>
@@ -7747,23 +7816,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W46" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X46" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-46</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-46</v>
       </c>
       <c r="Y46" s="66" t="s">
         <v>393</v>
       </c>
-      <c r="Z46" s="66" t="s">
-        <v>586</v>
+      <c r="Z46" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA46" s="66" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB46" s="66" t="s">
-        <v>586</v>
+        <v>414</v>
+      </c>
+      <c r="AB46" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC46" s="70" t="s">
         <v>1</v>
@@ -7774,10 +7843,10 @@
         <v>47</v>
       </c>
       <c r="B47" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D47" s="31" t="s">
         <v>275</v>
@@ -7808,11 +7877,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M47" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N47" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O47" s="69" t="str">
@@ -7826,7 +7895,7 @@
         <v>358</v>
       </c>
       <c r="R47" s="66" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S47" s="66" t="s">
         <v>1</v>
@@ -7844,23 +7913,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W47" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X47" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-47</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-47</v>
       </c>
       <c r="Y47" s="66" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z47" s="66" t="s">
-        <v>586</v>
+        <v>420</v>
+      </c>
+      <c r="Z47" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA47" s="66" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB47" s="66" t="s">
-        <v>586</v>
+        <v>414</v>
+      </c>
+      <c r="AB47" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC47" s="70" t="s">
         <v>1</v>
@@ -7871,10 +7940,10 @@
         <v>48</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C48" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D48" s="31" t="s">
         <v>275</v>
@@ -7905,11 +7974,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M48" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N48" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O48" s="69" t="str">
@@ -7923,7 +7992,7 @@
         <v>359</v>
       </c>
       <c r="R48" s="66" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S48" s="66" t="s">
         <v>1</v>
@@ -7941,23 +8010,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W48" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X48" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-48</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-48</v>
       </c>
       <c r="Y48" s="66" t="s">
         <v>394</v>
       </c>
-      <c r="Z48" s="66" t="s">
-        <v>586</v>
+      <c r="Z48" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA48" s="66" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB48" s="66" t="s">
-        <v>586</v>
+        <v>414</v>
+      </c>
+      <c r="AB48" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC48" s="70" t="s">
         <v>1</v>
@@ -7968,10 +8037,10 @@
         <v>49</v>
       </c>
       <c r="B49" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C49" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D49" s="31" t="s">
         <v>275</v>
@@ -8002,11 +8071,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M49" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N49" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O49" s="69" t="str">
@@ -8020,7 +8089,7 @@
         <v>360</v>
       </c>
       <c r="R49" s="66" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="S49" s="66" t="s">
         <v>1</v>
@@ -8038,23 +8107,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W49" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X49" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-49</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-49</v>
       </c>
       <c r="Y49" s="66" t="s">
         <v>395</v>
       </c>
-      <c r="Z49" s="66" t="s">
-        <v>586</v>
+      <c r="Z49" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA49" s="66" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB49" s="66" t="s">
-        <v>586</v>
+        <v>415</v>
+      </c>
+      <c r="AB49" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC49" s="70" t="s">
         <v>1</v>
@@ -8065,10 +8134,10 @@
         <v>50</v>
       </c>
       <c r="B50" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C50" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D50" s="31" t="s">
         <v>275</v>
@@ -8099,11 +8168,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M50" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N50" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Curvas de Nível</v>
       </c>
       <c r="O50" s="69" t="str">
@@ -8117,7 +8186,7 @@
         <v>361</v>
       </c>
       <c r="R50" s="66" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="S50" s="66" t="s">
         <v>1</v>
@@ -8135,23 +8204,23 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W50" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X50" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-50</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-50</v>
       </c>
       <c r="Y50" s="66" t="s">
         <v>396</v>
       </c>
-      <c r="Z50" s="66" t="s">
-        <v>586</v>
+      <c r="Z50" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA50" s="66" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB50" s="66" t="s">
-        <v>586</v>
+        <v>415</v>
+      </c>
+      <c r="AB50" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC50" s="70" t="s">
         <v>1</v>
@@ -8162,10 +8231,10 @@
         <v>51</v>
       </c>
       <c r="B51" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D51" s="31" t="s">
         <v>275</v>
@@ -8196,11 +8265,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M51" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N51" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Curvas de Nível</v>
       </c>
       <c r="O51" s="69" t="str">
@@ -8214,7 +8283,7 @@
         <v>362</v>
       </c>
       <c r="R51" s="66" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="S51" s="66" t="s">
         <v>1</v>
@@ -8232,23 +8301,23 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W51" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X51" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-51</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-51</v>
       </c>
       <c r="Y51" s="66" t="s">
         <v>396</v>
       </c>
-      <c r="Z51" s="66" t="s">
-        <v>586</v>
+      <c r="Z51" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA51" s="66" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB51" s="66" t="s">
-        <v>586</v>
+        <v>415</v>
+      </c>
+      <c r="AB51" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC51" s="70" t="s">
         <v>1</v>
@@ -8259,10 +8328,10 @@
         <v>52</v>
       </c>
       <c r="B52" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C52" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D52" s="31" t="s">
         <v>275</v>
@@ -8293,11 +8362,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M52" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N52" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Curvas de Nível</v>
       </c>
       <c r="O52" s="69" t="str">
@@ -8311,7 +8380,7 @@
         <v>363</v>
       </c>
       <c r="R52" s="66" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="S52" s="66" t="s">
         <v>1</v>
@@ -8329,23 +8398,23 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W52" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X52" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-52</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-52</v>
       </c>
       <c r="Y52" s="66" t="s">
         <v>396</v>
       </c>
-      <c r="Z52" s="66" t="s">
-        <v>586</v>
+      <c r="Z52" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA52" s="66" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB52" s="66" t="s">
-        <v>586</v>
+        <v>415</v>
+      </c>
+      <c r="AB52" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC52" s="70" t="s">
         <v>1</v>
@@ -8356,10 +8425,10 @@
         <v>53</v>
       </c>
       <c r="B53" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C53" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D53" s="31" t="s">
         <v>275</v>
@@ -8390,11 +8459,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M53" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N53" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Curvas de Nível</v>
       </c>
       <c r="O53" s="69" t="str">
@@ -8408,7 +8477,7 @@
         <v>364</v>
       </c>
       <c r="R53" s="66" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="S53" s="66" t="s">
         <v>1</v>
@@ -8426,23 +8495,23 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W53" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X53" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-53</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-53</v>
       </c>
       <c r="Y53" s="66" t="s">
         <v>396</v>
       </c>
-      <c r="Z53" s="66" t="s">
-        <v>586</v>
+      <c r="Z53" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA53" s="66" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB53" s="66" t="s">
-        <v>586</v>
+        <v>413</v>
+      </c>
+      <c r="AB53" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC53" s="70" t="s">
         <v>1</v>
@@ -8453,10 +8522,10 @@
         <v>54</v>
       </c>
       <c r="B54" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C54" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D54" s="31" t="s">
         <v>275</v>
@@ -8487,11 +8556,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M54" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N54" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Sondagens</v>
       </c>
       <c r="O54" s="69" t="str">
@@ -8505,7 +8574,7 @@
         <v>365</v>
       </c>
       <c r="R54" s="66" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="S54" s="66" t="s">
         <v>1</v>
@@ -8523,23 +8592,23 @@
         <v>Sondagens</v>
       </c>
       <c r="W54" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X54" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-54</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-54</v>
       </c>
       <c r="Y54" s="66" t="s">
         <v>388</v>
       </c>
-      <c r="Z54" s="66" t="s">
-        <v>586</v>
+      <c r="Z54" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA54" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB54" s="66" t="s">
-        <v>586</v>
+      <c r="AB54" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC54" s="70" t="s">
         <v>1</v>
@@ -8550,13 +8619,13 @@
         <v>55</v>
       </c>
       <c r="B55" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C55" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E55" s="31" t="s">
         <v>272</v>
@@ -8587,15 +8656,15 @@
         <v>Urbanísticos</v>
       </c>
       <c r="M55" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>De Planejamento</v>
       </c>
       <c r="N55" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Zonificações</v>
       </c>
       <c r="O55" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Area de Planejamento</v>
       </c>
       <c r="P55" s="69" t="s">
@@ -8605,7 +8674,7 @@
         <v>106</v>
       </c>
       <c r="R55" s="66" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="S55" s="66" t="s">
         <v>1</v>
@@ -8623,23 +8692,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W55" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X55" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-55</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-55</v>
       </c>
       <c r="Y55" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z55" s="66" t="s">
-        <v>586</v>
+      <c r="Z55" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA55" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB55" s="66" t="s">
-        <v>586</v>
+      <c r="AB55" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC55" s="70" t="s">
         <v>1</v>
@@ -8650,13 +8719,13 @@
         <v>56</v>
       </c>
       <c r="B56" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C56" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E56" s="31" t="s">
         <v>272</v>
@@ -8686,15 +8755,15 @@
         <v>Urbanísticos</v>
       </c>
       <c r="M56" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>De Planejamento</v>
       </c>
       <c r="N56" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Zonificações</v>
       </c>
       <c r="O56" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Região Administrativa</v>
       </c>
       <c r="P56" s="69" t="s">
@@ -8704,7 +8773,7 @@
         <v>108</v>
       </c>
       <c r="R56" s="66" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="S56" s="66" t="s">
         <v>1</v>
@@ -8722,23 +8791,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W56" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X56" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-56</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-56</v>
       </c>
       <c r="Y56" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z56" s="66" t="s">
-        <v>586</v>
+      <c r="Z56" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA56" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB56" s="66" t="s">
-        <v>586</v>
+      <c r="AB56" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC56" s="70" t="s">
         <v>1</v>
@@ -8749,13 +8818,13 @@
         <v>57</v>
       </c>
       <c r="B57" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C57" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E57" s="31" t="s">
         <v>272</v>
@@ -8783,15 +8852,15 @@
         <v>Urbanísticos</v>
       </c>
       <c r="M57" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>De Planejamento</v>
       </c>
       <c r="N57" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Zonificações</v>
       </c>
       <c r="O57" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Area de Interesse Especial</v>
       </c>
       <c r="P57" s="69" t="s">
@@ -8801,7 +8870,7 @@
         <v>109</v>
       </c>
       <c r="R57" s="66" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="S57" s="66" t="s">
         <v>1</v>
@@ -8819,23 +8888,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W57" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X57" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-57</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-57</v>
       </c>
       <c r="Y57" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z57" s="66" t="s">
-        <v>586</v>
+      <c r="Z57" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA57" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB57" s="66" t="s">
-        <v>586</v>
+      <c r="AB57" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC57" s="70" t="s">
         <v>1</v>
@@ -8846,13 +8915,13 @@
         <v>58</v>
       </c>
       <c r="B58" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C58" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D58" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E58" s="31" t="s">
         <v>272</v>
@@ -8898,7 +8967,7 @@
         <v>112</v>
       </c>
       <c r="R58" s="66" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="S58" s="66" t="s">
         <v>1</v>
@@ -8916,23 +8985,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W58" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X58" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-58</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-58</v>
       </c>
       <c r="Y58" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z58" s="66" t="s">
-        <v>586</v>
+      <c r="Z58" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA58" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB58" s="66" t="s">
-        <v>586</v>
+      <c r="AB58" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC58" s="70" t="s">
         <v>1</v>
@@ -8943,13 +9012,13 @@
         <v>59</v>
       </c>
       <c r="B59" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C59" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D59" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E59" s="31" t="s">
         <v>272</v>
@@ -8995,7 +9064,7 @@
         <v>115</v>
       </c>
       <c r="R59" s="66" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="S59" s="66" t="s">
         <v>1</v>
@@ -9013,23 +9082,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W59" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X59" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-59</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-59</v>
       </c>
       <c r="Y59" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z59" s="66" t="s">
-        <v>586</v>
+      <c r="Z59" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA59" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB59" s="66" t="s">
-        <v>586</v>
+      <c r="AB59" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC59" s="70" t="s">
         <v>1</v>
@@ -9040,13 +9109,13 @@
         <v>60</v>
       </c>
       <c r="B60" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C60" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D60" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E60" s="31" t="s">
         <v>272</v>
@@ -9092,7 +9161,7 @@
         <v>118</v>
       </c>
       <c r="R60" s="66" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="S60" s="66" t="s">
         <v>1</v>
@@ -9110,23 +9179,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W60" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X60" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-60</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-60</v>
       </c>
       <c r="Y60" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z60" s="66" t="s">
-        <v>586</v>
+      <c r="Z60" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA60" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB60" s="66" t="s">
-        <v>586</v>
+      <c r="AB60" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC60" s="70" t="s">
         <v>1</v>
@@ -9137,13 +9206,13 @@
         <v>61</v>
       </c>
       <c r="B61" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C61" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D61" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E61" s="31" t="s">
         <v>272</v>
@@ -9189,7 +9258,7 @@
         <v>119</v>
       </c>
       <c r="R61" s="66" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="S61" s="66" t="s">
         <v>1</v>
@@ -9207,23 +9276,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W61" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X61" s="67" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-61</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-61</v>
       </c>
       <c r="Y61" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z61" s="66" t="s">
-        <v>586</v>
+      <c r="Z61" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA61" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB61" s="66" t="s">
-        <v>586</v>
+      <c r="AB61" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC61" s="70" t="s">
         <v>1</v>
@@ -9234,13 +9303,13 @@
         <v>62</v>
       </c>
       <c r="B62" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C62" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D62" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E62" s="31" t="s">
         <v>272</v>
@@ -9286,7 +9355,7 @@
         <v>118</v>
       </c>
       <c r="R62" s="66" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="S62" s="66" t="s">
         <v>1</v>
@@ -9304,23 +9373,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W62" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X62" s="67" t="str">
-        <f t="shared" ref="X62:X100" si="13">CONCATENATE("Key-BRASIL-",A62)</f>
-        <v>Key-BRASIL-62</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-62</v>
       </c>
       <c r="Y62" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z62" s="66" t="s">
-        <v>586</v>
+      <c r="Z62" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA62" s="66" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB62" s="66" t="s">
-        <v>586</v>
+        <v>416</v>
+      </c>
+      <c r="AB62" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC62" s="70" t="s">
         <v>1</v>
@@ -9331,13 +9400,13 @@
         <v>63</v>
       </c>
       <c r="B63" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C63" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E63" s="31" t="s">
         <v>271</v>
@@ -9383,7 +9452,7 @@
         <v>123</v>
       </c>
       <c r="R63" s="66" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="S63" s="66" t="s">
         <v>1</v>
@@ -9401,23 +9470,23 @@
         <v>Frações</v>
       </c>
       <c r="W63" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X63" s="67" t="str">
-        <f t="shared" si="13"/>
-        <v>Key-BRASIL-63</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-63</v>
       </c>
       <c r="Y63" s="66" t="s">
         <v>397</v>
       </c>
-      <c r="Z63" s="66" t="s">
-        <v>586</v>
+      <c r="Z63" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA63" s="66" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB63" s="66" t="s">
-        <v>586</v>
+        <v>416</v>
+      </c>
+      <c r="AB63" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC63" s="70" t="s">
         <v>1</v>
@@ -9428,13 +9497,13 @@
         <v>64</v>
       </c>
       <c r="B64" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C64" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E64" s="31" t="s">
         <v>271</v>
@@ -9480,7 +9549,7 @@
         <v>125</v>
       </c>
       <c r="R64" s="66" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="S64" s="66" t="s">
         <v>1</v>
@@ -9498,23 +9567,23 @@
         <v>Frações</v>
       </c>
       <c r="W64" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X64" s="67" t="str">
-        <f t="shared" si="13"/>
-        <v>Key-BRASIL-64</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-64</v>
       </c>
       <c r="Y64" s="66" t="s">
         <v>397</v>
       </c>
-      <c r="Z64" s="66" t="s">
-        <v>586</v>
+      <c r="Z64" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA64" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB64" s="66" t="s">
-        <v>586</v>
+        <v>417</v>
+      </c>
+      <c r="AB64" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC64" s="70" t="s">
         <v>1</v>
@@ -9525,13 +9594,13 @@
         <v>65</v>
       </c>
       <c r="B65" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C65" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E65" s="31" t="s">
         <v>271</v>
@@ -9577,7 +9646,7 @@
         <v>127</v>
       </c>
       <c r="R65" s="66" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="S65" s="66" t="s">
         <v>1</v>
@@ -9595,23 +9664,23 @@
         <v>Frações</v>
       </c>
       <c r="W65" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X65" s="67" t="str">
-        <f t="shared" si="13"/>
-        <v>Key-BRASIL-65</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-65</v>
       </c>
       <c r="Y65" s="66" t="s">
         <v>398</v>
       </c>
-      <c r="Z65" s="66" t="s">
-        <v>586</v>
+      <c r="Z65" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA65" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB65" s="66" t="s">
-        <v>586</v>
+        <v>417</v>
+      </c>
+      <c r="AB65" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC65" s="70" t="s">
         <v>1</v>
@@ -9622,13 +9691,13 @@
         <v>66</v>
       </c>
       <c r="B66" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C66" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E66" s="31" t="s">
         <v>271</v>
@@ -9674,7 +9743,7 @@
         <v>129</v>
       </c>
       <c r="R66" s="66" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="S66" s="66" t="s">
         <v>1</v>
@@ -9692,23 +9761,23 @@
         <v>Frações</v>
       </c>
       <c r="W66" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X66" s="67" t="str">
-        <f t="shared" si="13"/>
-        <v>Key-BRASIL-66</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL-SP-66</v>
       </c>
       <c r="Y66" s="66" t="s">
         <v>398</v>
       </c>
-      <c r="Z66" s="66" t="s">
-        <v>586</v>
+      <c r="Z66" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA66" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB66" s="66" t="s">
-        <v>586</v>
+        <v>417</v>
+      </c>
+      <c r="AB66" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC66" s="70" t="s">
         <v>1</v>
@@ -9719,13 +9788,13 @@
         <v>67</v>
       </c>
       <c r="B67" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C67" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D67" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E67" s="31" t="s">
         <v>271</v>
@@ -9771,7 +9840,7 @@
         <v>131</v>
       </c>
       <c r="R67" s="66" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="S67" s="66" t="s">
         <v>1</v>
@@ -9789,23 +9858,23 @@
         <v>Frações</v>
       </c>
       <c r="W67" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X67" s="67" t="str">
-        <f t="shared" si="13"/>
-        <v>Key-BRASIL-67</v>
+        <f t="shared" ref="X67:X101" si="13">CONCATENATE("Key-BRASIL-SP-",A67)</f>
+        <v>Key-BRASIL-SP-67</v>
       </c>
       <c r="Y67" s="66" t="s">
         <v>398</v>
       </c>
-      <c r="Z67" s="66" t="s">
-        <v>586</v>
+      <c r="Z67" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA67" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB67" s="66" t="s">
-        <v>586</v>
+      <c r="AB67" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC67" s="70" t="s">
         <v>1</v>
@@ -9816,10 +9885,10 @@
         <v>68</v>
       </c>
       <c r="B68" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C68" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C68" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D68" s="31" t="s">
         <v>266</v>
@@ -9869,7 +9938,7 @@
         <v>366</v>
       </c>
       <c r="R68" s="66" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="S68" s="66" t="s">
         <v>1</v>
@@ -9887,23 +9956,23 @@
         <v>Construídas</v>
       </c>
       <c r="W68" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X68" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-68</v>
+        <v>Key-BRASIL-SP-68</v>
       </c>
       <c r="Y68" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z68" s="66" t="s">
-        <v>586</v>
+      <c r="Z68" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA68" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB68" s="66" t="s">
-        <v>586</v>
+      <c r="AB68" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC68" s="70" t="s">
         <v>1</v>
@@ -9914,10 +9983,10 @@
         <v>69</v>
       </c>
       <c r="B69" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C69" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C69" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D69" s="31" t="s">
         <v>266</v>
@@ -9967,7 +10036,7 @@
         <v>133</v>
       </c>
       <c r="R69" s="66" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="S69" s="66" t="s">
         <v>1</v>
@@ -9985,23 +10054,23 @@
         <v>Construídas</v>
       </c>
       <c r="W69" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X69" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-69</v>
+        <v>Key-BRASIL-SP-69</v>
       </c>
       <c r="Y69" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z69" s="66" t="s">
-        <v>586</v>
+      <c r="Z69" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA69" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB69" s="66" t="s">
-        <v>586</v>
+      <c r="AB69" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC69" s="70" t="s">
         <v>1</v>
@@ -10012,10 +10081,10 @@
         <v>70</v>
       </c>
       <c r="B70" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C70" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C70" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D70" s="31" t="s">
         <v>266</v>
@@ -10065,7 +10134,7 @@
         <v>135</v>
       </c>
       <c r="R70" s="66" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="S70" s="66" t="s">
         <v>1</v>
@@ -10083,23 +10152,23 @@
         <v>Construídas</v>
       </c>
       <c r="W70" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X70" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-70</v>
+        <v>Key-BRASIL-SP-70</v>
       </c>
       <c r="Y70" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z70" s="66" t="s">
-        <v>586</v>
+      <c r="Z70" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA70" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB70" s="66" t="s">
-        <v>586</v>
+      <c r="AB70" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC70" s="70" t="s">
         <v>1</v>
@@ -10110,10 +10179,10 @@
         <v>71</v>
       </c>
       <c r="B71" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C71" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C71" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D71" s="31" t="s">
         <v>266</v>
@@ -10163,7 +10232,7 @@
         <v>136</v>
       </c>
       <c r="R71" s="66" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="S71" s="66" t="s">
         <v>1</v>
@@ -10181,23 +10250,23 @@
         <v>Construídas</v>
       </c>
       <c r="W71" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X71" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-71</v>
+        <v>Key-BRASIL-SP-71</v>
       </c>
       <c r="Y71" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z71" s="66" t="s">
-        <v>586</v>
+      <c r="Z71" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA71" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB71" s="66" t="s">
-        <v>586</v>
+      <c r="AB71" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC71" s="70" t="s">
         <v>1</v>
@@ -10208,10 +10277,10 @@
         <v>72</v>
       </c>
       <c r="B72" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C72" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C72" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D72" s="31" t="s">
         <v>266</v>
@@ -10261,7 +10330,7 @@
         <v>138</v>
       </c>
       <c r="R72" s="66" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="S72" s="66" t="s">
         <v>1</v>
@@ -10279,23 +10348,23 @@
         <v>Construídas</v>
       </c>
       <c r="W72" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X72" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-72</v>
+        <v>Key-BRASIL-SP-72</v>
       </c>
       <c r="Y72" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z72" s="66" t="s">
-        <v>586</v>
+      <c r="Z72" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA72" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB72" s="66" t="s">
-        <v>586</v>
+      <c r="AB72" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC72" s="70" t="s">
         <v>1</v>
@@ -10306,10 +10375,10 @@
         <v>73</v>
       </c>
       <c r="B73" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C73" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C73" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D73" s="31" t="s">
         <v>266</v>
@@ -10358,7 +10427,7 @@
         <v>141</v>
       </c>
       <c r="R73" s="66" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="S73" s="66" t="s">
         <v>1</v>
@@ -10376,23 +10445,23 @@
         <v>Construídas</v>
       </c>
       <c r="W73" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X73" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-73</v>
+        <v>Key-BRASIL-SP-73</v>
       </c>
       <c r="Y73" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z73" s="66" t="s">
-        <v>586</v>
+      <c r="Z73" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA73" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB73" s="66" t="s">
-        <v>586</v>
+      <c r="AB73" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC73" s="70" t="s">
         <v>1</v>
@@ -10403,10 +10472,10 @@
         <v>74</v>
       </c>
       <c r="B74" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C74" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C74" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D74" s="31" t="s">
         <v>266</v>
@@ -10455,7 +10524,7 @@
         <v>142</v>
       </c>
       <c r="R74" s="66" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="S74" s="66" t="s">
         <v>1</v>
@@ -10473,23 +10542,23 @@
         <v>Construídas</v>
       </c>
       <c r="W74" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X74" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-74</v>
+        <v>Key-BRASIL-SP-74</v>
       </c>
       <c r="Y74" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z74" s="66" t="s">
-        <v>586</v>
+      <c r="Z74" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA74" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB74" s="66" t="s">
-        <v>586</v>
+        <v>417</v>
+      </c>
+      <c r="AB74" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC74" s="70" t="s">
         <v>1</v>
@@ -10500,10 +10569,10 @@
         <v>75</v>
       </c>
       <c r="B75" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C75" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C75" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D75" s="31" t="s">
         <v>267</v>
@@ -10553,7 +10622,7 @@
         <v>145</v>
       </c>
       <c r="R75" s="66" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="S75" s="66" t="s">
         <v>1</v>
@@ -10571,23 +10640,23 @@
         <v>Organizativas</v>
       </c>
       <c r="W75" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X75" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-75</v>
+        <v>Key-BRASIL-SP-75</v>
       </c>
       <c r="Y75" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z75" s="66" t="s">
-        <v>586</v>
+      <c r="Z75" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA75" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB75" s="66" t="s">
-        <v>586</v>
+        <v>417</v>
+      </c>
+      <c r="AB75" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC75" s="70" t="s">
         <v>1</v>
@@ -10598,10 +10667,10 @@
         <v>76</v>
       </c>
       <c r="B76" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C76" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C76" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D76" s="31" t="s">
         <v>267</v>
@@ -10650,7 +10719,7 @@
         <v>146</v>
       </c>
       <c r="R76" s="66" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="S76" s="66" t="s">
         <v>1</v>
@@ -10668,23 +10737,23 @@
         <v>Organizativas</v>
       </c>
       <c r="W76" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X76" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-76</v>
+        <v>Key-BRASIL-SP-76</v>
       </c>
       <c r="Y76" s="66" t="s">
         <v>399</v>
       </c>
-      <c r="Z76" s="66" t="s">
-        <v>586</v>
+      <c r="Z76" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA76" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB76" s="66" t="s">
-        <v>586</v>
+        <v>417</v>
+      </c>
+      <c r="AB76" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC76" s="70" t="s">
         <v>1</v>
@@ -10695,10 +10764,10 @@
         <v>77</v>
       </c>
       <c r="B77" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C77" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C77" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D77" s="31" t="s">
         <v>267</v>
@@ -10747,7 +10816,7 @@
         <v>148</v>
       </c>
       <c r="R77" s="66" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="S77" s="66" t="s">
         <v>1</v>
@@ -10765,23 +10834,23 @@
         <v>Organizativas</v>
       </c>
       <c r="W77" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X77" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-77</v>
+        <v>Key-BRASIL-SP-77</v>
       </c>
       <c r="Y77" s="66" t="s">
         <v>399</v>
       </c>
-      <c r="Z77" s="66" t="s">
-        <v>586</v>
+      <c r="Z77" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA77" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB77" s="66" t="s">
-        <v>586</v>
+        <v>417</v>
+      </c>
+      <c r="AB77" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC77" s="70" t="s">
         <v>1</v>
@@ -10792,10 +10861,10 @@
         <v>78</v>
       </c>
       <c r="B78" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C78" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C78" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D78" s="31" t="s">
         <v>267</v>
@@ -10844,7 +10913,7 @@
         <v>149</v>
       </c>
       <c r="R78" s="66" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="S78" s="66" t="s">
         <v>1</v>
@@ -10862,23 +10931,23 @@
         <v>Organizativas</v>
       </c>
       <c r="W78" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X78" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-78</v>
+        <v>Key-BRASIL-SP-78</v>
       </c>
       <c r="Y78" s="66" t="s">
         <v>399</v>
       </c>
-      <c r="Z78" s="66" t="s">
-        <v>586</v>
+      <c r="Z78" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA78" s="66" t="s">
-        <v>419</v>
-      </c>
-      <c r="AB78" s="66" t="s">
-        <v>586</v>
+        <v>418</v>
+      </c>
+      <c r="AB78" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC78" s="70" t="s">
         <v>1</v>
@@ -10889,10 +10958,10 @@
         <v>79</v>
       </c>
       <c r="B79" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C79" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C79" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D79" s="31" t="s">
         <v>267</v>
@@ -10941,7 +11010,7 @@
         <v>150</v>
       </c>
       <c r="R79" s="66" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="S79" s="66" t="s">
         <v>1</v>
@@ -10959,23 +11028,23 @@
         <v>Distribuição</v>
       </c>
       <c r="W79" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X79" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-79</v>
+        <v>Key-BRASIL-SP-79</v>
       </c>
       <c r="Y79" s="66" t="s">
         <v>400</v>
       </c>
-      <c r="Z79" s="66" t="s">
-        <v>586</v>
+      <c r="Z79" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA79" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB79" s="66" t="s">
-        <v>586</v>
+        <v>417</v>
+      </c>
+      <c r="AB79" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC79" s="70" t="s">
         <v>1</v>
@@ -10986,10 +11055,10 @@
         <v>80</v>
       </c>
       <c r="B80" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C80" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C80" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D80" s="31" t="s">
         <v>267</v>
@@ -11038,7 +11107,7 @@
         <v>151</v>
       </c>
       <c r="R80" s="66" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="S80" s="66" t="s">
         <v>1</v>
@@ -11056,23 +11125,23 @@
         <v>Distribuição</v>
       </c>
       <c r="W80" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X80" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-80</v>
+        <v>Key-BRASIL-SP-80</v>
       </c>
       <c r="Y80" s="66" t="s">
         <v>399</v>
       </c>
-      <c r="Z80" s="66" t="s">
-        <v>586</v>
+      <c r="Z80" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA80" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB80" s="66" t="s">
-        <v>586</v>
+        <v>417</v>
+      </c>
+      <c r="AB80" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC80" s="70" t="s">
         <v>1</v>
@@ -11083,10 +11152,10 @@
         <v>81</v>
       </c>
       <c r="B81" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C81" s="31" t="s">
         <v>441</v>
-      </c>
-      <c r="C81" s="31" t="s">
-        <v>443</v>
       </c>
       <c r="D81" s="31" t="s">
         <v>267</v>
@@ -11135,7 +11204,7 @@
         <v>153</v>
       </c>
       <c r="R81" s="66" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="S81" s="66" t="s">
         <v>1</v>
@@ -11153,23 +11222,23 @@
         <v>Distribuição</v>
       </c>
       <c r="W81" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X81" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-81</v>
+        <v>Key-BRASIL-SP-81</v>
       </c>
       <c r="Y81" s="66" t="s">
         <v>399</v>
       </c>
-      <c r="Z81" s="66" t="s">
-        <v>586</v>
+      <c r="Z81" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA81" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB81" s="66" t="s">
-        <v>586</v>
+        <v>419</v>
+      </c>
+      <c r="AB81" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC81" s="70" t="s">
         <v>1</v>
@@ -11180,13 +11249,13 @@
         <v>82</v>
       </c>
       <c r="B82" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C82" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D82" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E82" s="31" t="s">
         <v>154</v>
@@ -11232,7 +11301,7 @@
         <v>156</v>
       </c>
       <c r="R82" s="66" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="S82" s="66" t="s">
         <v>1</v>
@@ -11250,23 +11319,23 @@
         <v>Saúde</v>
       </c>
       <c r="W82" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X82" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-82</v>
+        <v>Key-BRASIL-SP-82</v>
       </c>
       <c r="Y82" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="Z82" s="66" t="s">
-        <v>586</v>
+      <c r="Z82" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA82" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB82" s="66" t="s">
-        <v>586</v>
+        <v>419</v>
+      </c>
+      <c r="AB82" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC82" s="70" t="s">
         <v>1</v>
@@ -11277,13 +11346,13 @@
         <v>83</v>
       </c>
       <c r="B83" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C83" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D83" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E83" s="31" t="s">
         <v>154</v>
@@ -11329,7 +11398,7 @@
         <v>158</v>
       </c>
       <c r="R83" s="66" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="S83" s="66" t="s">
         <v>1</v>
@@ -11347,23 +11416,23 @@
         <v>Saúde</v>
       </c>
       <c r="W83" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X83" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-83</v>
+        <v>Key-BRASIL-SP-83</v>
       </c>
       <c r="Y83" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="Z83" s="66" t="s">
-        <v>586</v>
+      <c r="Z83" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA83" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB83" s="66" t="s">
-        <v>586</v>
+        <v>419</v>
+      </c>
+      <c r="AB83" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC83" s="70" t="s">
         <v>1</v>
@@ -11374,13 +11443,13 @@
         <v>84</v>
       </c>
       <c r="B84" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C84" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D84" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E84" s="31" t="s">
         <v>154</v>
@@ -11426,7 +11495,7 @@
         <v>160</v>
       </c>
       <c r="R84" s="66" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="S84" s="66" t="s">
         <v>1</v>
@@ -11444,23 +11513,23 @@
         <v>Saúde</v>
       </c>
       <c r="W84" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X84" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-84</v>
+        <v>Key-BRASIL-SP-84</v>
       </c>
       <c r="Y84" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="Z84" s="66" t="s">
-        <v>586</v>
+      <c r="Z84" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA84" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB84" s="66" t="s">
-        <v>586</v>
+        <v>419</v>
+      </c>
+      <c r="AB84" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC84" s="70" t="s">
         <v>1</v>
@@ -11471,13 +11540,13 @@
         <v>85</v>
       </c>
       <c r="B85" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C85" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D85" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E85" s="31" t="s">
         <v>154</v>
@@ -11523,7 +11592,7 @@
         <v>163</v>
       </c>
       <c r="R85" s="66" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="S85" s="66" t="s">
         <v>1</v>
@@ -11541,23 +11610,23 @@
         <v>Saúde</v>
       </c>
       <c r="W85" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X85" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-85</v>
+        <v>Key-BRASIL-SP-85</v>
       </c>
       <c r="Y85" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="Z85" s="66" t="s">
-        <v>586</v>
+      <c r="Z85" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA85" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB85" s="66" t="s">
-        <v>586</v>
+        <v>419</v>
+      </c>
+      <c r="AB85" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC85" s="70" t="s">
         <v>1</v>
@@ -11568,13 +11637,13 @@
         <v>86</v>
       </c>
       <c r="B86" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C86" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D86" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E86" s="31" t="s">
         <v>154</v>
@@ -11620,7 +11689,7 @@
         <v>166</v>
       </c>
       <c r="R86" s="66" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="S86" s="66" t="s">
         <v>1</v>
@@ -11638,23 +11707,23 @@
         <v>Saúde</v>
       </c>
       <c r="W86" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X86" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-86</v>
+        <v>Key-BRASIL-SP-86</v>
       </c>
       <c r="Y86" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="Z86" s="66" t="s">
-        <v>586</v>
+      <c r="Z86" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA86" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB86" s="66" t="s">
-        <v>586</v>
+        <v>419</v>
+      </c>
+      <c r="AB86" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC86" s="70" t="s">
         <v>1</v>
@@ -11665,13 +11734,13 @@
         <v>87</v>
       </c>
       <c r="B87" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C87" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D87" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E87" s="31" t="s">
         <v>270</v>
@@ -11717,7 +11786,7 @@
         <v>168</v>
       </c>
       <c r="R87" s="66" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="S87" s="66" t="s">
         <v>1</v>
@@ -11735,23 +11804,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W87" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X87" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-87</v>
+        <v>Key-BRASIL-SP-87</v>
       </c>
       <c r="Y87" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="Z87" s="66" t="s">
-        <v>586</v>
+      <c r="Z87" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA87" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB87" s="66" t="s">
-        <v>586</v>
+        <v>419</v>
+      </c>
+      <c r="AB87" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC87" s="70" t="s">
         <v>1</v>
@@ -11762,13 +11831,13 @@
         <v>88</v>
       </c>
       <c r="B88" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C88" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D88" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E88" s="31" t="s">
         <v>270</v>
@@ -11814,7 +11883,7 @@
         <v>170</v>
       </c>
       <c r="R88" s="66" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="S88" s="66" t="s">
         <v>1</v>
@@ -11832,23 +11901,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W88" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X88" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-88</v>
+        <v>Key-BRASIL-SP-88</v>
       </c>
       <c r="Y88" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="Z88" s="66" t="s">
-        <v>586</v>
+      <c r="Z88" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA88" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB88" s="66" t="s">
-        <v>586</v>
+        <v>419</v>
+      </c>
+      <c r="AB88" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC88" s="70" t="s">
         <v>1</v>
@@ -11859,13 +11928,13 @@
         <v>89</v>
       </c>
       <c r="B89" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C89" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D89" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E89" s="31" t="s">
         <v>270</v>
@@ -11911,7 +11980,7 @@
         <v>172</v>
       </c>
       <c r="R89" s="66" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="S89" s="66" t="s">
         <v>1</v>
@@ -11929,23 +11998,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W89" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X89" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-89</v>
+        <v>Key-BRASIL-SP-89</v>
       </c>
       <c r="Y89" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="Z89" s="66" t="s">
-        <v>586</v>
+      <c r="Z89" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA89" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB89" s="66" t="s">
-        <v>586</v>
+        <v>419</v>
+      </c>
+      <c r="AB89" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC89" s="70" t="s">
         <v>1</v>
@@ -11956,13 +12025,13 @@
         <v>90</v>
       </c>
       <c r="B90" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C90" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D90" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E90" s="31" t="s">
         <v>270</v>
@@ -12008,7 +12077,7 @@
         <v>174</v>
       </c>
       <c r="R90" s="66" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="S90" s="66" t="s">
         <v>1</v>
@@ -12026,23 +12095,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W90" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X90" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-90</v>
+        <v>Key-BRASIL-SP-90</v>
       </c>
       <c r="Y90" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="Z90" s="66" t="s">
-        <v>586</v>
+      <c r="Z90" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA90" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB90" s="66" t="s">
-        <v>586</v>
+        <v>419</v>
+      </c>
+      <c r="AB90" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC90" s="70" t="s">
         <v>1</v>
@@ -12053,13 +12122,13 @@
         <v>91</v>
       </c>
       <c r="B91" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C91" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D91" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E91" s="31" t="s">
         <v>270</v>
@@ -12105,7 +12174,7 @@
         <v>369</v>
       </c>
       <c r="R91" s="66" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="S91" s="66" t="s">
         <v>1</v>
@@ -12123,23 +12192,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W91" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X91" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-91</v>
+        <v>Key-BRASIL-SP-91</v>
       </c>
       <c r="Y91" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="Z91" s="66" t="s">
-        <v>586</v>
+      <c r="Z91" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA91" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB91" s="66" t="s">
-        <v>586</v>
+        <v>419</v>
+      </c>
+      <c r="AB91" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC91" s="70" t="s">
         <v>1</v>
@@ -12150,13 +12219,13 @@
         <v>92</v>
       </c>
       <c r="B92" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C92" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D92" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E92" s="31" t="s">
         <v>270</v>
@@ -12202,7 +12271,7 @@
         <v>372</v>
       </c>
       <c r="R92" s="66" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="S92" s="66" t="s">
         <v>1</v>
@@ -12220,23 +12289,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W92" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X92" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-92</v>
+        <v>Key-BRASIL-SP-92</v>
       </c>
       <c r="Y92" s="66" t="s">
         <v>401</v>
       </c>
-      <c r="Z92" s="66" t="s">
-        <v>586</v>
+      <c r="Z92" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA92" s="66" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB92" s="66" t="s">
-        <v>586</v>
+        <v>413</v>
+      </c>
+      <c r="AB92" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC92" s="70" t="s">
         <v>1</v>
@@ -12247,13 +12316,13 @@
         <v>93</v>
       </c>
       <c r="B93" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C93" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D93" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E93" s="31" t="s">
         <v>175</v>
@@ -12299,7 +12368,7 @@
         <v>178</v>
       </c>
       <c r="R93" s="66" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="S93" s="66" t="s">
         <v>1</v>
@@ -12317,23 +12386,23 @@
         <v>INMET</v>
       </c>
       <c r="W93" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X93" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-93</v>
+        <v>Key-BRASIL-SP-93</v>
       </c>
       <c r="Y93" s="66" t="s">
         <v>402</v>
       </c>
-      <c r="Z93" s="66" t="s">
-        <v>586</v>
+      <c r="Z93" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA93" s="66" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB93" s="66" t="s">
-        <v>586</v>
+        <v>413</v>
+      </c>
+      <c r="AB93" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC93" s="70" t="s">
         <v>1</v>
@@ -12344,19 +12413,19 @@
         <v>94</v>
       </c>
       <c r="B94" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C94" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D94" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E94" s="31" t="s">
         <v>175</v>
       </c>
       <c r="F94" s="37" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G94" s="68" t="s">
         <v>1</v>
@@ -12390,13 +12459,13 @@
         <v>Estação Meteorológica Automática</v>
       </c>
       <c r="P94" s="69" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="Q94" s="69" t="s">
         <v>178</v>
       </c>
       <c r="R94" s="66" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="S94" s="66" t="s">
         <v>1</v>
@@ -12414,23 +12483,23 @@
         <v>INMET</v>
       </c>
       <c r="W94" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X94" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-94</v>
+        <v>Key-BRASIL-SP-94</v>
       </c>
       <c r="Y94" s="66" t="s">
         <v>402</v>
       </c>
-      <c r="Z94" s="66" t="s">
-        <v>586</v>
+      <c r="Z94" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA94" s="66" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB94" s="66" t="s">
-        <v>586</v>
+        <v>413</v>
+      </c>
+      <c r="AB94" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC94" s="70" t="s">
         <v>1</v>
@@ -12441,19 +12510,19 @@
         <v>95</v>
       </c>
       <c r="B95" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C95" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D95" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E95" s="31" t="s">
         <v>175</v>
       </c>
       <c r="F95" s="37" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G95" s="68" t="s">
         <v>1</v>
@@ -12487,13 +12556,13 @@
         <v>Estação Meteorológica Convencional</v>
       </c>
       <c r="P95" s="69" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="Q95" s="69" t="s">
         <v>178</v>
       </c>
       <c r="R95" s="66" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="S95" s="66" t="s">
         <v>1</v>
@@ -12511,23 +12580,23 @@
         <v>INMET</v>
       </c>
       <c r="W95" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X95" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-95</v>
+        <v>Key-BRASIL-SP-95</v>
       </c>
       <c r="Y95" s="66" t="s">
         <v>402</v>
       </c>
-      <c r="Z95" s="66" t="s">
-        <v>586</v>
+      <c r="Z95" s="77" t="s">
+        <v>1</v>
       </c>
       <c r="AA95" s="66" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB95" s="66" t="s">
-        <v>586</v>
+        <v>413</v>
+      </c>
+      <c r="AB95" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC95" s="70" t="s">
         <v>1</v>
@@ -12538,13 +12607,13 @@
         <v>96</v>
       </c>
       <c r="B96" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C96" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D96" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E96" s="31" t="s">
         <v>179</v>
@@ -12590,7 +12659,7 @@
         <v>182</v>
       </c>
       <c r="R96" s="66" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="S96" s="66" t="s">
         <v>1</v>
@@ -12608,23 +12677,23 @@
         <v>IBGE</v>
       </c>
       <c r="W96" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X96" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-96</v>
-      </c>
-      <c r="Y96" s="66" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z96" s="66" t="s">
-        <v>586</v>
-      </c>
-      <c r="AA96" s="66" t="s">
-        <v>421</v>
-      </c>
-      <c r="AB96" s="66" t="s">
-        <v>586</v>
+        <v>Key-BRASIL-SP-96</v>
+      </c>
+      <c r="Y96" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z96" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA96" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB96" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC96" s="70" t="s">
         <v>1</v>
@@ -12635,13 +12704,13 @@
         <v>97</v>
       </c>
       <c r="B97" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C97" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D97" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E97" s="31" t="s">
         <v>179</v>
@@ -12687,7 +12756,7 @@
         <v>182</v>
       </c>
       <c r="R97" s="66" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="S97" s="66" t="s">
         <v>1</v>
@@ -12705,23 +12774,23 @@
         <v>IBGE</v>
       </c>
       <c r="W97" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X97" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-97</v>
-      </c>
-      <c r="Y97" s="66" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z97" s="66" t="s">
-        <v>586</v>
-      </c>
-      <c r="AA97" s="66" t="s">
-        <v>421</v>
-      </c>
-      <c r="AB97" s="66" t="s">
-        <v>586</v>
+        <v>Key-BRASIL-SP-97</v>
+      </c>
+      <c r="Y97" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z97" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA97" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB97" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC97" s="70" t="s">
         <v>1</v>
@@ -12732,13 +12801,13 @@
         <v>98</v>
       </c>
       <c r="B98" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C98" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D98" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E98" s="31" t="s">
         <v>179</v>
@@ -12784,7 +12853,7 @@
         <v>186</v>
       </c>
       <c r="R98" s="66" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="S98" s="66" t="s">
         <v>1</v>
@@ -12802,23 +12871,23 @@
         <v>IBGE</v>
       </c>
       <c r="W98" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X98" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-98</v>
-      </c>
-      <c r="Y98" s="66" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z98" s="66" t="s">
-        <v>586</v>
-      </c>
-      <c r="AA98" s="66" t="s">
-        <v>421</v>
-      </c>
-      <c r="AB98" s="66" t="s">
-        <v>586</v>
+        <v>Key-BRASIL-SP-98</v>
+      </c>
+      <c r="Y98" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z98" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA98" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB98" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC98" s="70" t="s">
         <v>1</v>
@@ -12829,13 +12898,13 @@
         <v>99</v>
       </c>
       <c r="B99" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C99" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D99" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E99" s="31" t="s">
         <v>179</v>
@@ -12881,7 +12950,7 @@
         <v>189</v>
       </c>
       <c r="R99" s="66" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="S99" s="66" t="s">
         <v>1</v>
@@ -12899,23 +12968,23 @@
         <v>IBGE</v>
       </c>
       <c r="W99" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X99" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-99</v>
-      </c>
-      <c r="Y99" s="66" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z99" s="66" t="s">
-        <v>586</v>
-      </c>
-      <c r="AA99" s="66" t="s">
-        <v>421</v>
-      </c>
-      <c r="AB99" s="66" t="s">
-        <v>586</v>
+        <v>Key-BRASIL-SP-99</v>
+      </c>
+      <c r="Y99" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z99" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA99" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB99" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC99" s="70" t="s">
         <v>1</v>
@@ -12926,13 +12995,13 @@
         <v>100</v>
       </c>
       <c r="B100" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D100" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E100" s="31" t="s">
         <v>179</v>
@@ -12978,7 +13047,7 @@
         <v>192</v>
       </c>
       <c r="R100" s="66" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="S100" s="66" t="s">
         <v>1</v>
@@ -12996,95 +13065,200 @@
         <v>IBGE</v>
       </c>
       <c r="W100" s="66" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="X100" s="67" t="str">
         <f t="shared" si="13"/>
-        <v>Key-BRASIL-100</v>
-      </c>
-      <c r="Y100" s="66" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z100" s="66" t="s">
+        <v>Key-BRASIL-SP-100</v>
+      </c>
+      <c r="Y100" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z100" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA100" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB100" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC100" s="70" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" s="78" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="62">
+        <v>101</v>
+      </c>
+      <c r="B101" s="72" t="s">
         <v>586</v>
       </c>
-      <c r="AA100" s="66" t="s">
-        <v>421</v>
-      </c>
-      <c r="AB100" s="66" t="s">
-        <v>586</v>
-      </c>
-      <c r="AC100" s="70" t="s">
+      <c r="C101" s="73" t="s">
+        <v>587</v>
+      </c>
+      <c r="D101" s="73" t="s">
+        <v>588</v>
+      </c>
+      <c r="E101" s="73" t="s">
+        <v>589</v>
+      </c>
+      <c r="F101" s="73" t="s">
+        <v>590</v>
+      </c>
+      <c r="G101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="I101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="J101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="K101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="L101" s="75" t="str">
+        <f t="shared" ref="L101:O101" si="16">SUBSTITUTE(CONCATENATE("", C101), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M101" s="75" t="str">
+        <f t="shared" si="16"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N101" s="75" t="str">
+        <f t="shared" si="16"/>
+        <v>Macros</v>
+      </c>
+      <c r="O101" s="75" t="str">
+        <f t="shared" si="16"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P101" s="76" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q101" s="76" t="s">
+        <v>592</v>
+      </c>
+      <c r="R101" s="76" t="s">
+        <v>593</v>
+      </c>
+      <c r="S101" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="T101" s="76" t="str">
+        <f t="shared" ref="T101:V101" si="17">SUBSTITUTE(C101, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U101" s="76" t="str">
+        <f t="shared" si="17"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V101" s="66" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="W101" s="66" t="s">
+        <v>438</v>
+      </c>
+      <c r="X101" s="67" t="str">
+        <f t="shared" si="13"/>
+        <v>Key-BRASIL-SP-101</v>
+      </c>
+      <c r="Y101" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z101" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA101" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC101" s="77" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B100 W2:W100">
-    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:B101">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:D100 T41:V100 L41:Q1048576 AD41:XFD1048576">
-    <cfRule type="cellIs" dxfId="30" priority="4" operator="equal">
+  <conditionalFormatting sqref="C2:D100 L41:Q100 T41:V100 AD41:XFD100 AD102:XFD1048576">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F101:F1048576 A1:D1 T1:X1 A101:D1048576 T101:X1048576">
-    <cfRule type="cellIs" dxfId="29" priority="456" operator="equal">
+  <conditionalFormatting sqref="F1 F102:F1048576 A1:D1 T1:X1 A102:D1048576 T102:X1048576">
+    <cfRule type="cellIs" dxfId="31" priority="460" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="28" priority="1494"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AD1:XFD29 T2:V28 L7:O9 Q7:Q9 L10:Q29 T29:U29 V29:V40 O30:O40">
-    <cfRule type="cellIs" dxfId="27" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F93 F96:F100">
-    <cfRule type="duplicateValues" dxfId="26" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="24" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F40">
-    <cfRule type="duplicateValues" dxfId="22" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F40">
-    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F100 F2:F93">
-    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F101:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="13" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="973"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="976"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="980"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="984"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="988"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="992"/>
+  <conditionalFormatting sqref="F101">
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R100">
+  <conditionalFormatting sqref="F102:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="14" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="980"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="996"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L102:R1048576">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R101">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R101:R1048576">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+  <conditionalFormatting sqref="W2:W101">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13486,7 +13660,7 @@
         <v>34</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D1" s="19" t="s">
         <v>33</v>
@@ -13799,22 +13973,22 @@
         <v>381</v>
       </c>
       <c r="AY2" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AZ2" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA2" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="BB2" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="BC2" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="BC2" s="40" t="s">
-        <v>425</v>
-      </c>
       <c r="BD2" s="32" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="BE2" s="40" t="str">
         <f t="shared" ref="BE2" si="0">_xlfn.CONCAT("""",C2,"""")</f>
@@ -13973,22 +14147,22 @@
         <v>381</v>
       </c>
       <c r="AY3" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AZ3" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA3" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="BB3" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="BC3" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="BC3" s="40" t="s">
-        <v>425</v>
-      </c>
       <c r="BD3" s="32" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="BE3" s="40" t="str">
         <f t="shared" ref="BE3" si="1">_xlfn.CONCAT("""",C3,"""")</f>
@@ -14147,22 +14321,22 @@
         <v>381</v>
       </c>
       <c r="AY4" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AZ4" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA4" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="BB4" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="BC4" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="BC4" s="40" t="s">
-        <v>425</v>
-      </c>
       <c r="BD4" s="32" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="BE4" s="40" t="str">
         <f t="shared" ref="BE4:BE5" si="2">_xlfn.CONCAT("""",C4,"""")</f>
@@ -14321,22 +14495,22 @@
         <v>381</v>
       </c>
       <c r="AY5" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AZ5" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA5" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="BB5" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="BC5" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="BC5" s="40" t="s">
-        <v>425</v>
-      </c>
       <c r="BD5" s="32" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="BE5" s="40" t="str">
         <f t="shared" si="2"/>
@@ -14495,22 +14669,22 @@
         <v>381</v>
       </c>
       <c r="AY6" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AZ6" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA6" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="BB6" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="BC6" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="BC6" s="40" t="s">
-        <v>425</v>
-      </c>
       <c r="BD6" s="32" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="BE6" s="40" t="str">
         <f t="shared" ref="BE6:BE9" si="3">_xlfn.CONCAT("""",C6,"""")</f>
@@ -14669,22 +14843,22 @@
         <v>381</v>
       </c>
       <c r="AY7" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AZ7" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA7" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="BB7" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="BC7" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="BC7" s="40" t="s">
-        <v>425</v>
-      </c>
       <c r="BD7" s="32" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="BE7" s="40" t="str">
         <f t="shared" si="3"/>
@@ -14835,31 +15009,31 @@
         <v>1</v>
       </c>
       <c r="AV8" s="32" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AW8" s="40" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AX8" s="32" t="s">
         <v>381</v>
       </c>
       <c r="AY8" s="40" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AZ8" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA8" s="40" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="BB8" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="BC8" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="BC8" s="40" t="s">
-        <v>425</v>
-      </c>
       <c r="BD8" s="32" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="BE8" s="40" t="str">
         <f t="shared" si="3"/>
@@ -14910,7 +15084,7 @@
         <v>78</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="P9" s="39" t="s">
         <v>1</v>
@@ -15018,22 +15192,22 @@
         <v>381</v>
       </c>
       <c r="AY9" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AZ9" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA9" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="BB9" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="BC9" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="BC9" s="40" t="s">
-        <v>425</v>
-      </c>
       <c r="BD9" s="32" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="BE9" s="40" t="str">
         <f t="shared" si="3"/>
@@ -15084,7 +15258,7 @@
         <v>78</v>
       </c>
       <c r="O10" s="30" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="P10" s="39" t="s">
         <v>1</v>
@@ -15192,22 +15366,22 @@
         <v>381</v>
       </c>
       <c r="AY10" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AZ10" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA10" s="40" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="BB10" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="BC10" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="BC10" s="40" t="s">
-        <v>425</v>
-      </c>
       <c r="BD10" s="32" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="BE10" s="40" t="str">
         <f t="shared" ref="BE10" si="5">_xlfn.CONCAT("""",C10,"""")</f>

--- a/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
+++ b/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFEF49C-1E31-4818-AD10-E711FDA3247F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C96268-BF6D-4C39-ACC0-215012DA467C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -3023,15 +3023,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="6"/>
+    <col min="1" max="1" width="9.69140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="41.53515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>41</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>49</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>51</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>42</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>43</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>52</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>54</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
         <v>55</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
@@ -3220,19 +3220,19 @@
         <v>378</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46258.60483715278</v>
+        <v>46264.566054861112</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
         <v>382</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
         <v>384</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
         <v>385</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
         <v>57</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
         <v>58</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>59</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>60</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
         <v>376</v>
       </c>
@@ -3331,38 +3331,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <dimension ref="A1:AC101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.53515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.53515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.84375" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.3046875" style="27" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="23.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="232.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="230.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" style="33" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="23.3828125" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.53515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.53515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="232.69140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="230.3046875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.53515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.53515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.69140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="51.84375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.69140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.84375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.3046875" style="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="62">
         <v>2</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="62">
         <v>3</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="62">
         <v>4</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="62">
         <v>5</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="62">
         <v>6</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="62">
         <v>7</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="62">
         <v>8</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="62">
         <v>9</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="62">
         <v>10</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="62">
         <v>11</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="62">
         <v>12</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="62">
         <v>13</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="62">
         <v>14</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="62">
         <v>15</v>
       </c>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="62">
         <v>16</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="62">
         <v>17</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="62">
         <v>18</v>
       </c>
@@ -5111,7 +5111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="62">
         <v>19</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="62">
         <v>20</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="62">
         <v>21</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="62">
         <v>22</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="62">
         <v>23</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="62">
         <v>24</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="62">
         <v>25</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="62">
         <v>26</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="62">
         <v>27</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="62">
         <v>28</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="62">
         <v>29</v>
       </c>
@@ -6189,7 +6189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="62">
         <v>30</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="62">
         <v>31</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="62">
         <v>32</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="62">
         <v>33</v>
       </c>
@@ -6577,7 +6577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="62">
         <v>34</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="62">
         <v>35</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="62">
         <v>36</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="62">
         <v>37</v>
       </c>
@@ -6965,7 +6965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="62">
         <v>38</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="62">
         <v>39</v>
       </c>
@@ -7159,7 +7159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="62">
         <v>40</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="62">
         <v>41</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="62">
         <v>42</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="62">
         <v>43</v>
       </c>
@@ -7547,7 +7547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="62">
         <v>44</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="62">
         <v>45</v>
       </c>
@@ -7741,7 +7741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="62">
         <v>46</v>
       </c>
@@ -7838,7 +7838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="62">
         <v>47</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="62">
         <v>48</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="62">
         <v>49</v>
       </c>
@@ -8129,7 +8129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="62">
         <v>50</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="62">
         <v>51</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="62">
         <v>52</v>
       </c>
@@ -8420,7 +8420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="62">
         <v>53</v>
       </c>
@@ -8517,7 +8517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="62">
         <v>54</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="62">
         <v>55</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="62">
         <v>56</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="62">
         <v>57</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="62">
         <v>58</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="62">
         <v>59</v>
       </c>
@@ -9104,7 +9104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="62">
         <v>60</v>
       </c>
@@ -9201,7 +9201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="62">
         <v>61</v>
       </c>
@@ -9298,7 +9298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="62">
         <v>62</v>
       </c>
@@ -9395,7 +9395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="62">
         <v>63</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="62">
         <v>64</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="62">
         <v>65</v>
       </c>
@@ -9686,7 +9686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="62">
         <v>66</v>
       </c>
@@ -9783,7 +9783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="62">
         <v>67</v>
       </c>
@@ -9880,7 +9880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="62">
         <v>68</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="62">
         <v>69</v>
       </c>
@@ -10076,7 +10076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="62">
         <v>70</v>
       </c>
@@ -10174,7 +10174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="62">
         <v>71</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="62">
         <v>72</v>
       </c>
@@ -10370,7 +10370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="62">
         <v>73</v>
       </c>
@@ -10467,7 +10467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="62">
         <v>74</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="62">
         <v>75</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="62">
         <v>76</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="62">
         <v>77</v>
       </c>
@@ -10856,7 +10856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="62">
         <v>78</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="62">
         <v>79</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="62">
         <v>80</v>
       </c>
@@ -11147,7 +11147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="62">
         <v>81</v>
       </c>
@@ -11244,7 +11244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="62">
         <v>82</v>
       </c>
@@ -11341,7 +11341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="62">
         <v>83</v>
       </c>
@@ -11438,7 +11438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="62">
         <v>84</v>
       </c>
@@ -11535,7 +11535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="62">
         <v>85</v>
       </c>
@@ -11632,7 +11632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="62">
         <v>86</v>
       </c>
@@ -11729,7 +11729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="62">
         <v>87</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="62">
         <v>88</v>
       </c>
@@ -11923,7 +11923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="62">
         <v>89</v>
       </c>
@@ -12020,7 +12020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="62">
         <v>90</v>
       </c>
@@ -12117,7 +12117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="62">
         <v>91</v>
       </c>
@@ -12214,7 +12214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="62">
         <v>92</v>
       </c>
@@ -12311,7 +12311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="62">
         <v>93</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="62">
         <v>94</v>
       </c>
@@ -12505,7 +12505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="62">
         <v>95</v>
       </c>
@@ -12602,7 +12602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="62">
         <v>96</v>
       </c>
@@ -12699,7 +12699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="62">
         <v>97</v>
       </c>
@@ -12796,7 +12796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="62">
         <v>98</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="62">
         <v>99</v>
       </c>
@@ -12990,7 +12990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="62">
         <v>100</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:29" s="78" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:29" s="78" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="62">
         <v>101</v>
       </c>
@@ -13098,10 +13098,10 @@
         <v>587</v>
       </c>
       <c r="D101" s="73" t="s">
+        <v>589</v>
+      </c>
+      <c r="E101" s="73" t="s">
         <v>588</v>
-      </c>
-      <c r="E101" s="73" t="s">
-        <v>589</v>
       </c>
       <c r="F101" s="73" t="s">
         <v>590</v>
@@ -13127,11 +13127,11 @@
       </c>
       <c r="M101" s="75" t="str">
         <f t="shared" si="16"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N101" s="75" t="str">
         <f t="shared" si="16"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O101" s="75" t="str">
         <f t="shared" si="16"/>
@@ -13155,11 +13155,11 @@
       </c>
       <c r="U101" s="76" t="str">
         <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V101" s="66" t="str">
         <f t="shared" si="17"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W101" s="66" t="s">
         <v>438</v>
@@ -13269,15 +13269,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>22</v>
       </c>
@@ -13342,7 +13342,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -13487,14 +13487,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="21">
         <v>1</v>
       </c>
@@ -13508,7 +13508,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13">
         <v>2</v>
       </c>
@@ -13522,7 +13522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>3</v>
       </c>
@@ -13536,7 +13536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>4</v>
       </c>
@@ -13550,7 +13550,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>5</v>
       </c>
@@ -13564,7 +13564,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>6</v>
       </c>
@@ -13591,68 +13591,68 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:BE10"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.84375" style="25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="32.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="7.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="16.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="5.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="5.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="9.7109375" style="48" bestFit="1" customWidth="1"/>
-    <col min="58" max="16384" width="9.140625" style="25"/>
+    <col min="15" max="15" width="32.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.84375" style="58" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.84375" style="58" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.84375" style="58" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="3.84375" style="58" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.84375" style="58" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="3.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="3.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.3046875" style="48" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.3828125" style="25" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="5.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16.3046875" style="48" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="5.84375" style="48" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="5.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="9.69140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="58" max="16384" width="9.15234375" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="29" t="s">
         <v>74</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="38">
         <v>2</v>
       </c>
@@ -13995,7 +13995,7 @@
         <v>"Continente"</v>
       </c>
     </row>
-    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="38">
         <v>3</v>
       </c>
@@ -14169,7 +14169,7 @@
         <v>"SubContinente"</v>
       </c>
     </row>
-    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="38">
         <v>4</v>
       </c>
@@ -14343,7 +14343,7 @@
         <v>"País"</v>
       </c>
     </row>
-    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="38">
         <v>5</v>
       </c>
@@ -14517,7 +14517,7 @@
         <v>"Região"</v>
       </c>
     </row>
-    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="38">
         <v>6</v>
       </c>
@@ -14691,7 +14691,7 @@
         <v>"Região"</v>
       </c>
     </row>
-    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="38">
         <v>7</v>
       </c>
@@ -14865,7 +14865,7 @@
         <v>"Estado"</v>
       </c>
     </row>
-    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="38">
         <v>8</v>
       </c>
@@ -15040,7 +15040,7 @@
         <v>"Capital"</v>
       </c>
     </row>
-    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="38">
         <v>9</v>
       </c>
@@ -15214,7 +15214,7 @@
         <v>"UF"</v>
       </c>
     </row>
-    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="38">
         <v>10</v>
       </c>

--- a/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
+++ b/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C96268-BF6D-4C39-ACC0-215012DA467C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9526BA7E-4C0D-411A-AA36-350ED3831A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="611">
   <si>
     <t>Key</t>
   </si>
@@ -1264,18 +1264,9 @@
     <t>[ OST_ToposolidFinish1 ]</t>
   </si>
   <si>
-    <t>[ OST_TopographyContours , OST_ToposolidContours , OST_ToposolidSecondaryContours ]</t>
-  </si>
-  <si>
     <t>[ OST_Floors ]</t>
   </si>
   <si>
-    <t>[ OST_SiteProperty , OST_SitePropertyLineSegment ]</t>
-  </si>
-  <si>
-    <t>[ OST_Areas , OST_Rooms ]</t>
-  </si>
-  <si>
     <t>[ OST_Rooms ]</t>
   </si>
   <si>
@@ -1828,9 +1819,6 @@
     <t>Parâmetro Rvt</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Atributo Ifc</t>
   </si>
   <si>
@@ -1846,16 +1834,79 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
+  </si>
+  <si>
+    <t>[ OST_TopographyContours : OST_ToposolidContours : OST_ToposolidSecondaryContours ]</t>
+  </si>
+  <si>
+    <t>[ OST_SiteProperty : OST_SitePropertyLineSegment ]</t>
+  </si>
+  <si>
+    <t>[ OST_Areas : OST_Rooms ]</t>
   </si>
 </sst>
 </file>
@@ -1963,7 +2014,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2092,12 +2143,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBE79D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
@@ -2154,7 +2199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2365,12 +2410,6 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2380,17 +2419,20 @@
     <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="35">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2690,6 +2732,16 @@
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3023,15 +3075,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="41.53515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="6"/>
+    <col min="1" max="1" width="9.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="41.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -3042,7 +3094,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -3053,18 +3105,18 @@
         <v>378</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C3" s="52" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -3075,7 +3127,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -3087,7 +3139,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -3099,7 +3151,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -3110,7 +3162,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>41</v>
       </c>
@@ -3121,7 +3173,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>49</v>
       </c>
@@ -3132,7 +3184,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>51</v>
       </c>
@@ -3143,7 +3195,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>42</v>
       </c>
@@ -3154,7 +3206,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>43</v>
       </c>
@@ -3165,7 +3217,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>52</v>
       </c>
@@ -3176,7 +3228,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
@@ -3187,7 +3239,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>54</v>
       </c>
@@ -3198,7 +3250,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>55</v>
       </c>
@@ -3209,30 +3261,30 @@
         <v>378</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C17" s="52" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46264.566054861112</v>
+        <v>46268.693379861113</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>382</v>
       </c>
@@ -3243,7 +3295,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>384</v>
       </c>
@@ -3255,7 +3307,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>385</v>
       </c>
@@ -3267,7 +3319,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>57</v>
       </c>
@@ -3278,7 +3330,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>58</v>
       </c>
@@ -3289,29 +3341,29 @@
         <v>378</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C24" s="52" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>60</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C25" s="52" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>376</v>
       </c>
@@ -3330,39 +3382,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
-  <dimension ref="A1:AC101"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD105"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.84375" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.3046875" style="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" style="27" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="23.3828125" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.53515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="232.69140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="230.3046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.53515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.53515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.69140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="51.84375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.3828125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.84375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.3046875" style="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="23.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="232.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="230.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="51.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.140625" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="4.28515625" style="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3439,24 +3491,27 @@
         <v>80</v>
       </c>
       <c r="Z1" s="26" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="AA1" s="16" t="s">
         <v>79</v>
       </c>
       <c r="AB1" s="26" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="AC1" s="26" t="s">
         <v>374</v>
       </c>
+      <c r="AD1" s="26" t="s">
+        <v>607</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="62">
         <v>2</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C2" s="31" t="s">
         <v>255</v>
@@ -3510,7 +3565,7 @@
         <v>81</v>
       </c>
       <c r="R2" s="66" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="S2" s="66" t="s">
         <v>1</v>
@@ -3528,7 +3583,7 @@
         <v>Naturais</v>
       </c>
       <c r="W2" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X2" s="67" t="str">
         <f>CONCATENATE("Key-BRASIL-SP-",A2)</f>
@@ -3537,25 +3592,28 @@
       <c r="Y2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z2" s="66" t="s">
-        <v>584</v>
+      <c r="Z2" s="75" t="s">
+        <v>1</v>
       </c>
       <c r="AA2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AB2" s="66" t="s">
-        <v>584</v>
+      <c r="AB2" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC2" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD2" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="62">
         <v>3</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C3" s="31" t="s">
         <v>255</v>
@@ -3607,7 +3665,7 @@
         <v>82</v>
       </c>
       <c r="R3" s="66" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="S3" s="66" t="s">
         <v>1</v>
@@ -3625,7 +3683,7 @@
         <v>Naturais</v>
       </c>
       <c r="W3" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X3" s="67" t="str">
         <f t="shared" ref="X3:X66" si="3">CONCATENATE("Key-BRASIL-SP-",A3)</f>
@@ -3634,25 +3692,28 @@
       <c r="Y3" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z3" s="66" t="s">
-        <v>584</v>
+      <c r="Z3" s="75" t="s">
+        <v>1</v>
       </c>
       <c r="AA3" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AB3" s="66" t="s">
-        <v>584</v>
+      <c r="AB3" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC3" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD3" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="62">
         <v>4</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C4" s="31" t="s">
         <v>255</v>
@@ -3704,7 +3765,7 @@
         <v>84</v>
       </c>
       <c r="R4" s="66" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="S4" s="66" t="s">
         <v>1</v>
@@ -3722,7 +3783,7 @@
         <v>Naturais</v>
       </c>
       <c r="W4" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X4" s="67" t="str">
         <f t="shared" si="3"/>
@@ -3731,25 +3792,28 @@
       <c r="Y4" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z4" s="66" t="s">
-        <v>584</v>
+      <c r="Z4" s="75" t="s">
+        <v>1</v>
       </c>
       <c r="AA4" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AB4" s="66" t="s">
-        <v>584</v>
+      <c r="AB4" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC4" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD4" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="62">
         <v>5</v>
       </c>
       <c r="B5" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>255</v>
@@ -3802,7 +3866,7 @@
         <v>85</v>
       </c>
       <c r="R5" s="66" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="S5" s="66" t="s">
         <v>1</v>
@@ -3820,7 +3884,7 @@
         <v>Políticas</v>
       </c>
       <c r="W5" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X5" s="67" t="str">
         <f t="shared" si="3"/>
@@ -3829,25 +3893,28 @@
       <c r="Y5" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z5" s="66" t="s">
-        <v>584</v>
+      <c r="Z5" s="75" t="s">
+        <v>1</v>
       </c>
       <c r="AA5" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB5" s="66" t="s">
-        <v>584</v>
+      <c r="AB5" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC5" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD5" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="62">
         <v>6</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C6" s="31" t="s">
         <v>255</v>
@@ -3899,7 +3966,7 @@
         <v>87</v>
       </c>
       <c r="R6" s="66" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="S6" s="66" t="s">
         <v>1</v>
@@ -3917,7 +3984,7 @@
         <v>Políticas</v>
       </c>
       <c r="W6" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X6" s="67" t="str">
         <f t="shared" si="3"/>
@@ -3926,25 +3993,28 @@
       <c r="Y6" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z6" s="66" t="s">
-        <v>584</v>
+      <c r="Z6" s="75" t="s">
+        <v>1</v>
       </c>
       <c r="AA6" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB6" s="66" t="s">
-        <v>584</v>
+      <c r="AB6" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC6" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD6" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="62">
         <v>7</v>
       </c>
       <c r="B7" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>255</v>
@@ -3990,13 +4060,13 @@
         <v>Região</v>
       </c>
       <c r="P7" s="71" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="Q7" s="69" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="R7" s="66" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="S7" s="66" t="s">
         <v>1</v>
@@ -4014,7 +4084,7 @@
         <v>Políticas</v>
       </c>
       <c r="W7" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X7" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4023,25 +4093,28 @@
       <c r="Y7" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z7" s="66" t="s">
-        <v>584</v>
+      <c r="Z7" s="75" t="s">
+        <v>1</v>
       </c>
       <c r="AA7" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="AB7" s="66" t="s">
-        <v>584</v>
+      <c r="AB7" s="70" t="s">
+        <v>1</v>
       </c>
       <c r="AC7" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD7" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="62">
         <v>8</v>
       </c>
       <c r="B8" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>255</v>
@@ -4053,7 +4126,7 @@
         <v>257</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="G8" s="68" t="s">
         <v>1</v>
@@ -4087,13 +4160,13 @@
         <v>Região Intermediária</v>
       </c>
       <c r="P8" s="71" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="Q8" s="69" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="R8" s="66" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="S8" s="66" t="s">
         <v>1</v>
@@ -4111,7 +4184,7 @@
         <v>Políticas</v>
       </c>
       <c r="W8" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X8" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4120,7 +4193,7 @@
       <c r="Y8" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z8" s="77" t="s">
+      <c r="Z8" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA8" s="66" t="s">
@@ -4132,13 +4205,16 @@
       <c r="AC8" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD8" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="62">
         <v>9</v>
       </c>
       <c r="B9" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>255</v>
@@ -4150,7 +4226,7 @@
         <v>257</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G9" s="68" t="s">
         <v>1</v>
@@ -4184,13 +4260,13 @@
         <v>Região Imediata</v>
       </c>
       <c r="P9" s="71" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="Q9" s="69" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="R9" s="66" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="S9" s="66" t="s">
         <v>1</v>
@@ -4208,7 +4284,7 @@
         <v>Políticas</v>
       </c>
       <c r="W9" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X9" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4217,7 +4293,7 @@
       <c r="Y9" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z9" s="77" t="s">
+      <c r="Z9" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA9" s="66" t="s">
@@ -4229,13 +4305,16 @@
       <c r="AC9" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD9" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
         <v>10</v>
       </c>
       <c r="B10" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>255</v>
@@ -4288,7 +4367,7 @@
         <v>90</v>
       </c>
       <c r="R10" s="66" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="S10" s="66" t="s">
         <v>1</v>
@@ -4306,7 +4385,7 @@
         <v>Políticas</v>
       </c>
       <c r="W10" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X10" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4315,7 +4394,7 @@
       <c r="Y10" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z10" s="77" t="s">
+      <c r="Z10" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA10" s="66" t="s">
@@ -4327,13 +4406,16 @@
       <c r="AC10" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD10" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="62">
         <v>11</v>
       </c>
       <c r="B11" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C11" s="31" t="s">
         <v>255</v>
@@ -4385,7 +4467,7 @@
         <v>92</v>
       </c>
       <c r="R11" s="66" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="S11" s="66" t="s">
         <v>1</v>
@@ -4403,7 +4485,7 @@
         <v>Políticas</v>
       </c>
       <c r="W11" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X11" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4412,7 +4494,7 @@
       <c r="Y11" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z11" s="77" t="s">
+      <c r="Z11" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA11" s="66" t="s">
@@ -4424,13 +4506,16 @@
       <c r="AC11" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD11" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="62">
         <v>12</v>
       </c>
       <c r="B12" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>255</v>
@@ -4483,7 +4568,7 @@
         <v>94</v>
       </c>
       <c r="R12" s="66" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="S12" s="66" t="s">
         <v>1</v>
@@ -4501,7 +4586,7 @@
         <v>Políticas</v>
       </c>
       <c r="W12" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X12" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4510,7 +4595,7 @@
       <c r="Y12" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z12" s="77" t="s">
+      <c r="Z12" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA12" s="66" t="s">
@@ -4522,13 +4607,16 @@
       <c r="AC12" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD12" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="62">
         <v>13</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>255</v>
@@ -4575,13 +4663,13 @@
         <v>Capital</v>
       </c>
       <c r="P13" s="69" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="Q13" s="69" t="s">
         <v>95</v>
       </c>
       <c r="R13" s="66" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="S13" s="66" t="s">
         <v>1</v>
@@ -4599,7 +4687,7 @@
         <v>Políticas</v>
       </c>
       <c r="W13" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X13" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4608,7 +4696,7 @@
       <c r="Y13" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z13" s="77" t="s">
+      <c r="Z13" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA13" s="66" t="s">
@@ -4620,13 +4708,16 @@
       <c r="AC13" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD13" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="62">
         <v>14</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>255</v>
@@ -4638,7 +4729,7 @@
         <v>257</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="G14" s="68" t="s">
         <v>1</v>
@@ -4673,13 +4764,13 @@
         <v>Capital do Sul</v>
       </c>
       <c r="P14" s="69" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="Q14" s="69" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="R14" s="66" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="S14" s="66" t="s">
         <v>1</v>
@@ -4697,7 +4788,7 @@
         <v>Políticas</v>
       </c>
       <c r="W14" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X14" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4706,7 +4797,7 @@
       <c r="Y14" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z14" s="77" t="s">
+      <c r="Z14" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA14" s="66" t="s">
@@ -4718,13 +4809,16 @@
       <c r="AC14" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD14" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="62">
         <v>15</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>255</v>
@@ -4736,7 +4830,7 @@
         <v>257</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G15" s="68" t="s">
         <v>1</v>
@@ -4771,13 +4865,13 @@
         <v>Capital do Sudeste</v>
       </c>
       <c r="P15" s="69" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="Q15" s="69" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="R15" s="66" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="S15" s="66" t="s">
         <v>1</v>
@@ -4795,7 +4889,7 @@
         <v>Políticas</v>
       </c>
       <c r="W15" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X15" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4804,7 +4898,7 @@
       <c r="Y15" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z15" s="77" t="s">
+      <c r="Z15" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA15" s="66" t="s">
@@ -4816,13 +4910,16 @@
       <c r="AC15" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD15" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="62">
         <v>16</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>255</v>
@@ -4834,7 +4931,7 @@
         <v>257</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="G16" s="68" t="s">
         <v>1</v>
@@ -4869,13 +4966,13 @@
         <v>Capital do Norte</v>
       </c>
       <c r="P16" s="69" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="Q16" s="69" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="R16" s="66" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="S16" s="66" t="s">
         <v>1</v>
@@ -4893,7 +4990,7 @@
         <v>Políticas</v>
       </c>
       <c r="W16" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X16" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4902,7 +4999,7 @@
       <c r="Y16" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z16" s="77" t="s">
+      <c r="Z16" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA16" s="66" t="s">
@@ -4914,13 +5011,16 @@
       <c r="AC16" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD16" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="62">
         <v>17</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>255</v>
@@ -4932,7 +5032,7 @@
         <v>257</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G17" s="68" t="s">
         <v>1</v>
@@ -4967,13 +5067,13 @@
         <v>Capital do Nordeste</v>
       </c>
       <c r="P17" s="69" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="Q17" s="69" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="R17" s="66" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="S17" s="66" t="s">
         <v>1</v>
@@ -4991,7 +5091,7 @@
         <v>Políticas</v>
       </c>
       <c r="W17" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X17" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5000,7 +5100,7 @@
       <c r="Y17" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z17" s="77" t="s">
+      <c r="Z17" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA17" s="66" t="s">
@@ -5012,13 +5112,16 @@
       <c r="AC17" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD17" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="62">
         <v>18</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>255</v>
@@ -5030,7 +5133,7 @@
         <v>257</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="G18" s="68" t="s">
         <v>1</v>
@@ -5065,13 +5168,13 @@
         <v>Capital do CentroOeste</v>
       </c>
       <c r="P18" s="69" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="Q18" s="69" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="R18" s="66" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="S18" s="66" t="s">
         <v>1</v>
@@ -5089,7 +5192,7 @@
         <v>Políticas</v>
       </c>
       <c r="W18" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X18" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5098,7 +5201,7 @@
       <c r="Y18" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z18" s="77" t="s">
+      <c r="Z18" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA18" s="66" t="s">
@@ -5110,13 +5213,16 @@
       <c r="AC18" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD18" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="62">
         <v>19</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>255</v>
@@ -5163,13 +5269,13 @@
         <v>Cidade</v>
       </c>
       <c r="P19" s="69" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="Q19" s="69" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="R19" s="66" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="S19" s="66" t="s">
         <v>1</v>
@@ -5187,7 +5293,7 @@
         <v>Políticas</v>
       </c>
       <c r="W19" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X19" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5196,7 +5302,7 @@
       <c r="Y19" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z19" s="77" t="s">
+      <c r="Z19" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA19" s="66" t="s">
@@ -5208,13 +5314,16 @@
       <c r="AC19" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD19" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="62">
         <v>20</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>255</v>
@@ -5226,7 +5335,7 @@
         <v>257</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="G20" s="68" t="s">
         <v>1</v>
@@ -5261,13 +5370,13 @@
         <v>Cidade do Sul</v>
       </c>
       <c r="P20" s="69" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="Q20" s="69" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="R20" s="66" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="S20" s="66" t="s">
         <v>1</v>
@@ -5285,7 +5394,7 @@
         <v>Políticas</v>
       </c>
       <c r="W20" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X20" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5294,7 +5403,7 @@
       <c r="Y20" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z20" s="77" t="s">
+      <c r="Z20" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA20" s="66" t="s">
@@ -5306,13 +5415,16 @@
       <c r="AC20" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD20" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="62">
         <v>21</v>
       </c>
       <c r="B21" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>255</v>
@@ -5324,7 +5436,7 @@
         <v>257</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G21" s="68" t="s">
         <v>1</v>
@@ -5359,13 +5471,13 @@
         <v>Cidade do Sudeste</v>
       </c>
       <c r="P21" s="69" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="Q21" s="69" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="R21" s="66" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="S21" s="66" t="s">
         <v>1</v>
@@ -5383,7 +5495,7 @@
         <v>Políticas</v>
       </c>
       <c r="W21" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X21" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5392,7 +5504,7 @@
       <c r="Y21" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z21" s="77" t="s">
+      <c r="Z21" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA21" s="66" t="s">
@@ -5404,13 +5516,16 @@
       <c r="AC21" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD21" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="62">
         <v>22</v>
       </c>
       <c r="B22" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>255</v>
@@ -5422,7 +5537,7 @@
         <v>257</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="G22" s="68" t="s">
         <v>1</v>
@@ -5457,13 +5572,13 @@
         <v>Cidade do Norte</v>
       </c>
       <c r="P22" s="69" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="Q22" s="69" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R22" s="66" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="S22" s="66" t="s">
         <v>1</v>
@@ -5481,7 +5596,7 @@
         <v>Políticas</v>
       </c>
       <c r="W22" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X22" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5490,7 +5605,7 @@
       <c r="Y22" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z22" s="77" t="s">
+      <c r="Z22" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA22" s="66" t="s">
@@ -5502,13 +5617,16 @@
       <c r="AC22" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD22" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="62">
         <v>23</v>
       </c>
       <c r="B23" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C23" s="31" t="s">
         <v>255</v>
@@ -5520,7 +5638,7 @@
         <v>257</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="G23" s="68" t="s">
         <v>1</v>
@@ -5555,13 +5673,13 @@
         <v>Cidade do Nordeste</v>
       </c>
       <c r="P23" s="69" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="Q23" s="69" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="R23" s="66" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="S23" s="66" t="s">
         <v>1</v>
@@ -5579,7 +5697,7 @@
         <v>Políticas</v>
       </c>
       <c r="W23" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X23" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5588,7 +5706,7 @@
       <c r="Y23" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z23" s="77" t="s">
+      <c r="Z23" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA23" s="66" t="s">
@@ -5600,13 +5718,16 @@
       <c r="AC23" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD23" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="62">
         <v>24</v>
       </c>
       <c r="B24" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C24" s="31" t="s">
         <v>255</v>
@@ -5618,7 +5739,7 @@
         <v>257</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G24" s="68" t="s">
         <v>1</v>
@@ -5653,13 +5774,13 @@
         <v>Cidade do CentroOeste</v>
       </c>
       <c r="P24" s="69" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="Q24" s="69" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="R24" s="66" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="S24" s="66" t="s">
         <v>1</v>
@@ -5677,7 +5798,7 @@
         <v>Políticas</v>
       </c>
       <c r="W24" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X24" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5686,7 +5807,7 @@
       <c r="Y24" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z24" s="77" t="s">
+      <c r="Z24" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA24" s="66" t="s">
@@ -5698,13 +5819,16 @@
       <c r="AC24" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD24" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="62">
         <v>25</v>
       </c>
       <c r="B25" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C25" s="31" t="s">
         <v>255</v>
@@ -5757,7 +5881,7 @@
         <v>96</v>
       </c>
       <c r="R25" s="66" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="S25" s="66" t="s">
         <v>1</v>
@@ -5775,7 +5899,7 @@
         <v>Políticas</v>
       </c>
       <c r="W25" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X25" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5784,7 +5908,7 @@
       <c r="Y25" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z25" s="77" t="s">
+      <c r="Z25" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA25" s="66" t="s">
@@ -5796,13 +5920,16 @@
       <c r="AC25" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD25" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="62">
         <v>26</v>
       </c>
       <c r="B26" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C26" s="31" t="s">
         <v>255</v>
@@ -5855,7 +5982,7 @@
         <v>98</v>
       </c>
       <c r="R26" s="66" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="S26" s="66" t="s">
         <v>1</v>
@@ -5873,7 +6000,7 @@
         <v>Políticas</v>
       </c>
       <c r="W26" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X26" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5882,7 +6009,7 @@
       <c r="Y26" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z26" s="77" t="s">
+      <c r="Z26" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA26" s="66" t="s">
@@ -5894,13 +6021,16 @@
       <c r="AC26" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD26" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="62">
         <v>27</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C27" s="31" t="s">
         <v>255</v>
@@ -5953,7 +6083,7 @@
         <v>100</v>
       </c>
       <c r="R27" s="66" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="S27" s="66" t="s">
         <v>1</v>
@@ -5971,7 +6101,7 @@
         <v>Bioclimáticas</v>
       </c>
       <c r="W27" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X27" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5980,7 +6110,7 @@
       <c r="Y27" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z27" s="77" t="s">
+      <c r="Z27" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA27" s="66" t="s">
@@ -5992,13 +6122,16 @@
       <c r="AC27" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD27" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="62">
         <v>28</v>
       </c>
       <c r="B28" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C28" s="31" t="s">
         <v>255</v>
@@ -6051,7 +6184,7 @@
         <v>102</v>
       </c>
       <c r="R28" s="66" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="S28" s="66" t="s">
         <v>1</v>
@@ -6069,7 +6202,7 @@
         <v>Bioclimáticas</v>
       </c>
       <c r="W28" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X28" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6078,7 +6211,7 @@
       <c r="Y28" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z28" s="77" t="s">
+      <c r="Z28" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA28" s="66" t="s">
@@ -6090,13 +6223,16 @@
       <c r="AC28" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD28" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="62">
         <v>29</v>
       </c>
       <c r="B29" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C29" s="31" t="s">
         <v>255</v>
@@ -6149,7 +6285,7 @@
         <v>104</v>
       </c>
       <c r="R29" s="66" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="S29" s="66" t="s">
         <v>1</v>
@@ -6167,7 +6303,7 @@
         <v>Ilhas de Calor</v>
       </c>
       <c r="W29" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X29" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6176,7 +6312,7 @@
       <c r="Y29" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z29" s="77" t="s">
+      <c r="Z29" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA29" s="66" t="s">
@@ -6188,13 +6324,16 @@
       <c r="AC29" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD29" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="62">
         <v>30</v>
       </c>
       <c r="B30" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C30" s="31" t="s">
         <v>255</v>
@@ -6246,7 +6385,7 @@
         <v>225</v>
       </c>
       <c r="R30" s="66" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="S30" s="66" t="s">
         <v>1</v>
@@ -6264,7 +6403,7 @@
         <v>Marcos</v>
       </c>
       <c r="W30" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X30" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6273,11 +6412,11 @@
       <c r="Y30" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z30" s="77" t="s">
+      <c r="Z30" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA30" s="70" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AB30" s="70" t="s">
         <v>1</v>
@@ -6285,13 +6424,16 @@
       <c r="AC30" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD30" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="62">
         <v>31</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C31" s="31" t="s">
         <v>255</v>
@@ -6343,7 +6485,7 @@
         <v>227</v>
       </c>
       <c r="R31" s="66" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="S31" s="66" t="s">
         <v>1</v>
@@ -6361,7 +6503,7 @@
         <v>Marcos</v>
       </c>
       <c r="W31" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X31" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6370,11 +6512,11 @@
       <c r="Y31" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z31" s="77" t="s">
+      <c r="Z31" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA31" s="70" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AB31" s="70" t="s">
         <v>1</v>
@@ -6382,13 +6524,16 @@
       <c r="AC31" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD31" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="62">
         <v>32</v>
       </c>
       <c r="B32" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C32" s="31" t="s">
         <v>255</v>
@@ -6440,7 +6585,7 @@
         <v>229</v>
       </c>
       <c r="R32" s="66" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="S32" s="66" t="s">
         <v>1</v>
@@ -6458,7 +6603,7 @@
         <v>Marcos</v>
       </c>
       <c r="W32" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X32" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6467,11 +6612,11 @@
       <c r="Y32" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z32" s="77" t="s">
+      <c r="Z32" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA32" s="70" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AB32" s="70" t="s">
         <v>1</v>
@@ -6479,13 +6624,16 @@
       <c r="AC32" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD32" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="62">
         <v>33</v>
       </c>
       <c r="B33" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C33" s="31" t="s">
         <v>255</v>
@@ -6537,7 +6685,7 @@
         <v>237</v>
       </c>
       <c r="R33" s="66" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="S33" s="66" t="s">
         <v>1</v>
@@ -6555,7 +6703,7 @@
         <v>Marcos</v>
       </c>
       <c r="W33" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X33" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6564,11 +6712,11 @@
       <c r="Y33" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z33" s="77" t="s">
+      <c r="Z33" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA33" s="70" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AB33" s="70" t="s">
         <v>1</v>
@@ -6576,13 +6724,16 @@
       <c r="AC33" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD33" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="62">
         <v>34</v>
       </c>
       <c r="B34" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C34" s="31" t="s">
         <v>255</v>
@@ -6634,7 +6785,7 @@
         <v>231</v>
       </c>
       <c r="R34" s="66" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="S34" s="66" t="s">
         <v>1</v>
@@ -6652,7 +6803,7 @@
         <v>Marcos</v>
       </c>
       <c r="W34" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X34" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6661,11 +6812,11 @@
       <c r="Y34" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z34" s="77" t="s">
+      <c r="Z34" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA34" s="70" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AB34" s="70" t="s">
         <v>1</v>
@@ -6673,13 +6824,16 @@
       <c r="AC34" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD34" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="62">
         <v>35</v>
       </c>
       <c r="B35" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C35" s="31" t="s">
         <v>255</v>
@@ -6731,7 +6885,7 @@
         <v>233</v>
       </c>
       <c r="R35" s="66" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="S35" s="66" t="s">
         <v>1</v>
@@ -6749,7 +6903,7 @@
         <v>Marcos</v>
       </c>
       <c r="W35" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X35" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6758,11 +6912,11 @@
       <c r="Y35" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z35" s="77" t="s">
+      <c r="Z35" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA35" s="70" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AB35" s="70" t="s">
         <v>1</v>
@@ -6770,13 +6924,16 @@
       <c r="AC35" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD35" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="62">
         <v>36</v>
       </c>
       <c r="B36" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C36" s="31" t="s">
         <v>255</v>
@@ -6828,7 +6985,7 @@
         <v>235</v>
       </c>
       <c r="R36" s="66" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="S36" s="66" t="s">
         <v>1</v>
@@ -6846,7 +7003,7 @@
         <v>Marcos</v>
       </c>
       <c r="W36" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X36" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6855,11 +7012,11 @@
       <c r="Y36" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z36" s="77" t="s">
+      <c r="Z36" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA36" s="70" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AB36" s="70" t="s">
         <v>1</v>
@@ -6867,13 +7024,16 @@
       <c r="AC36" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD36" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="62">
         <v>37</v>
       </c>
       <c r="B37" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C37" s="31" t="s">
         <v>255</v>
@@ -6925,7 +7085,7 @@
         <v>239</v>
       </c>
       <c r="R37" s="66" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="S37" s="66" t="s">
         <v>1</v>
@@ -6943,7 +7103,7 @@
         <v>Marcos</v>
       </c>
       <c r="W37" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X37" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6952,11 +7112,11 @@
       <c r="Y37" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z37" s="77" t="s">
+      <c r="Z37" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA37" s="70" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AB37" s="70" t="s">
         <v>1</v>
@@ -6964,13 +7124,16 @@
       <c r="AC37" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD37" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="62">
         <v>38</v>
       </c>
       <c r="B38" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C38" s="31" t="s">
         <v>255</v>
@@ -7022,7 +7185,7 @@
         <v>241</v>
       </c>
       <c r="R38" s="66" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="S38" s="66" t="s">
         <v>1</v>
@@ -7040,7 +7203,7 @@
         <v>Marcos</v>
       </c>
       <c r="W38" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X38" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7049,11 +7212,11 @@
       <c r="Y38" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z38" s="77" t="s">
+      <c r="Z38" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA38" s="70" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AB38" s="70" t="s">
         <v>1</v>
@@ -7061,13 +7224,16 @@
       <c r="AC38" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD38" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="62">
         <v>39</v>
       </c>
       <c r="B39" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C39" s="31" t="s">
         <v>255</v>
@@ -7119,7 +7285,7 @@
         <v>243</v>
       </c>
       <c r="R39" s="66" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="S39" s="66" t="s">
         <v>1</v>
@@ -7137,7 +7303,7 @@
         <v>Marcos</v>
       </c>
       <c r="W39" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X39" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7146,11 +7312,11 @@
       <c r="Y39" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z39" s="77" t="s">
+      <c r="Z39" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA39" s="70" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AB39" s="70" t="s">
         <v>1</v>
@@ -7158,13 +7324,16 @@
       <c r="AC39" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD39" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="62">
         <v>40</v>
       </c>
       <c r="B40" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C40" s="31" t="s">
         <v>255</v>
@@ -7216,7 +7385,7 @@
         <v>245</v>
       </c>
       <c r="R40" s="66" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="S40" s="66" t="s">
         <v>1</v>
@@ -7234,7 +7403,7 @@
         <v>Marcos</v>
       </c>
       <c r="W40" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X40" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7243,11 +7412,11 @@
       <c r="Y40" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="Z40" s="77" t="s">
+      <c r="Z40" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA40" s="70" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AB40" s="70" t="s">
         <v>1</v>
@@ -7255,16 +7424,19 @@
       <c r="AC40" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD40" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="62">
         <v>41</v>
       </c>
       <c r="B41" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D41" s="31" t="s">
         <v>275</v>
@@ -7313,7 +7485,7 @@
         <v>352</v>
       </c>
       <c r="R41" s="66" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="S41" s="66" t="s">
         <v>1</v>
@@ -7331,7 +7503,7 @@
         <v>Pontos Cotados</v>
       </c>
       <c r="W41" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X41" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7340,11 +7512,11 @@
       <c r="Y41" s="66" t="s">
         <v>388</v>
       </c>
-      <c r="Z41" s="77" t="s">
+      <c r="Z41" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA41" s="66" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AB41" s="70" t="s">
         <v>1</v>
@@ -7352,16 +7524,19 @@
       <c r="AC41" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD41" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="62">
         <v>42</v>
       </c>
       <c r="B42" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D42" s="31" t="s">
         <v>275</v>
@@ -7410,7 +7585,7 @@
         <v>353</v>
       </c>
       <c r="R42" s="66" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="S42" s="66" t="s">
         <v>1</v>
@@ -7428,7 +7603,7 @@
         <v>Pontos Cotados</v>
       </c>
       <c r="W42" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X42" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7437,11 +7612,11 @@
       <c r="Y42" s="66" t="s">
         <v>389</v>
       </c>
-      <c r="Z42" s="77" t="s">
+      <c r="Z42" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA42" s="66" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AB42" s="70" t="s">
         <v>1</v>
@@ -7449,16 +7624,19 @@
       <c r="AC42" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD42" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="62">
         <v>43</v>
       </c>
       <c r="B43" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D43" s="31" t="s">
         <v>275</v>
@@ -7507,7 +7685,7 @@
         <v>354</v>
       </c>
       <c r="R43" s="66" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="S43" s="66" t="s">
         <v>1</v>
@@ -7525,7 +7703,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W43" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X43" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7534,11 +7712,11 @@
       <c r="Y43" s="66" t="s">
         <v>390</v>
       </c>
-      <c r="Z43" s="77" t="s">
+      <c r="Z43" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA43" s="66" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AB43" s="70" t="s">
         <v>1</v>
@@ -7546,16 +7724,19 @@
       <c r="AC43" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD43" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="62">
         <v>44</v>
       </c>
       <c r="B44" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D44" s="31" t="s">
         <v>275</v>
@@ -7604,7 +7785,7 @@
         <v>355</v>
       </c>
       <c r="R44" s="66" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="S44" s="66" t="s">
         <v>1</v>
@@ -7622,7 +7803,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W44" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X44" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7631,11 +7812,11 @@
       <c r="Y44" s="66" t="s">
         <v>391</v>
       </c>
-      <c r="Z44" s="77" t="s">
+      <c r="Z44" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA44" s="66" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AB44" s="70" t="s">
         <v>1</v>
@@ -7643,16 +7824,19 @@
       <c r="AC44" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD44" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="62">
         <v>45</v>
       </c>
       <c r="B45" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D45" s="31" t="s">
         <v>275</v>
@@ -7701,7 +7885,7 @@
         <v>356</v>
       </c>
       <c r="R45" s="66" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="S45" s="66" t="s">
         <v>1</v>
@@ -7719,7 +7903,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W45" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X45" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7728,11 +7912,11 @@
       <c r="Y45" s="66" t="s">
         <v>392</v>
       </c>
-      <c r="Z45" s="77" t="s">
+      <c r="Z45" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA45" s="66" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AB45" s="70" t="s">
         <v>1</v>
@@ -7740,16 +7924,19 @@
       <c r="AC45" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD45" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="62">
         <v>46</v>
       </c>
       <c r="B46" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D46" s="31" t="s">
         <v>275</v>
@@ -7798,7 +7985,7 @@
         <v>357</v>
       </c>
       <c r="R46" s="66" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="S46" s="66" t="s">
         <v>1</v>
@@ -7816,7 +8003,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W46" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X46" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7825,11 +8012,11 @@
       <c r="Y46" s="66" t="s">
         <v>393</v>
       </c>
-      <c r="Z46" s="77" t="s">
+      <c r="Z46" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA46" s="66" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AB46" s="70" t="s">
         <v>1</v>
@@ -7837,16 +8024,19 @@
       <c r="AC46" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD46" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="62">
         <v>47</v>
       </c>
       <c r="B47" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D47" s="31" t="s">
         <v>275</v>
@@ -7895,7 +8085,7 @@
         <v>358</v>
       </c>
       <c r="R47" s="66" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="S47" s="66" t="s">
         <v>1</v>
@@ -7913,20 +8103,20 @@
         <v>Terrenos</v>
       </c>
       <c r="W47" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X47" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-47</v>
       </c>
       <c r="Y47" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="Z47" s="77" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z47" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA47" s="66" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AB47" s="70" t="s">
         <v>1</v>
@@ -7934,16 +8124,19 @@
       <c r="AC47" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD47" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="62">
         <v>48</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C48" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D48" s="31" t="s">
         <v>275</v>
@@ -7992,7 +8185,7 @@
         <v>359</v>
       </c>
       <c r="R48" s="66" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="S48" s="66" t="s">
         <v>1</v>
@@ -8010,7 +8203,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W48" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X48" s="67" t="str">
         <f t="shared" si="3"/>
@@ -8019,11 +8212,11 @@
       <c r="Y48" s="66" t="s">
         <v>394</v>
       </c>
-      <c r="Z48" s="77" t="s">
+      <c r="Z48" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA48" s="66" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AB48" s="70" t="s">
         <v>1</v>
@@ -8031,16 +8224,19 @@
       <c r="AC48" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD48" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="62">
         <v>49</v>
       </c>
       <c r="B49" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C49" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D49" s="31" t="s">
         <v>275</v>
@@ -8089,7 +8285,7 @@
         <v>360</v>
       </c>
       <c r="R49" s="66" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="S49" s="66" t="s">
         <v>1</v>
@@ -8107,7 +8303,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W49" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X49" s="67" t="str">
         <f t="shared" si="3"/>
@@ -8116,11 +8312,11 @@
       <c r="Y49" s="66" t="s">
         <v>395</v>
       </c>
-      <c r="Z49" s="77" t="s">
+      <c r="Z49" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA49" s="66" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AB49" s="70" t="s">
         <v>1</v>
@@ -8128,16 +8324,19 @@
       <c r="AC49" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD49" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="62">
         <v>50</v>
       </c>
       <c r="B50" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C50" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D50" s="31" t="s">
         <v>275</v>
@@ -8186,7 +8385,7 @@
         <v>361</v>
       </c>
       <c r="R50" s="66" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="S50" s="66" t="s">
         <v>1</v>
@@ -8204,20 +8403,20 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W50" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X50" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-50</v>
       </c>
       <c r="Y50" s="66" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z50" s="77" t="s">
+        <v>608</v>
+      </c>
+      <c r="Z50" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA50" s="66" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AB50" s="70" t="s">
         <v>1</v>
@@ -8225,16 +8424,19 @@
       <c r="AC50" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD50" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="62">
         <v>51</v>
       </c>
       <c r="B51" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D51" s="31" t="s">
         <v>275</v>
@@ -8283,7 +8485,7 @@
         <v>362</v>
       </c>
       <c r="R51" s="66" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S51" s="66" t="s">
         <v>1</v>
@@ -8301,20 +8503,20 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W51" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X51" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-51</v>
       </c>
       <c r="Y51" s="66" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z51" s="77" t="s">
+        <v>608</v>
+      </c>
+      <c r="Z51" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA51" s="66" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AB51" s="70" t="s">
         <v>1</v>
@@ -8322,16 +8524,19 @@
       <c r="AC51" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD51" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="62">
         <v>52</v>
       </c>
       <c r="B52" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C52" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D52" s="31" t="s">
         <v>275</v>
@@ -8380,7 +8585,7 @@
         <v>363</v>
       </c>
       <c r="R52" s="66" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S52" s="66" t="s">
         <v>1</v>
@@ -8398,20 +8603,20 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W52" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X52" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-52</v>
       </c>
       <c r="Y52" s="66" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z52" s="77" t="s">
+        <v>608</v>
+      </c>
+      <c r="Z52" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA52" s="66" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AB52" s="70" t="s">
         <v>1</v>
@@ -8419,16 +8624,19 @@
       <c r="AC52" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD52" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="62">
         <v>53</v>
       </c>
       <c r="B53" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C53" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D53" s="31" t="s">
         <v>275</v>
@@ -8477,7 +8685,7 @@
         <v>364</v>
       </c>
       <c r="R53" s="66" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S53" s="66" t="s">
         <v>1</v>
@@ -8495,20 +8703,20 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W53" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X53" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-53</v>
       </c>
       <c r="Y53" s="66" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z53" s="77" t="s">
+        <v>608</v>
+      </c>
+      <c r="Z53" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA53" s="66" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AB53" s="70" t="s">
         <v>1</v>
@@ -8516,16 +8724,19 @@
       <c r="AC53" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD53" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="62">
         <v>54</v>
       </c>
       <c r="B54" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C54" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D54" s="31" t="s">
         <v>275</v>
@@ -8574,7 +8785,7 @@
         <v>365</v>
       </c>
       <c r="R54" s="66" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="S54" s="66" t="s">
         <v>1</v>
@@ -8592,7 +8803,7 @@
         <v>Sondagens</v>
       </c>
       <c r="W54" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X54" s="67" t="str">
         <f t="shared" si="3"/>
@@ -8601,7 +8812,7 @@
       <c r="Y54" s="66" t="s">
         <v>388</v>
       </c>
-      <c r="Z54" s="77" t="s">
+      <c r="Z54" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA54" s="66" t="s">
@@ -8613,19 +8824,22 @@
       <c r="AC54" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD54" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="55" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="62">
         <v>55</v>
       </c>
       <c r="B55" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C55" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E55" s="31" t="s">
         <v>272</v>
@@ -8674,7 +8888,7 @@
         <v>106</v>
       </c>
       <c r="R55" s="66" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="S55" s="66" t="s">
         <v>1</v>
@@ -8692,7 +8906,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W55" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X55" s="67" t="str">
         <f t="shared" si="3"/>
@@ -8701,7 +8915,7 @@
       <c r="Y55" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z55" s="77" t="s">
+      <c r="Z55" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA55" s="66" t="s">
@@ -8713,19 +8927,22 @@
       <c r="AC55" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD55" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="62">
         <v>56</v>
       </c>
       <c r="B56" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C56" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E56" s="31" t="s">
         <v>272</v>
@@ -8773,7 +8990,7 @@
         <v>108</v>
       </c>
       <c r="R56" s="66" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="S56" s="66" t="s">
         <v>1</v>
@@ -8791,7 +9008,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W56" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X56" s="67" t="str">
         <f t="shared" si="3"/>
@@ -8800,7 +9017,7 @@
       <c r="Y56" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z56" s="77" t="s">
+      <c r="Z56" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA56" s="66" t="s">
@@ -8812,19 +9029,22 @@
       <c r="AC56" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD56" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="62">
         <v>57</v>
       </c>
       <c r="B57" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C57" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E57" s="31" t="s">
         <v>272</v>
@@ -8870,7 +9090,7 @@
         <v>109</v>
       </c>
       <c r="R57" s="66" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="S57" s="66" t="s">
         <v>1</v>
@@ -8888,7 +9108,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W57" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X57" s="67" t="str">
         <f t="shared" si="3"/>
@@ -8897,7 +9117,7 @@
       <c r="Y57" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z57" s="77" t="s">
+      <c r="Z57" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA57" s="66" t="s">
@@ -8909,19 +9129,22 @@
       <c r="AC57" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD57" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="62">
         <v>58</v>
       </c>
       <c r="B58" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C58" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D58" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E58" s="31" t="s">
         <v>272</v>
@@ -8967,7 +9190,7 @@
         <v>112</v>
       </c>
       <c r="R58" s="66" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="S58" s="66" t="s">
         <v>1</v>
@@ -8985,7 +9208,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W58" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X58" s="67" t="str">
         <f t="shared" si="3"/>
@@ -8994,7 +9217,7 @@
       <c r="Y58" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z58" s="77" t="s">
+      <c r="Z58" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA58" s="66" t="s">
@@ -9006,19 +9229,22 @@
       <c r="AC58" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD58" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="59" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="62">
         <v>59</v>
       </c>
       <c r="B59" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C59" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D59" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E59" s="31" t="s">
         <v>272</v>
@@ -9064,7 +9290,7 @@
         <v>115</v>
       </c>
       <c r="R59" s="66" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="S59" s="66" t="s">
         <v>1</v>
@@ -9082,7 +9308,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W59" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X59" s="67" t="str">
         <f t="shared" si="3"/>
@@ -9091,7 +9317,7 @@
       <c r="Y59" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z59" s="77" t="s">
+      <c r="Z59" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA59" s="66" t="s">
@@ -9103,19 +9329,22 @@
       <c r="AC59" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD59" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="62">
         <v>60</v>
       </c>
       <c r="B60" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C60" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D60" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E60" s="31" t="s">
         <v>272</v>
@@ -9161,7 +9390,7 @@
         <v>118</v>
       </c>
       <c r="R60" s="66" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="S60" s="66" t="s">
         <v>1</v>
@@ -9179,7 +9408,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W60" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X60" s="67" t="str">
         <f t="shared" si="3"/>
@@ -9188,7 +9417,7 @@
       <c r="Y60" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z60" s="77" t="s">
+      <c r="Z60" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA60" s="66" t="s">
@@ -9200,19 +9429,22 @@
       <c r="AC60" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD60" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="62">
         <v>61</v>
       </c>
       <c r="B61" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C61" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D61" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E61" s="31" t="s">
         <v>272</v>
@@ -9258,7 +9490,7 @@
         <v>119</v>
       </c>
       <c r="R61" s="66" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="S61" s="66" t="s">
         <v>1</v>
@@ -9276,7 +9508,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W61" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X61" s="67" t="str">
         <f t="shared" si="3"/>
@@ -9285,7 +9517,7 @@
       <c r="Y61" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z61" s="77" t="s">
+      <c r="Z61" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA61" s="66" t="s">
@@ -9297,19 +9529,22 @@
       <c r="AC61" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD61" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="62" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="62">
         <v>62</v>
       </c>
       <c r="B62" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C62" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D62" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E62" s="31" t="s">
         <v>272</v>
@@ -9355,7 +9590,7 @@
         <v>118</v>
       </c>
       <c r="R62" s="66" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="S62" s="66" t="s">
         <v>1</v>
@@ -9373,7 +9608,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W62" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X62" s="67" t="str">
         <f t="shared" si="3"/>
@@ -9382,11 +9617,11 @@
       <c r="Y62" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z62" s="77" t="s">
+      <c r="Z62" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA62" s="66" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AB62" s="70" t="s">
         <v>1</v>
@@ -9394,19 +9629,22 @@
       <c r="AC62" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD62" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="63" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="62">
         <v>63</v>
       </c>
       <c r="B63" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C63" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E63" s="31" t="s">
         <v>271</v>
@@ -9452,7 +9690,7 @@
         <v>123</v>
       </c>
       <c r="R63" s="66" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="S63" s="66" t="s">
         <v>1</v>
@@ -9470,20 +9708,20 @@
         <v>Frações</v>
       </c>
       <c r="W63" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X63" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-63</v>
       </c>
       <c r="Y63" s="66" t="s">
-        <v>397</v>
-      </c>
-      <c r="Z63" s="77" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z63" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA63" s="66" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AB63" s="70" t="s">
         <v>1</v>
@@ -9491,19 +9729,22 @@
       <c r="AC63" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD63" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="64" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="62">
         <v>64</v>
       </c>
       <c r="B64" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C64" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E64" s="31" t="s">
         <v>271</v>
@@ -9549,7 +9790,7 @@
         <v>125</v>
       </c>
       <c r="R64" s="66" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="S64" s="66" t="s">
         <v>1</v>
@@ -9567,20 +9808,20 @@
         <v>Frações</v>
       </c>
       <c r="W64" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X64" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-64</v>
       </c>
       <c r="Y64" s="66" t="s">
-        <v>397</v>
-      </c>
-      <c r="Z64" s="77" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z64" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA64" s="66" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB64" s="70" t="s">
         <v>1</v>
@@ -9588,19 +9829,22 @@
       <c r="AC64" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD64" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="65" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="62">
         <v>65</v>
       </c>
       <c r="B65" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C65" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E65" s="31" t="s">
         <v>271</v>
@@ -9646,7 +9890,7 @@
         <v>127</v>
       </c>
       <c r="R65" s="66" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="S65" s="66" t="s">
         <v>1</v>
@@ -9664,20 +9908,20 @@
         <v>Frações</v>
       </c>
       <c r="W65" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X65" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-65</v>
       </c>
       <c r="Y65" s="66" t="s">
-        <v>398</v>
-      </c>
-      <c r="Z65" s="77" t="s">
+        <v>609</v>
+      </c>
+      <c r="Z65" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA65" s="66" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB65" s="70" t="s">
         <v>1</v>
@@ -9685,19 +9929,22 @@
       <c r="AC65" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD65" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="66" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="62">
         <v>66</v>
       </c>
       <c r="B66" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C66" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E66" s="31" t="s">
         <v>271</v>
@@ -9743,7 +9990,7 @@
         <v>129</v>
       </c>
       <c r="R66" s="66" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="S66" s="66" t="s">
         <v>1</v>
@@ -9761,20 +10008,20 @@
         <v>Frações</v>
       </c>
       <c r="W66" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X66" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-66</v>
       </c>
       <c r="Y66" s="66" t="s">
-        <v>398</v>
-      </c>
-      <c r="Z66" s="77" t="s">
+        <v>609</v>
+      </c>
+      <c r="Z66" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA66" s="66" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB66" s="70" t="s">
         <v>1</v>
@@ -9782,19 +10029,22 @@
       <c r="AC66" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD66" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="67" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="62">
         <v>67</v>
       </c>
       <c r="B67" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C67" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D67" s="31" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E67" s="31" t="s">
         <v>271</v>
@@ -9840,7 +10090,7 @@
         <v>131</v>
       </c>
       <c r="R67" s="66" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="S67" s="66" t="s">
         <v>1</v>
@@ -9858,16 +10108,16 @@
         <v>Frações</v>
       </c>
       <c r="W67" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X67" s="67" t="str">
-        <f t="shared" ref="X67:X101" si="13">CONCATENATE("Key-BRASIL-SP-",A67)</f>
+        <f t="shared" ref="X67:X105" si="13">CONCATENATE("Key-BRASIL-SP-",A67)</f>
         <v>Key-BRASIL-SP-67</v>
       </c>
       <c r="Y67" s="66" t="s">
-        <v>398</v>
-      </c>
-      <c r="Z67" s="77" t="s">
+        <v>609</v>
+      </c>
+      <c r="Z67" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA67" s="66" t="s">
@@ -9879,16 +10129,19 @@
       <c r="AC67" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD67" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="68" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="62">
         <v>68</v>
       </c>
       <c r="B68" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C68" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D68" s="31" t="s">
         <v>266</v>
@@ -9938,7 +10191,7 @@
         <v>366</v>
       </c>
       <c r="R68" s="66" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="S68" s="66" t="s">
         <v>1</v>
@@ -9956,7 +10209,7 @@
         <v>Construídas</v>
       </c>
       <c r="W68" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X68" s="67" t="str">
         <f t="shared" si="13"/>
@@ -9965,7 +10218,7 @@
       <c r="Y68" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z68" s="77" t="s">
+      <c r="Z68" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA68" s="66" t="s">
@@ -9977,16 +10230,19 @@
       <c r="AC68" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD68" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="69" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="62">
         <v>69</v>
       </c>
       <c r="B69" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C69" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D69" s="31" t="s">
         <v>266</v>
@@ -10036,7 +10292,7 @@
         <v>133</v>
       </c>
       <c r="R69" s="66" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="S69" s="66" t="s">
         <v>1</v>
@@ -10054,7 +10310,7 @@
         <v>Construídas</v>
       </c>
       <c r="W69" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X69" s="67" t="str">
         <f t="shared" si="13"/>
@@ -10063,7 +10319,7 @@
       <c r="Y69" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z69" s="77" t="s">
+      <c r="Z69" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA69" s="66" t="s">
@@ -10075,16 +10331,19 @@
       <c r="AC69" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD69" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="70" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="62">
         <v>70</v>
       </c>
       <c r="B70" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C70" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D70" s="31" t="s">
         <v>266</v>
@@ -10134,7 +10393,7 @@
         <v>135</v>
       </c>
       <c r="R70" s="66" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="S70" s="66" t="s">
         <v>1</v>
@@ -10152,7 +10411,7 @@
         <v>Construídas</v>
       </c>
       <c r="W70" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X70" s="67" t="str">
         <f t="shared" si="13"/>
@@ -10161,7 +10420,7 @@
       <c r="Y70" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z70" s="77" t="s">
+      <c r="Z70" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA70" s="66" t="s">
@@ -10173,16 +10432,19 @@
       <c r="AC70" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD70" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="71" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="62">
         <v>71</v>
       </c>
       <c r="B71" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C71" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D71" s="31" t="s">
         <v>266</v>
@@ -10232,7 +10494,7 @@
         <v>136</v>
       </c>
       <c r="R71" s="66" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="S71" s="66" t="s">
         <v>1</v>
@@ -10250,7 +10512,7 @@
         <v>Construídas</v>
       </c>
       <c r="W71" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X71" s="67" t="str">
         <f t="shared" si="13"/>
@@ -10259,7 +10521,7 @@
       <c r="Y71" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z71" s="77" t="s">
+      <c r="Z71" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA71" s="66" t="s">
@@ -10271,16 +10533,19 @@
       <c r="AC71" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD71" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="72" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="62">
         <v>72</v>
       </c>
       <c r="B72" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C72" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D72" s="31" t="s">
         <v>266</v>
@@ -10330,7 +10595,7 @@
         <v>138</v>
       </c>
       <c r="R72" s="66" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="S72" s="66" t="s">
         <v>1</v>
@@ -10348,7 +10613,7 @@
         <v>Construídas</v>
       </c>
       <c r="W72" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X72" s="67" t="str">
         <f t="shared" si="13"/>
@@ -10357,7 +10622,7 @@
       <c r="Y72" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z72" s="77" t="s">
+      <c r="Z72" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA72" s="66" t="s">
@@ -10369,16 +10634,19 @@
       <c r="AC72" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD72" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="73" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="62">
         <v>73</v>
       </c>
       <c r="B73" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C73" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D73" s="31" t="s">
         <v>266</v>
@@ -10427,7 +10695,7 @@
         <v>141</v>
       </c>
       <c r="R73" s="66" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="S73" s="66" t="s">
         <v>1</v>
@@ -10445,7 +10713,7 @@
         <v>Construídas</v>
       </c>
       <c r="W73" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X73" s="67" t="str">
         <f t="shared" si="13"/>
@@ -10454,7 +10722,7 @@
       <c r="Y73" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z73" s="77" t="s">
+      <c r="Z73" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA73" s="66" t="s">
@@ -10466,16 +10734,19 @@
       <c r="AC73" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD73" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="74" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="62">
         <v>74</v>
       </c>
       <c r="B74" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C74" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D74" s="31" t="s">
         <v>266</v>
@@ -10524,7 +10795,7 @@
         <v>142</v>
       </c>
       <c r="R74" s="66" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="S74" s="66" t="s">
         <v>1</v>
@@ -10542,7 +10813,7 @@
         <v>Construídas</v>
       </c>
       <c r="W74" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X74" s="67" t="str">
         <f t="shared" si="13"/>
@@ -10551,11 +10822,11 @@
       <c r="Y74" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z74" s="77" t="s">
+      <c r="Z74" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA74" s="66" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB74" s="70" t="s">
         <v>1</v>
@@ -10563,16 +10834,19 @@
       <c r="AC74" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD74" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="75" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="62">
         <v>75</v>
       </c>
       <c r="B75" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C75" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D75" s="31" t="s">
         <v>267</v>
@@ -10622,7 +10896,7 @@
         <v>145</v>
       </c>
       <c r="R75" s="66" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="S75" s="66" t="s">
         <v>1</v>
@@ -10640,7 +10914,7 @@
         <v>Organizativas</v>
       </c>
       <c r="W75" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X75" s="67" t="str">
         <f t="shared" si="13"/>
@@ -10649,11 +10923,11 @@
       <c r="Y75" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="Z75" s="77" t="s">
+      <c r="Z75" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA75" s="66" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB75" s="70" t="s">
         <v>1</v>
@@ -10661,16 +10935,19 @@
       <c r="AC75" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD75" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="76" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="62">
         <v>76</v>
       </c>
       <c r="B76" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C76" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D76" s="31" t="s">
         <v>267</v>
@@ -10719,7 +10996,7 @@
         <v>146</v>
       </c>
       <c r="R76" s="66" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="S76" s="66" t="s">
         <v>1</v>
@@ -10737,20 +11014,20 @@
         <v>Organizativas</v>
       </c>
       <c r="W76" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X76" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-76</v>
       </c>
       <c r="Y76" s="66" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z76" s="77" t="s">
+        <v>610</v>
+      </c>
+      <c r="Z76" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA76" s="66" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB76" s="70" t="s">
         <v>1</v>
@@ -10758,16 +11035,19 @@
       <c r="AC76" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD76" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="77" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="62">
         <v>77</v>
       </c>
       <c r="B77" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C77" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D77" s="31" t="s">
         <v>267</v>
@@ -10816,7 +11096,7 @@
         <v>148</v>
       </c>
       <c r="R77" s="66" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="S77" s="66" t="s">
         <v>1</v>
@@ -10834,20 +11114,20 @@
         <v>Organizativas</v>
       </c>
       <c r="W77" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X77" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-77</v>
       </c>
       <c r="Y77" s="66" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z77" s="77" t="s">
+        <v>610</v>
+      </c>
+      <c r="Z77" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA77" s="66" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB77" s="70" t="s">
         <v>1</v>
@@ -10855,16 +11135,19 @@
       <c r="AC77" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD77" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="78" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="62">
         <v>78</v>
       </c>
       <c r="B78" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C78" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D78" s="31" t="s">
         <v>267</v>
@@ -10913,7 +11196,7 @@
         <v>149</v>
       </c>
       <c r="R78" s="66" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="S78" s="66" t="s">
         <v>1</v>
@@ -10931,20 +11214,20 @@
         <v>Organizativas</v>
       </c>
       <c r="W78" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X78" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-78</v>
       </c>
       <c r="Y78" s="66" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z78" s="77" t="s">
+        <v>610</v>
+      </c>
+      <c r="Z78" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA78" s="66" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AB78" s="70" t="s">
         <v>1</v>
@@ -10952,16 +11235,19 @@
       <c r="AC78" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD78" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="79" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="62">
         <v>79</v>
       </c>
       <c r="B79" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C79" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D79" s="31" t="s">
         <v>267</v>
@@ -11010,7 +11296,7 @@
         <v>150</v>
       </c>
       <c r="R79" s="66" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="S79" s="66" t="s">
         <v>1</v>
@@ -11028,20 +11314,20 @@
         <v>Distribuição</v>
       </c>
       <c r="W79" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X79" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-79</v>
       </c>
       <c r="Y79" s="66" t="s">
-        <v>400</v>
-      </c>
-      <c r="Z79" s="77" t="s">
+        <v>397</v>
+      </c>
+      <c r="Z79" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA79" s="66" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB79" s="70" t="s">
         <v>1</v>
@@ -11049,16 +11335,19 @@
       <c r="AC79" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD79" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="80" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="62">
         <v>80</v>
       </c>
       <c r="B80" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C80" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D80" s="31" t="s">
         <v>267</v>
@@ -11107,7 +11396,7 @@
         <v>151</v>
       </c>
       <c r="R80" s="66" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="S80" s="66" t="s">
         <v>1</v>
@@ -11125,20 +11414,20 @@
         <v>Distribuição</v>
       </c>
       <c r="W80" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X80" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-80</v>
       </c>
       <c r="Y80" s="66" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z80" s="77" t="s">
+        <v>610</v>
+      </c>
+      <c r="Z80" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA80" s="66" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB80" s="70" t="s">
         <v>1</v>
@@ -11146,16 +11435,19 @@
       <c r="AC80" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD80" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="81" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="62">
         <v>81</v>
       </c>
       <c r="B81" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C81" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D81" s="31" t="s">
         <v>267</v>
@@ -11204,7 +11496,7 @@
         <v>153</v>
       </c>
       <c r="R81" s="66" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="S81" s="66" t="s">
         <v>1</v>
@@ -11222,20 +11514,20 @@
         <v>Distribuição</v>
       </c>
       <c r="W81" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X81" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-81</v>
       </c>
       <c r="Y81" s="66" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z81" s="77" t="s">
+        <v>610</v>
+      </c>
+      <c r="Z81" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA81" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB81" s="70" t="s">
         <v>1</v>
@@ -11243,19 +11535,22 @@
       <c r="AC81" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD81" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="82" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="62">
         <v>82</v>
       </c>
       <c r="B82" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C82" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D82" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E82" s="31" t="s">
         <v>154</v>
@@ -11301,7 +11596,7 @@
         <v>156</v>
       </c>
       <c r="R82" s="66" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="S82" s="66" t="s">
         <v>1</v>
@@ -11319,20 +11614,20 @@
         <v>Saúde</v>
       </c>
       <c r="W82" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X82" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-82</v>
       </c>
       <c r="Y82" s="66" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z82" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z82" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA82" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB82" s="70" t="s">
         <v>1</v>
@@ -11340,19 +11635,22 @@
       <c r="AC82" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD82" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="83" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="62">
         <v>83</v>
       </c>
       <c r="B83" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C83" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D83" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E83" s="31" t="s">
         <v>154</v>
@@ -11398,7 +11696,7 @@
         <v>158</v>
       </c>
       <c r="R83" s="66" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="S83" s="66" t="s">
         <v>1</v>
@@ -11416,20 +11714,20 @@
         <v>Saúde</v>
       </c>
       <c r="W83" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X83" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-83</v>
       </c>
       <c r="Y83" s="66" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z83" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z83" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA83" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB83" s="70" t="s">
         <v>1</v>
@@ -11437,19 +11735,22 @@
       <c r="AC83" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD83" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="84" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="62">
         <v>84</v>
       </c>
       <c r="B84" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C84" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D84" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E84" s="31" t="s">
         <v>154</v>
@@ -11495,7 +11796,7 @@
         <v>160</v>
       </c>
       <c r="R84" s="66" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="S84" s="66" t="s">
         <v>1</v>
@@ -11513,20 +11814,20 @@
         <v>Saúde</v>
       </c>
       <c r="W84" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X84" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-84</v>
       </c>
       <c r="Y84" s="66" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z84" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z84" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA84" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB84" s="70" t="s">
         <v>1</v>
@@ -11534,19 +11835,22 @@
       <c r="AC84" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD84" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="85" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="62">
         <v>85</v>
       </c>
       <c r="B85" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C85" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D85" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E85" s="31" t="s">
         <v>154</v>
@@ -11592,7 +11896,7 @@
         <v>163</v>
       </c>
       <c r="R85" s="66" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="S85" s="66" t="s">
         <v>1</v>
@@ -11610,20 +11914,20 @@
         <v>Saúde</v>
       </c>
       <c r="W85" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X85" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-85</v>
       </c>
       <c r="Y85" s="66" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z85" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z85" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA85" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB85" s="70" t="s">
         <v>1</v>
@@ -11631,19 +11935,22 @@
       <c r="AC85" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD85" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="86" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="62">
         <v>86</v>
       </c>
       <c r="B86" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C86" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D86" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E86" s="31" t="s">
         <v>154</v>
@@ -11689,7 +11996,7 @@
         <v>166</v>
       </c>
       <c r="R86" s="66" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="S86" s="66" t="s">
         <v>1</v>
@@ -11707,20 +12014,20 @@
         <v>Saúde</v>
       </c>
       <c r="W86" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X86" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-86</v>
       </c>
       <c r="Y86" s="66" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z86" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z86" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA86" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB86" s="70" t="s">
         <v>1</v>
@@ -11728,19 +12035,22 @@
       <c r="AC86" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD86" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="87" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="62">
         <v>87</v>
       </c>
       <c r="B87" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C87" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D87" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E87" s="31" t="s">
         <v>270</v>
@@ -11786,7 +12096,7 @@
         <v>168</v>
       </c>
       <c r="R87" s="66" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="S87" s="66" t="s">
         <v>1</v>
@@ -11804,20 +12114,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W87" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X87" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-87</v>
       </c>
       <c r="Y87" s="66" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z87" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z87" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA87" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB87" s="70" t="s">
         <v>1</v>
@@ -11825,19 +12135,22 @@
       <c r="AC87" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD87" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="62">
         <v>88</v>
       </c>
       <c r="B88" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C88" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D88" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E88" s="31" t="s">
         <v>270</v>
@@ -11883,7 +12196,7 @@
         <v>170</v>
       </c>
       <c r="R88" s="66" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="S88" s="66" t="s">
         <v>1</v>
@@ -11901,20 +12214,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W88" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X88" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-88</v>
       </c>
       <c r="Y88" s="66" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z88" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z88" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA88" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB88" s="70" t="s">
         <v>1</v>
@@ -11922,19 +12235,22 @@
       <c r="AC88" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD88" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="62">
         <v>89</v>
       </c>
       <c r="B89" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C89" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D89" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E89" s="31" t="s">
         <v>270</v>
@@ -11980,7 +12296,7 @@
         <v>172</v>
       </c>
       <c r="R89" s="66" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="S89" s="66" t="s">
         <v>1</v>
@@ -11998,20 +12314,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W89" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X89" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-89</v>
       </c>
       <c r="Y89" s="66" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z89" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z89" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA89" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB89" s="70" t="s">
         <v>1</v>
@@ -12019,19 +12335,22 @@
       <c r="AC89" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD89" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="62">
         <v>90</v>
       </c>
       <c r="B90" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C90" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D90" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E90" s="31" t="s">
         <v>270</v>
@@ -12077,7 +12396,7 @@
         <v>174</v>
       </c>
       <c r="R90" s="66" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="S90" s="66" t="s">
         <v>1</v>
@@ -12095,20 +12414,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W90" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X90" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-90</v>
       </c>
       <c r="Y90" s="66" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z90" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z90" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA90" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB90" s="70" t="s">
         <v>1</v>
@@ -12116,19 +12435,22 @@
       <c r="AC90" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD90" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="62">
         <v>91</v>
       </c>
       <c r="B91" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C91" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D91" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E91" s="31" t="s">
         <v>270</v>
@@ -12174,7 +12496,7 @@
         <v>369</v>
       </c>
       <c r="R91" s="66" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="S91" s="66" t="s">
         <v>1</v>
@@ -12192,20 +12514,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W91" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X91" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-91</v>
       </c>
       <c r="Y91" s="66" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z91" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z91" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA91" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AB91" s="70" t="s">
         <v>1</v>
@@ -12213,19 +12535,22 @@
       <c r="AC91" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD91" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="62">
         <v>92</v>
       </c>
       <c r="B92" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C92" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D92" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E92" s="31" t="s">
         <v>270</v>
@@ -12271,7 +12596,7 @@
         <v>372</v>
       </c>
       <c r="R92" s="66" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="S92" s="66" t="s">
         <v>1</v>
@@ -12289,20 +12614,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W92" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X92" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-92</v>
       </c>
       <c r="Y92" s="66" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z92" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z92" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA92" s="66" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AB92" s="70" t="s">
         <v>1</v>
@@ -12310,19 +12635,22 @@
       <c r="AC92" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD92" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="62">
         <v>93</v>
       </c>
       <c r="B93" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C93" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D93" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E93" s="31" t="s">
         <v>175</v>
@@ -12368,7 +12696,7 @@
         <v>178</v>
       </c>
       <c r="R93" s="66" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="S93" s="66" t="s">
         <v>1</v>
@@ -12386,20 +12714,20 @@
         <v>INMET</v>
       </c>
       <c r="W93" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X93" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-93</v>
       </c>
       <c r="Y93" s="66" t="s">
-        <v>402</v>
-      </c>
-      <c r="Z93" s="77" t="s">
+        <v>399</v>
+      </c>
+      <c r="Z93" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA93" s="66" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AB93" s="70" t="s">
         <v>1</v>
@@ -12407,25 +12735,28 @@
       <c r="AC93" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD93" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="62">
         <v>94</v>
       </c>
       <c r="B94" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C94" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D94" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E94" s="31" t="s">
         <v>175</v>
       </c>
       <c r="F94" s="37" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="G94" s="68" t="s">
         <v>1</v>
@@ -12459,13 +12790,13 @@
         <v>Estação Meteorológica Automática</v>
       </c>
       <c r="P94" s="69" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="Q94" s="69" t="s">
         <v>178</v>
       </c>
       <c r="R94" s="66" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="S94" s="66" t="s">
         <v>1</v>
@@ -12483,20 +12814,20 @@
         <v>INMET</v>
       </c>
       <c r="W94" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X94" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-94</v>
       </c>
       <c r="Y94" s="66" t="s">
-        <v>402</v>
-      </c>
-      <c r="Z94" s="77" t="s">
+        <v>399</v>
+      </c>
+      <c r="Z94" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA94" s="66" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AB94" s="70" t="s">
         <v>1</v>
@@ -12504,25 +12835,28 @@
       <c r="AC94" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD94" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="62">
         <v>95</v>
       </c>
       <c r="B95" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C95" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D95" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E95" s="31" t="s">
         <v>175</v>
       </c>
       <c r="F95" s="37" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="G95" s="68" t="s">
         <v>1</v>
@@ -12556,13 +12890,13 @@
         <v>Estação Meteorológica Convencional</v>
       </c>
       <c r="P95" s="69" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="Q95" s="69" t="s">
         <v>178</v>
       </c>
       <c r="R95" s="66" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="S95" s="66" t="s">
         <v>1</v>
@@ -12580,20 +12914,20 @@
         <v>INMET</v>
       </c>
       <c r="W95" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X95" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-95</v>
       </c>
       <c r="Y95" s="66" t="s">
-        <v>402</v>
-      </c>
-      <c r="Z95" s="77" t="s">
+        <v>399</v>
+      </c>
+      <c r="Z95" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA95" s="66" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AB95" s="70" t="s">
         <v>1</v>
@@ -12601,19 +12935,22 @@
       <c r="AC95" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD95" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="62">
         <v>96</v>
       </c>
       <c r="B96" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C96" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D96" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E96" s="31" t="s">
         <v>179</v>
@@ -12659,7 +12996,7 @@
         <v>182</v>
       </c>
       <c r="R96" s="66" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="S96" s="66" t="s">
         <v>1</v>
@@ -12677,19 +13014,19 @@
         <v>IBGE</v>
       </c>
       <c r="W96" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X96" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-96</v>
       </c>
-      <c r="Y96" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z96" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA96" s="77" t="s">
+      <c r="Y96" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z96" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA96" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AB96" s="70" t="s">
@@ -12698,19 +13035,22 @@
       <c r="AC96" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD96" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="62">
         <v>97</v>
       </c>
       <c r="B97" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C97" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D97" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E97" s="31" t="s">
         <v>179</v>
@@ -12756,7 +13096,7 @@
         <v>182</v>
       </c>
       <c r="R97" s="66" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="S97" s="66" t="s">
         <v>1</v>
@@ -12774,19 +13114,19 @@
         <v>IBGE</v>
       </c>
       <c r="W97" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X97" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-97</v>
       </c>
-      <c r="Y97" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z97" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA97" s="77" t="s">
+      <c r="Y97" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z97" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA97" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AB97" s="70" t="s">
@@ -12795,19 +13135,22 @@
       <c r="AC97" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD97" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="98" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="62">
         <v>98</v>
       </c>
       <c r="B98" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C98" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D98" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E98" s="31" t="s">
         <v>179</v>
@@ -12853,7 +13196,7 @@
         <v>186</v>
       </c>
       <c r="R98" s="66" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="S98" s="66" t="s">
         <v>1</v>
@@ -12871,19 +13214,19 @@
         <v>IBGE</v>
       </c>
       <c r="W98" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X98" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-98</v>
       </c>
-      <c r="Y98" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z98" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA98" s="77" t="s">
+      <c r="Y98" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z98" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA98" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AB98" s="70" t="s">
@@ -12892,19 +13235,22 @@
       <c r="AC98" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD98" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="99" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="62">
         <v>99</v>
       </c>
       <c r="B99" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C99" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D99" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E99" s="31" t="s">
         <v>179</v>
@@ -12950,7 +13296,7 @@
         <v>189</v>
       </c>
       <c r="R99" s="66" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="S99" s="66" t="s">
         <v>1</v>
@@ -12968,19 +13314,19 @@
         <v>IBGE</v>
       </c>
       <c r="W99" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X99" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-99</v>
       </c>
-      <c r="Y99" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z99" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA99" s="77" t="s">
+      <c r="Y99" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z99" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA99" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AB99" s="70" t="s">
@@ -12989,19 +13335,22 @@
       <c r="AC99" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD99" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="100" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="62">
         <v>100</v>
       </c>
       <c r="B100" s="63" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D100" s="31" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E100" s="31" t="s">
         <v>179</v>
@@ -13047,7 +13396,7 @@
         <v>192</v>
       </c>
       <c r="R100" s="66" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="S100" s="66" t="s">
         <v>1</v>
@@ -13065,19 +13414,19 @@
         <v>IBGE</v>
       </c>
       <c r="W100" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X100" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-100</v>
       </c>
-      <c r="Y100" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z100" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA100" s="77" t="s">
+      <c r="Y100" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z100" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA100" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AB100" s="70" t="s">
@@ -13086,74 +13435,77 @@
       <c r="AC100" s="70" t="s">
         <v>1</v>
       </c>
+      <c r="AD100" s="70" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="101" spans="1:29" s="78" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="62">
         <v>101</v>
       </c>
-      <c r="B101" s="72" t="s">
+      <c r="B101" s="77" t="s">
+        <v>582</v>
+      </c>
+      <c r="C101" s="37" t="s">
+        <v>583</v>
+      </c>
+      <c r="D101" s="37" t="s">
+        <v>585</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>584</v>
+      </c>
+      <c r="F101" s="37" t="s">
         <v>586</v>
       </c>
-      <c r="C101" s="73" t="s">
-        <v>587</v>
-      </c>
-      <c r="D101" s="73" t="s">
-        <v>589</v>
-      </c>
-      <c r="E101" s="73" t="s">
-        <v>588</v>
-      </c>
-      <c r="F101" s="73" t="s">
-        <v>590</v>
-      </c>
-      <c r="G101" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H101" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="I101" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="J101" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="K101" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="L101" s="75" t="str">
-        <f t="shared" ref="L101:O101" si="16">SUBSTITUTE(CONCATENATE("", C101), ".", " ")</f>
+      <c r="G101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="I101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="J101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="L101" s="73" t="str">
+        <f t="shared" ref="L101:O105" si="16">SUBSTITUTE(CONCATENATE("", C101), ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="M101" s="75" t="str">
+      <c r="M101" s="73" t="str">
         <f t="shared" si="16"/>
         <v>Macros</v>
       </c>
-      <c r="N101" s="75" t="str">
+      <c r="N101" s="73" t="str">
         <f t="shared" si="16"/>
         <v>Métodos</v>
       </c>
-      <c r="O101" s="75" t="str">
+      <c r="O101" s="73" t="str">
         <f t="shared" si="16"/>
-        <v>API Revit</v>
-      </c>
-      <c r="P101" s="76" t="s">
-        <v>591</v>
-      </c>
-      <c r="Q101" s="76" t="s">
-        <v>592</v>
-      </c>
-      <c r="R101" s="76" t="s">
-        <v>593</v>
-      </c>
-      <c r="S101" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="T101" s="76" t="str">
-        <f t="shared" ref="T101:V101" si="17">SUBSTITUTE(C101, ".", " ")</f>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P101" s="74" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q101" s="74" t="s">
+        <v>588</v>
+      </c>
+      <c r="R101" s="74" t="s">
+        <v>589</v>
+      </c>
+      <c r="S101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="T101" s="74" t="str">
+        <f t="shared" ref="T101:V105" si="17">SUBSTITUTE(C101, ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="U101" s="76" t="str">
+      <c r="U101" s="74" t="str">
         <f t="shared" si="17"/>
         <v>Macros</v>
       </c>
@@ -13162,103 +13514,509 @@
         <v>Métodos</v>
       </c>
       <c r="W101" s="66" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="X101" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-101</v>
       </c>
-      <c r="Y101" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z101" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA101" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB101" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC101" s="77" t="s">
+      <c r="Y101" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z101" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA101" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC101" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD101" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="62">
+        <v>102</v>
+      </c>
+      <c r="B102" s="77" t="s">
+        <v>582</v>
+      </c>
+      <c r="C102" s="37" t="s">
+        <v>583</v>
+      </c>
+      <c r="D102" s="37" t="s">
+        <v>585</v>
+      </c>
+      <c r="E102" s="37" t="s">
+        <v>584</v>
+      </c>
+      <c r="F102" s="37" t="s">
+        <v>590</v>
+      </c>
+      <c r="G102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="H102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="I102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="J102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="L102" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>De API</v>
+      </c>
+      <c r="M102" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Macros</v>
+      </c>
+      <c r="N102" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O102" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P102" s="74" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q102" s="74" t="s">
+        <v>592</v>
+      </c>
+      <c r="R102" s="74" t="s">
+        <v>593</v>
+      </c>
+      <c r="S102" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="T102" s="74" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U102" s="74" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V102" s="66" t="str">
+        <f t="shared" si="17"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W102" s="66" t="s">
+        <v>435</v>
+      </c>
+      <c r="X102" s="67" t="str">
+        <f t="shared" si="13"/>
+        <v>Key-BRASIL-SP-102</v>
+      </c>
+      <c r="Y102" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z102" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA102" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC102" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD102" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="62">
+        <v>103</v>
+      </c>
+      <c r="B103" s="77" t="s">
+        <v>582</v>
+      </c>
+      <c r="C103" s="37" t="s">
+        <v>583</v>
+      </c>
+      <c r="D103" s="37" t="s">
+        <v>585</v>
+      </c>
+      <c r="E103" s="37" t="s">
+        <v>584</v>
+      </c>
+      <c r="F103" s="37" t="s">
+        <v>594</v>
+      </c>
+      <c r="G103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="H103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="I103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="J103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="L103" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>De API</v>
+      </c>
+      <c r="M103" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Macros</v>
+      </c>
+      <c r="N103" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O103" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P103" s="74" t="s">
+        <v>595</v>
+      </c>
+      <c r="Q103" s="74" t="s">
+        <v>596</v>
+      </c>
+      <c r="R103" s="74" t="s">
+        <v>597</v>
+      </c>
+      <c r="S103" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="T103" s="74" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U103" s="74" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V103" s="66" t="str">
+        <f t="shared" si="17"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W103" s="66" t="s">
+        <v>435</v>
+      </c>
+      <c r="X103" s="67" t="str">
+        <f t="shared" si="13"/>
+        <v>Key-BRASIL-SP-103</v>
+      </c>
+      <c r="Y103" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z103" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA103" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB103" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC103" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD103" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="62">
+        <v>104</v>
+      </c>
+      <c r="B104" s="77" t="s">
+        <v>582</v>
+      </c>
+      <c r="C104" s="37" t="s">
+        <v>583</v>
+      </c>
+      <c r="D104" s="37" t="s">
+        <v>585</v>
+      </c>
+      <c r="E104" s="37" t="s">
+        <v>584</v>
+      </c>
+      <c r="F104" s="37" t="s">
+        <v>598</v>
+      </c>
+      <c r="G104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="H104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="I104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="J104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="L104" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>De API</v>
+      </c>
+      <c r="M104" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Macros</v>
+      </c>
+      <c r="N104" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O104" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P104" s="74" t="s">
+        <v>599</v>
+      </c>
+      <c r="Q104" s="74" t="s">
+        <v>600</v>
+      </c>
+      <c r="R104" s="74" t="s">
+        <v>601</v>
+      </c>
+      <c r="S104" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="T104" s="74" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U104" s="74" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V104" s="66" t="str">
+        <f t="shared" si="17"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W104" s="66" t="s">
+        <v>435</v>
+      </c>
+      <c r="X104" s="67" t="str">
+        <f t="shared" si="13"/>
+        <v>Key-BRASIL-SP-104</v>
+      </c>
+      <c r="Y104" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z104" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA104" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB104" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC104" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD104" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="62">
+        <v>105</v>
+      </c>
+      <c r="B105" s="77" t="s">
+        <v>582</v>
+      </c>
+      <c r="C105" s="37" t="s">
+        <v>583</v>
+      </c>
+      <c r="D105" s="37" t="s">
+        <v>585</v>
+      </c>
+      <c r="E105" s="37" t="s">
+        <v>602</v>
+      </c>
+      <c r="F105" s="37" t="s">
+        <v>603</v>
+      </c>
+      <c r="G105" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="H105" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="I105" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="J105" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K105" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="L105" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>De API</v>
+      </c>
+      <c r="M105" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Macros</v>
+      </c>
+      <c r="N105" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O105" s="73" t="str">
+        <f t="shared" si="16"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P105" s="74" t="s">
+        <v>604</v>
+      </c>
+      <c r="Q105" s="74" t="s">
+        <v>605</v>
+      </c>
+      <c r="R105" s="74" t="s">
+        <v>606</v>
+      </c>
+      <c r="S105" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="T105" s="74" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U105" s="74" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V105" s="66" t="str">
+        <f t="shared" si="17"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W105" s="66" t="s">
+        <v>435</v>
+      </c>
+      <c r="X105" s="67" t="str">
+        <f t="shared" si="13"/>
+        <v>Key-BRASIL-SP-105</v>
+      </c>
+      <c r="Y105" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z105" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA105" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB105" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC105" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD105" s="75" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B101">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B105">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:D100 L41:Q100 T41:V100 AD41:XFD100 AD102:XFD1048576">
-    <cfRule type="cellIs" dxfId="32" priority="8" operator="equal">
+  <conditionalFormatting sqref="C2:D100 L41:Q100 T41:V100 AE41:XFD100 AE106:XFD1048576">
+    <cfRule type="cellIs" dxfId="33" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F102:F1048576 A1:D1 T1:X1 A102:D1048576 T102:X1048576">
-    <cfRule type="cellIs" dxfId="31" priority="460" operator="equal">
+  <conditionalFormatting sqref="E105:F105">
+    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1 F106:F1048576 A1:D1 T1:X1 A106:D1048576 T106:X1048576">
+    <cfRule type="cellIs" dxfId="31" priority="464" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="30" priority="1498"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1502"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AD1:XFD29 T2:V28 L7:O9 Q7:Q9 L10:Q29 T29:U29 V29:V40 O30:O40">
-    <cfRule type="cellIs" dxfId="29" priority="19" operator="equal">
+  <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AE1:XFD29 T2:V28 L7:O9 Q7:Q9 L10:Q29 T29:U29 V29:V40 O30:O40">
+    <cfRule type="cellIs" dxfId="29" priority="23" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F93 F96:F100">
-    <cfRule type="duplicateValues" dxfId="28" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F40">
-    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F40">
-    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F100 F2:F93">
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F101">
+  <conditionalFormatting sqref="F101:F104">
     <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F102:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="14" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="977"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="980"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="984"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="988"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="992"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="996"/>
+  <conditionalFormatting sqref="F106:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="14" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="981"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1000"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L102:R1048576">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+  <conditionalFormatting sqref="L106:R1048576">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R101">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R100">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W101">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+  <conditionalFormatting sqref="W2:W105">
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13269,15 +14027,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="23" t="s">
         <v>22</v>
       </c>
@@ -13342,7 +14100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -13407,7 +14165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -13487,14 +14245,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21">
         <v>1</v>
       </c>
@@ -13508,7 +14266,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="13">
         <v>2</v>
       </c>
@@ -13522,7 +14280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="13">
         <v>3</v>
       </c>
@@ -13536,7 +14294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="13">
         <v>4</v>
       </c>
@@ -13550,7 +14308,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="13">
         <v>5</v>
       </c>
@@ -13564,7 +14322,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="13">
         <v>6</v>
       </c>
@@ -13591,68 +14349,68 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:BE10"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.53515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="32.53515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="3.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.53515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.84375" style="48" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.84375" style="48" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.84375" style="48" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.84375" style="58" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.84375" style="58" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="3.84375" style="58" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="3.84375" style="58" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="3.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.84375" style="58" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="3.84375" style="48" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="3.84375" style="48" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="7.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.3046875" style="48" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.3828125" style="25" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.84375" style="48" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.69140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="16.3046875" style="48" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="5.84375" style="48" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="5.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="9.69140625" style="48" bestFit="1" customWidth="1"/>
-    <col min="58" max="16384" width="9.15234375" style="25"/>
+    <col min="15" max="15" width="32.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.85546875" style="58" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="3.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.42578125" style="25" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="5.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="5.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="5.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="9.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="58" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>74</v>
       </c>
@@ -13660,7 +14418,7 @@
         <v>34</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D1" s="19" t="s">
         <v>33</v>
@@ -13821,7 +14579,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38">
         <v>2</v>
       </c>
@@ -13973,29 +14731,29 @@
         <v>381</v>
       </c>
       <c r="AY2" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AZ2" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA2" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="BB2" s="32" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BC2" s="40" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="BD2" s="32" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="BE2" s="40" t="str">
         <f t="shared" ref="BE2" si="0">_xlfn.CONCAT("""",C2,"""")</f>
         <v>"Continente"</v>
       </c>
     </row>
-    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38">
         <v>3</v>
       </c>
@@ -14147,29 +14905,29 @@
         <v>381</v>
       </c>
       <c r="AY3" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AZ3" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA3" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="BB3" s="32" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BC3" s="40" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="BD3" s="32" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="BE3" s="40" t="str">
         <f t="shared" ref="BE3" si="1">_xlfn.CONCAT("""",C3,"""")</f>
         <v>"SubContinente"</v>
       </c>
     </row>
-    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="38">
         <v>4</v>
       </c>
@@ -14321,29 +15079,29 @@
         <v>381</v>
       </c>
       <c r="AY4" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AZ4" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA4" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="BB4" s="32" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BC4" s="40" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="BD4" s="32" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="BE4" s="40" t="str">
         <f t="shared" ref="BE4:BE5" si="2">_xlfn.CONCAT("""",C4,"""")</f>
         <v>"País"</v>
       </c>
     </row>
-    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>5</v>
       </c>
@@ -14495,29 +15253,29 @@
         <v>381</v>
       </c>
       <c r="AY5" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AZ5" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA5" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="BB5" s="32" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BC5" s="40" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="BD5" s="32" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="BE5" s="40" t="str">
         <f t="shared" si="2"/>
         <v>"Região"</v>
       </c>
     </row>
-    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="38">
         <v>6</v>
       </c>
@@ -14669,29 +15427,29 @@
         <v>381</v>
       </c>
       <c r="AY6" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AZ6" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA6" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="BB6" s="32" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BC6" s="40" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="BD6" s="32" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="BE6" s="40" t="str">
         <f t="shared" ref="BE6:BE9" si="3">_xlfn.CONCAT("""",C6,"""")</f>
         <v>"Região"</v>
       </c>
     </row>
-    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="38">
         <v>7</v>
       </c>
@@ -14843,29 +15601,29 @@
         <v>381</v>
       </c>
       <c r="AY7" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AZ7" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA7" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="BB7" s="32" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BC7" s="40" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="BD7" s="32" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="BE7" s="40" t="str">
         <f t="shared" si="3"/>
         <v>"Estado"</v>
       </c>
     </row>
-    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38">
         <v>8</v>
       </c>
@@ -15009,38 +15767,38 @@
         <v>1</v>
       </c>
       <c r="AV8" s="32" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AW8" s="40" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AX8" s="32" t="s">
         <v>381</v>
       </c>
       <c r="AY8" s="40" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AZ8" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA8" s="40" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="BB8" s="32" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BC8" s="40" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="BD8" s="32" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="BE8" s="40" t="str">
         <f t="shared" si="3"/>
         <v>"Capital"</v>
       </c>
     </row>
-    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="38">
         <v>9</v>
       </c>
@@ -15084,7 +15842,7 @@
         <v>78</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="P9" s="39" t="s">
         <v>1</v>
@@ -15192,29 +15950,29 @@
         <v>381</v>
       </c>
       <c r="AY9" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AZ9" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA9" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="BB9" s="32" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BC9" s="40" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="BD9" s="32" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="BE9" s="40" t="str">
         <f t="shared" si="3"/>
         <v>"UF"</v>
       </c>
     </row>
-    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="38">
         <v>10</v>
       </c>
@@ -15258,7 +16016,7 @@
         <v>78</v>
       </c>
       <c r="O10" s="30" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="P10" s="39" t="s">
         <v>1</v>
@@ -15366,22 +16124,22 @@
         <v>381</v>
       </c>
       <c r="AY10" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AZ10" s="32" t="s">
         <v>223</v>
       </c>
       <c r="BA10" s="40" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="BB10" s="32" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BC10" s="40" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="BD10" s="32" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="BE10" s="40" t="str">
         <f t="shared" ref="BE10" si="5">_xlfn.CONCAT("""",C10,"""")</f>

--- a/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
+++ b/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9526BA7E-4C0D-411A-AA36-350ED3831A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7B604E-2073-430E-9DB4-03238C63CB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="622">
   <si>
     <t>Key</t>
   </si>
@@ -1822,18 +1822,6 @@
     <t>Atributo Ifc</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>Função.Auxiliar</t>
   </si>
   <si>
@@ -1882,9 +1870,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -1907,6 +1892,54 @@
   </si>
   <si>
     <t>[ OST_Areas : OST_Rooms ]</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API Método</t>
+  </si>
+  <si>
+    <t>Função Auxiliar</t>
+  </si>
+  <si>
+    <t>API Plataforma</t>
+  </si>
+  <si>
+    <t>API Macros</t>
+  </si>
+  <si>
+    <t>Função Global</t>
+  </si>
+  <si>
+    <t>Função Local</t>
+  </si>
+  <si>
+    <t>Função Filtro</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>API Método Visual</t>
+  </si>
+  <si>
+    <t>Bloco de Código</t>
+  </si>
+  <si>
+    <t>API Macros Visuais</t>
   </si>
 </sst>
 </file>
@@ -2199,7 +2232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2422,17 +2455,56 @@
     <xf numFmtId="0" fontId="12" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="38">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2747,14 +2819,6 @@
       <font>
         <b val="0"/>
         <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -3278,7 +3342,7 @@
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46268.693379861113</v>
+        <v>46273.675280555559</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>378</v>
@@ -3401,7 +3465,7 @@
     <col min="15" max="15" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="232.7109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="230.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.42578125" style="27" customWidth="1"/>
     <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9.5703125" bestFit="1" customWidth="1"/>
@@ -3503,7 +3567,7 @@
         <v>374</v>
       </c>
       <c r="AD1" s="26" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3567,7 +3631,7 @@
       <c r="R2" s="66" t="s">
         <v>470</v>
       </c>
-      <c r="S2" s="66" t="s">
+      <c r="S2" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T2" s="66" t="str">
@@ -3667,7 +3731,7 @@
       <c r="R3" s="66" t="s">
         <v>471</v>
       </c>
-      <c r="S3" s="66" t="s">
+      <c r="S3" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T3" s="66" t="str">
@@ -3767,7 +3831,7 @@
       <c r="R4" s="66" t="s">
         <v>472</v>
       </c>
-      <c r="S4" s="66" t="s">
+      <c r="S4" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T4" s="66" t="str">
@@ -3868,7 +3932,7 @@
       <c r="R5" s="66" t="s">
         <v>473</v>
       </c>
-      <c r="S5" s="66" t="s">
+      <c r="S5" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T5" s="66" t="str">
@@ -3968,7 +4032,7 @@
       <c r="R6" s="66" t="s">
         <v>474</v>
       </c>
-      <c r="S6" s="66" t="s">
+      <c r="S6" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T6" s="66" t="str">
@@ -4068,7 +4132,7 @@
       <c r="R7" s="66" t="s">
         <v>475</v>
       </c>
-      <c r="S7" s="66" t="s">
+      <c r="S7" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T7" s="66" t="str">
@@ -4168,7 +4232,7 @@
       <c r="R8" s="66" t="s">
         <v>476</v>
       </c>
-      <c r="S8" s="66" t="s">
+      <c r="S8" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T8" s="66" t="str">
@@ -4268,7 +4332,7 @@
       <c r="R9" s="66" t="s">
         <v>477</v>
       </c>
-      <c r="S9" s="66" t="s">
+      <c r="S9" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T9" s="66" t="str">
@@ -4369,7 +4433,7 @@
       <c r="R10" s="66" t="s">
         <v>478</v>
       </c>
-      <c r="S10" s="66" t="s">
+      <c r="S10" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T10" s="66" t="str">
@@ -4469,7 +4533,7 @@
       <c r="R11" s="66" t="s">
         <v>479</v>
       </c>
-      <c r="S11" s="66" t="s">
+      <c r="S11" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T11" s="66" t="str">
@@ -4570,7 +4634,7 @@
       <c r="R12" s="66" t="s">
         <v>480</v>
       </c>
-      <c r="S12" s="66" t="s">
+      <c r="S12" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T12" s="66" t="str">
@@ -4671,7 +4735,7 @@
       <c r="R13" s="66" t="s">
         <v>481</v>
       </c>
-      <c r="S13" s="66" t="s">
+      <c r="S13" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T13" s="66" t="str">
@@ -4772,7 +4836,7 @@
       <c r="R14" s="66" t="s">
         <v>482</v>
       </c>
-      <c r="S14" s="66" t="s">
+      <c r="S14" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T14" s="66" t="str">
@@ -4873,7 +4937,7 @@
       <c r="R15" s="66" t="s">
         <v>483</v>
       </c>
-      <c r="S15" s="66" t="s">
+      <c r="S15" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T15" s="66" t="str">
@@ -4974,7 +5038,7 @@
       <c r="R16" s="66" t="s">
         <v>484</v>
       </c>
-      <c r="S16" s="66" t="s">
+      <c r="S16" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T16" s="66" t="str">
@@ -5075,7 +5139,7 @@
       <c r="R17" s="66" t="s">
         <v>485</v>
       </c>
-      <c r="S17" s="66" t="s">
+      <c r="S17" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T17" s="66" t="str">
@@ -5176,7 +5240,7 @@
       <c r="R18" s="66" t="s">
         <v>486</v>
       </c>
-      <c r="S18" s="66" t="s">
+      <c r="S18" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T18" s="66" t="str">
@@ -5277,7 +5341,7 @@
       <c r="R19" s="66" t="s">
         <v>487</v>
       </c>
-      <c r="S19" s="66" t="s">
+      <c r="S19" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T19" s="66" t="str">
@@ -5378,7 +5442,7 @@
       <c r="R20" s="66" t="s">
         <v>488</v>
       </c>
-      <c r="S20" s="66" t="s">
+      <c r="S20" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T20" s="66" t="str">
@@ -5479,7 +5543,7 @@
       <c r="R21" s="66" t="s">
         <v>489</v>
       </c>
-      <c r="S21" s="66" t="s">
+      <c r="S21" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T21" s="66" t="str">
@@ -5580,7 +5644,7 @@
       <c r="R22" s="66" t="s">
         <v>490</v>
       </c>
-      <c r="S22" s="66" t="s">
+      <c r="S22" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T22" s="66" t="str">
@@ -5681,7 +5745,7 @@
       <c r="R23" s="66" t="s">
         <v>491</v>
       </c>
-      <c r="S23" s="66" t="s">
+      <c r="S23" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T23" s="66" t="str">
@@ -5782,7 +5846,7 @@
       <c r="R24" s="66" t="s">
         <v>492</v>
       </c>
-      <c r="S24" s="66" t="s">
+      <c r="S24" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T24" s="66" t="str">
@@ -5883,7 +5947,7 @@
       <c r="R25" s="66" t="s">
         <v>493</v>
       </c>
-      <c r="S25" s="66" t="s">
+      <c r="S25" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T25" s="66" t="str">
@@ -5984,7 +6048,7 @@
       <c r="R26" s="66" t="s">
         <v>494</v>
       </c>
-      <c r="S26" s="66" t="s">
+      <c r="S26" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T26" s="66" t="str">
@@ -6085,7 +6149,7 @@
       <c r="R27" s="66" t="s">
         <v>495</v>
       </c>
-      <c r="S27" s="66" t="s">
+      <c r="S27" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T27" s="66" t="str">
@@ -6186,7 +6250,7 @@
       <c r="R28" s="66" t="s">
         <v>496</v>
       </c>
-      <c r="S28" s="66" t="s">
+      <c r="S28" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T28" s="66" t="str">
@@ -6287,7 +6351,7 @@
       <c r="R29" s="66" t="s">
         <v>497</v>
       </c>
-      <c r="S29" s="66" t="s">
+      <c r="S29" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T29" s="66" t="str">
@@ -6387,7 +6451,7 @@
       <c r="R30" s="66" t="s">
         <v>498</v>
       </c>
-      <c r="S30" s="66" t="s">
+      <c r="S30" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T30" s="66" t="str">
@@ -6487,7 +6551,7 @@
       <c r="R31" s="66" t="s">
         <v>499</v>
       </c>
-      <c r="S31" s="66" t="s">
+      <c r="S31" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T31" s="66" t="str">
@@ -6587,7 +6651,7 @@
       <c r="R32" s="66" t="s">
         <v>500</v>
       </c>
-      <c r="S32" s="66" t="s">
+      <c r="S32" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T32" s="66" t="str">
@@ -6687,7 +6751,7 @@
       <c r="R33" s="66" t="s">
         <v>501</v>
       </c>
-      <c r="S33" s="66" t="s">
+      <c r="S33" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T33" s="66" t="str">
@@ -6787,7 +6851,7 @@
       <c r="R34" s="66" t="s">
         <v>502</v>
       </c>
-      <c r="S34" s="66" t="s">
+      <c r="S34" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T34" s="66" t="str">
@@ -6887,7 +6951,7 @@
       <c r="R35" s="66" t="s">
         <v>503</v>
       </c>
-      <c r="S35" s="66" t="s">
+      <c r="S35" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T35" s="66" t="str">
@@ -6987,7 +7051,7 @@
       <c r="R36" s="66" t="s">
         <v>504</v>
       </c>
-      <c r="S36" s="66" t="s">
+      <c r="S36" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T36" s="66" t="str">
@@ -7087,7 +7151,7 @@
       <c r="R37" s="66" t="s">
         <v>505</v>
       </c>
-      <c r="S37" s="66" t="s">
+      <c r="S37" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T37" s="66" t="str">
@@ -7187,7 +7251,7 @@
       <c r="R38" s="66" t="s">
         <v>506</v>
       </c>
-      <c r="S38" s="66" t="s">
+      <c r="S38" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T38" s="66" t="str">
@@ -7287,7 +7351,7 @@
       <c r="R39" s="66" t="s">
         <v>507</v>
       </c>
-      <c r="S39" s="66" t="s">
+      <c r="S39" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T39" s="66" t="str">
@@ -7387,7 +7451,7 @@
       <c r="R40" s="66" t="s">
         <v>508</v>
       </c>
-      <c r="S40" s="66" t="s">
+      <c r="S40" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T40" s="66" t="str">
@@ -7487,7 +7551,7 @@
       <c r="R41" s="66" t="s">
         <v>509</v>
       </c>
-      <c r="S41" s="66" t="s">
+      <c r="S41" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T41" s="66" t="str">
@@ -7587,7 +7651,7 @@
       <c r="R42" s="66" t="s">
         <v>510</v>
       </c>
-      <c r="S42" s="66" t="s">
+      <c r="S42" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T42" s="66" t="str">
@@ -7687,7 +7751,7 @@
       <c r="R43" s="66" t="s">
         <v>511</v>
       </c>
-      <c r="S43" s="66" t="s">
+      <c r="S43" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T43" s="66" t="str">
@@ -7787,7 +7851,7 @@
       <c r="R44" s="66" t="s">
         <v>512</v>
       </c>
-      <c r="S44" s="66" t="s">
+      <c r="S44" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T44" s="66" t="str">
@@ -7887,7 +7951,7 @@
       <c r="R45" s="66" t="s">
         <v>513</v>
       </c>
-      <c r="S45" s="66" t="s">
+      <c r="S45" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T45" s="66" t="str">
@@ -7987,7 +8051,7 @@
       <c r="R46" s="66" t="s">
         <v>514</v>
       </c>
-      <c r="S46" s="66" t="s">
+      <c r="S46" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T46" s="66" t="str">
@@ -8087,7 +8151,7 @@
       <c r="R47" s="66" t="s">
         <v>515</v>
       </c>
-      <c r="S47" s="66" t="s">
+      <c r="S47" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T47" s="66" t="str">
@@ -8187,7 +8251,7 @@
       <c r="R48" s="66" t="s">
         <v>516</v>
       </c>
-      <c r="S48" s="66" t="s">
+      <c r="S48" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T48" s="66" t="str">
@@ -8287,7 +8351,7 @@
       <c r="R49" s="66" t="s">
         <v>517</v>
       </c>
-      <c r="S49" s="66" t="s">
+      <c r="S49" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T49" s="66" t="str">
@@ -8387,7 +8451,7 @@
       <c r="R50" s="66" t="s">
         <v>518</v>
       </c>
-      <c r="S50" s="66" t="s">
+      <c r="S50" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T50" s="66" t="str">
@@ -8410,7 +8474,7 @@
         <v>Key-BRASIL-SP-50</v>
       </c>
       <c r="Y50" s="66" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="Z50" s="75" t="s">
         <v>1</v>
@@ -8487,7 +8551,7 @@
       <c r="R51" s="66" t="s">
         <v>519</v>
       </c>
-      <c r="S51" s="66" t="s">
+      <c r="S51" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T51" s="66" t="str">
@@ -8510,7 +8574,7 @@
         <v>Key-BRASIL-SP-51</v>
       </c>
       <c r="Y51" s="66" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="Z51" s="75" t="s">
         <v>1</v>
@@ -8587,7 +8651,7 @@
       <c r="R52" s="66" t="s">
         <v>520</v>
       </c>
-      <c r="S52" s="66" t="s">
+      <c r="S52" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T52" s="66" t="str">
@@ -8610,7 +8674,7 @@
         <v>Key-BRASIL-SP-52</v>
       </c>
       <c r="Y52" s="66" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="Z52" s="75" t="s">
         <v>1</v>
@@ -8687,7 +8751,7 @@
       <c r="R53" s="66" t="s">
         <v>521</v>
       </c>
-      <c r="S53" s="66" t="s">
+      <c r="S53" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T53" s="66" t="str">
@@ -8710,7 +8774,7 @@
         <v>Key-BRASIL-SP-53</v>
       </c>
       <c r="Y53" s="66" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="Z53" s="75" t="s">
         <v>1</v>
@@ -8787,7 +8851,7 @@
       <c r="R54" s="66" t="s">
         <v>522</v>
       </c>
-      <c r="S54" s="66" t="s">
+      <c r="S54" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T54" s="66" t="str">
@@ -8890,7 +8954,7 @@
       <c r="R55" s="66" t="s">
         <v>523</v>
       </c>
-      <c r="S55" s="66" t="s">
+      <c r="S55" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T55" s="66" t="str">
@@ -8992,7 +9056,7 @@
       <c r="R56" s="66" t="s">
         <v>524</v>
       </c>
-      <c r="S56" s="66" t="s">
+      <c r="S56" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T56" s="66" t="str">
@@ -9092,7 +9156,7 @@
       <c r="R57" s="66" t="s">
         <v>525</v>
       </c>
-      <c r="S57" s="66" t="s">
+      <c r="S57" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T57" s="66" t="str">
@@ -9192,7 +9256,7 @@
       <c r="R58" s="66" t="s">
         <v>526</v>
       </c>
-      <c r="S58" s="66" t="s">
+      <c r="S58" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T58" s="66" t="str">
@@ -9292,7 +9356,7 @@
       <c r="R59" s="66" t="s">
         <v>527</v>
       </c>
-      <c r="S59" s="66" t="s">
+      <c r="S59" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T59" s="66" t="str">
@@ -9392,7 +9456,7 @@
       <c r="R60" s="66" t="s">
         <v>528</v>
       </c>
-      <c r="S60" s="66" t="s">
+      <c r="S60" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T60" s="66" t="str">
@@ -9492,7 +9556,7 @@
       <c r="R61" s="66" t="s">
         <v>529</v>
       </c>
-      <c r="S61" s="66" t="s">
+      <c r="S61" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T61" s="66" t="str">
@@ -9592,7 +9656,7 @@
       <c r="R62" s="66" t="s">
         <v>528</v>
       </c>
-      <c r="S62" s="66" t="s">
+      <c r="S62" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T62" s="66" t="str">
@@ -9692,7 +9756,7 @@
       <c r="R63" s="66" t="s">
         <v>530</v>
       </c>
-      <c r="S63" s="66" t="s">
+      <c r="S63" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T63" s="66" t="str">
@@ -9792,7 +9856,7 @@
       <c r="R64" s="66" t="s">
         <v>531</v>
       </c>
-      <c r="S64" s="66" t="s">
+      <c r="S64" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T64" s="66" t="str">
@@ -9892,7 +9956,7 @@
       <c r="R65" s="66" t="s">
         <v>532</v>
       </c>
-      <c r="S65" s="66" t="s">
+      <c r="S65" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T65" s="66" t="str">
@@ -9915,7 +9979,7 @@
         <v>Key-BRASIL-SP-65</v>
       </c>
       <c r="Y65" s="66" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="Z65" s="75" t="s">
         <v>1</v>
@@ -9992,7 +10056,7 @@
       <c r="R66" s="66" t="s">
         <v>533</v>
       </c>
-      <c r="S66" s="66" t="s">
+      <c r="S66" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T66" s="66" t="str">
@@ -10015,7 +10079,7 @@
         <v>Key-BRASIL-SP-66</v>
       </c>
       <c r="Y66" s="66" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="Z66" s="75" t="s">
         <v>1</v>
@@ -10092,7 +10156,7 @@
       <c r="R67" s="66" t="s">
         <v>534</v>
       </c>
-      <c r="S67" s="66" t="s">
+      <c r="S67" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T67" s="66" t="str">
@@ -10115,7 +10179,7 @@
         <v>Key-BRASIL-SP-67</v>
       </c>
       <c r="Y67" s="66" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="Z67" s="75" t="s">
         <v>1</v>
@@ -10193,7 +10257,7 @@
       <c r="R68" s="66" t="s">
         <v>535</v>
       </c>
-      <c r="S68" s="66" t="s">
+      <c r="S68" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T68" s="66" t="str">
@@ -10294,7 +10358,7 @@
       <c r="R69" s="66" t="s">
         <v>536</v>
       </c>
-      <c r="S69" s="66" t="s">
+      <c r="S69" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T69" s="66" t="str">
@@ -10395,7 +10459,7 @@
       <c r="R70" s="66" t="s">
         <v>535</v>
       </c>
-      <c r="S70" s="66" t="s">
+      <c r="S70" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T70" s="66" t="str">
@@ -10496,7 +10560,7 @@
       <c r="R71" s="66" t="s">
         <v>537</v>
       </c>
-      <c r="S71" s="66" t="s">
+      <c r="S71" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T71" s="66" t="str">
@@ -10597,7 +10661,7 @@
       <c r="R72" s="66" t="s">
         <v>538</v>
       </c>
-      <c r="S72" s="66" t="s">
+      <c r="S72" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T72" s="66" t="str">
@@ -10697,7 +10761,7 @@
       <c r="R73" s="66" t="s">
         <v>539</v>
       </c>
-      <c r="S73" s="66" t="s">
+      <c r="S73" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T73" s="66" t="str">
@@ -10797,7 +10861,7 @@
       <c r="R74" s="66" t="s">
         <v>540</v>
       </c>
-      <c r="S74" s="66" t="s">
+      <c r="S74" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T74" s="66" t="str">
@@ -10898,7 +10962,7 @@
       <c r="R75" s="66" t="s">
         <v>541</v>
       </c>
-      <c r="S75" s="66" t="s">
+      <c r="S75" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T75" s="66" t="str">
@@ -10998,7 +11062,7 @@
       <c r="R76" s="66" t="s">
         <v>542</v>
       </c>
-      <c r="S76" s="66" t="s">
+      <c r="S76" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T76" s="66" t="str">
@@ -11021,7 +11085,7 @@
         <v>Key-BRASIL-SP-76</v>
       </c>
       <c r="Y76" s="66" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="Z76" s="75" t="s">
         <v>1</v>
@@ -11098,7 +11162,7 @@
       <c r="R77" s="66" t="s">
         <v>543</v>
       </c>
-      <c r="S77" s="66" t="s">
+      <c r="S77" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T77" s="66" t="str">
@@ -11121,7 +11185,7 @@
         <v>Key-BRASIL-SP-77</v>
       </c>
       <c r="Y77" s="66" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="Z77" s="75" t="s">
         <v>1</v>
@@ -11198,7 +11262,7 @@
       <c r="R78" s="66" t="s">
         <v>544</v>
       </c>
-      <c r="S78" s="66" t="s">
+      <c r="S78" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T78" s="66" t="str">
@@ -11221,7 +11285,7 @@
         <v>Key-BRASIL-SP-78</v>
       </c>
       <c r="Y78" s="66" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="Z78" s="75" t="s">
         <v>1</v>
@@ -11298,7 +11362,7 @@
       <c r="R79" s="66" t="s">
         <v>545</v>
       </c>
-      <c r="S79" s="66" t="s">
+      <c r="S79" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T79" s="66" t="str">
@@ -11398,7 +11462,7 @@
       <c r="R80" s="66" t="s">
         <v>546</v>
       </c>
-      <c r="S80" s="66" t="s">
+      <c r="S80" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T80" s="66" t="str">
@@ -11421,7 +11485,7 @@
         <v>Key-BRASIL-SP-80</v>
       </c>
       <c r="Y80" s="66" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="Z80" s="75" t="s">
         <v>1</v>
@@ -11498,7 +11562,7 @@
       <c r="R81" s="66" t="s">
         <v>547</v>
       </c>
-      <c r="S81" s="66" t="s">
+      <c r="S81" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T81" s="66" t="str">
@@ -11521,7 +11585,7 @@
         <v>Key-BRASIL-SP-81</v>
       </c>
       <c r="Y81" s="66" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="Z81" s="75" t="s">
         <v>1</v>
@@ -11598,7 +11662,7 @@
       <c r="R82" s="66" t="s">
         <v>548</v>
       </c>
-      <c r="S82" s="66" t="s">
+      <c r="S82" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T82" s="66" t="str">
@@ -11698,7 +11762,7 @@
       <c r="R83" s="66" t="s">
         <v>549</v>
       </c>
-      <c r="S83" s="66" t="s">
+      <c r="S83" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T83" s="66" t="str">
@@ -11798,7 +11862,7 @@
       <c r="R84" s="66" t="s">
         <v>550</v>
       </c>
-      <c r="S84" s="66" t="s">
+      <c r="S84" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T84" s="66" t="str">
@@ -11898,7 +11962,7 @@
       <c r="R85" s="66" t="s">
         <v>551</v>
       </c>
-      <c r="S85" s="66" t="s">
+      <c r="S85" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T85" s="66" t="str">
@@ -11998,7 +12062,7 @@
       <c r="R86" s="66" t="s">
         <v>552</v>
       </c>
-      <c r="S86" s="66" t="s">
+      <c r="S86" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T86" s="66" t="str">
@@ -12098,7 +12162,7 @@
       <c r="R87" s="66" t="s">
         <v>553</v>
       </c>
-      <c r="S87" s="66" t="s">
+      <c r="S87" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T87" s="66" t="str">
@@ -12198,7 +12262,7 @@
       <c r="R88" s="66" t="s">
         <v>554</v>
       </c>
-      <c r="S88" s="66" t="s">
+      <c r="S88" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T88" s="66" t="str">
@@ -12298,7 +12362,7 @@
       <c r="R89" s="66" t="s">
         <v>555</v>
       </c>
-      <c r="S89" s="66" t="s">
+      <c r="S89" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T89" s="66" t="str">
@@ -12398,7 +12462,7 @@
       <c r="R90" s="66" t="s">
         <v>556</v>
       </c>
-      <c r="S90" s="66" t="s">
+      <c r="S90" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T90" s="66" t="str">
@@ -12498,7 +12562,7 @@
       <c r="R91" s="66" t="s">
         <v>557</v>
       </c>
-      <c r="S91" s="66" t="s">
+      <c r="S91" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T91" s="66" t="str">
@@ -12598,7 +12662,7 @@
       <c r="R92" s="66" t="s">
         <v>558</v>
       </c>
-      <c r="S92" s="66" t="s">
+      <c r="S92" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T92" s="66" t="str">
@@ -12698,7 +12762,7 @@
       <c r="R93" s="66" t="s">
         <v>559</v>
       </c>
-      <c r="S93" s="66" t="s">
+      <c r="S93" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T93" s="66" t="str">
@@ -12798,7 +12862,7 @@
       <c r="R94" s="66" t="s">
         <v>560</v>
       </c>
-      <c r="S94" s="66" t="s">
+      <c r="S94" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T94" s="66" t="str">
@@ -12898,7 +12962,7 @@
       <c r="R95" s="66" t="s">
         <v>561</v>
       </c>
-      <c r="S95" s="66" t="s">
+      <c r="S95" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T95" s="66" t="str">
@@ -12998,7 +13062,7 @@
       <c r="R96" s="66" t="s">
         <v>562</v>
       </c>
-      <c r="S96" s="66" t="s">
+      <c r="S96" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T96" s="66" t="str">
@@ -13098,7 +13162,7 @@
       <c r="R97" s="66" t="s">
         <v>562</v>
       </c>
-      <c r="S97" s="66" t="s">
+      <c r="S97" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T97" s="66" t="str">
@@ -13198,7 +13262,7 @@
       <c r="R98" s="66" t="s">
         <v>563</v>
       </c>
-      <c r="S98" s="66" t="s">
+      <c r="S98" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T98" s="66" t="str">
@@ -13298,7 +13362,7 @@
       <c r="R99" s="66" t="s">
         <v>564</v>
       </c>
-      <c r="S99" s="66" t="s">
+      <c r="S99" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T99" s="66" t="str">
@@ -13398,7 +13462,7 @@
       <c r="R100" s="66" t="s">
         <v>565</v>
       </c>
-      <c r="S100" s="66" t="s">
+      <c r="S100" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T100" s="66" t="str">
@@ -13439,85 +13503,78 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:30" s="78" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="62">
         <v>101</v>
       </c>
-      <c r="B101" s="77" t="s">
+      <c r="B101" s="76" t="s">
+        <v>606</v>
+      </c>
+      <c r="C101" s="37" t="s">
+        <v>607</v>
+      </c>
+      <c r="D101" s="37" t="s">
+        <v>608</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>609</v>
+      </c>
+      <c r="F101" s="37" t="s">
         <v>582</v>
       </c>
-      <c r="C101" s="37" t="s">
+      <c r="G101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="I101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="J101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="L101" s="73" t="s">
+        <v>607</v>
+      </c>
+      <c r="M101" s="73" t="s">
+        <v>608</v>
+      </c>
+      <c r="N101" s="73" t="s">
+        <v>610</v>
+      </c>
+      <c r="O101" s="73" t="s">
+        <v>611</v>
+      </c>
+      <c r="P101" s="74" t="s">
         <v>583</v>
       </c>
-      <c r="D101" s="37" t="s">
+      <c r="Q101" s="74" t="s">
+        <v>584</v>
+      </c>
+      <c r="R101" s="74" t="s">
         <v>585</v>
       </c>
-      <c r="E101" s="37" t="s">
-        <v>584</v>
-      </c>
-      <c r="F101" s="37" t="s">
-        <v>586</v>
-      </c>
-      <c r="G101" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="H101" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="I101" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="J101" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="K101" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="L101" s="73" t="str">
-        <f t="shared" ref="L101:O105" si="16">SUBSTITUTE(CONCATENATE("", C101), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M101" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Macros</v>
-      </c>
-      <c r="N101" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O101" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P101" s="74" t="s">
-        <v>587</v>
-      </c>
-      <c r="Q101" s="74" t="s">
-        <v>588</v>
-      </c>
-      <c r="R101" s="74" t="s">
-        <v>589</v>
-      </c>
-      <c r="S101" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="T101" s="74" t="str">
-        <f t="shared" ref="T101:V105" si="17">SUBSTITUTE(C101, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U101" s="74" t="str">
-        <f t="shared" si="17"/>
-        <v>Macros</v>
-      </c>
-      <c r="V101" s="66" t="str">
-        <f t="shared" si="17"/>
-        <v>Métodos</v>
+      <c r="S101" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="T101" s="74" t="s">
+        <v>612</v>
+      </c>
+      <c r="U101" s="74" t="s">
+        <v>613</v>
+      </c>
+      <c r="V101" s="66" t="s">
+        <v>610</v>
       </c>
       <c r="W101" s="66" t="s">
         <v>435</v>
       </c>
       <c r="X101" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="X101:X105" si="16">CONCATENATE("Key-BRASIL-SP-",A101)</f>
         <v>Key-BRASIL-SP-101</v>
       </c>
       <c r="Y101" s="75" t="s">
@@ -13539,24 +13596,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:30" s="78" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="62">
         <v>102</v>
       </c>
-      <c r="B102" s="77" t="s">
-        <v>582</v>
+      <c r="B102" s="76" t="s">
+        <v>606</v>
       </c>
       <c r="C102" s="37" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D102" s="37" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="E102" s="37" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G102" s="72" t="s">
         <v>1</v>
@@ -13573,51 +13630,44 @@
       <c r="K102" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="L102" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>De API</v>
-      </c>
-      <c r="M102" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Macros</v>
-      </c>
-      <c r="N102" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O102" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Função Global</v>
+      <c r="L102" s="73" t="s">
+        <v>607</v>
+      </c>
+      <c r="M102" s="73" t="s">
+        <v>608</v>
+      </c>
+      <c r="N102" s="73" t="s">
+        <v>610</v>
+      </c>
+      <c r="O102" s="73" t="s">
+        <v>614</v>
       </c>
       <c r="P102" s="74" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="Q102" s="74" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="R102" s="74" t="s">
-        <v>593</v>
-      </c>
-      <c r="S102" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="T102" s="74" t="str">
-        <f t="shared" si="17"/>
-        <v>De API</v>
-      </c>
-      <c r="U102" s="74" t="str">
-        <f t="shared" si="17"/>
-        <v>Macros</v>
-      </c>
-      <c r="V102" s="66" t="str">
-        <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>589</v>
+      </c>
+      <c r="S102" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="T102" s="74" t="s">
+        <v>612</v>
+      </c>
+      <c r="U102" s="74" t="s">
+        <v>613</v>
+      </c>
+      <c r="V102" s="66" t="s">
+        <v>610</v>
       </c>
       <c r="W102" s="66" t="s">
         <v>435</v>
       </c>
       <c r="X102" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>Key-BRASIL-SP-102</v>
       </c>
       <c r="Y102" s="75" t="s">
@@ -13639,24 +13689,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:30" s="78" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="62">
         <v>103</v>
       </c>
-      <c r="B103" s="77" t="s">
-        <v>582</v>
+      <c r="B103" s="76" t="s">
+        <v>606</v>
       </c>
       <c r="C103" s="37" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D103" s="37" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="E103" s="37" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="F103" s="37" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="G103" s="72" t="s">
         <v>1</v>
@@ -13673,51 +13723,44 @@
       <c r="K103" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="L103" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>De API</v>
-      </c>
-      <c r="M103" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Macros</v>
-      </c>
-      <c r="N103" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O103" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Função Local</v>
+      <c r="L103" s="73" t="s">
+        <v>607</v>
+      </c>
+      <c r="M103" s="73" t="s">
+        <v>608</v>
+      </c>
+      <c r="N103" s="73" t="s">
+        <v>610</v>
+      </c>
+      <c r="O103" s="73" t="s">
+        <v>615</v>
       </c>
       <c r="P103" s="74" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="Q103" s="74" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="R103" s="74" t="s">
-        <v>597</v>
-      </c>
-      <c r="S103" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="T103" s="74" t="str">
-        <f t="shared" si="17"/>
-        <v>De API</v>
-      </c>
-      <c r="U103" s="74" t="str">
-        <f t="shared" si="17"/>
-        <v>Macros</v>
-      </c>
-      <c r="V103" s="66" t="str">
-        <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>593</v>
+      </c>
+      <c r="S103" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="T103" s="74" t="s">
+        <v>612</v>
+      </c>
+      <c r="U103" s="74" t="s">
+        <v>613</v>
+      </c>
+      <c r="V103" s="66" t="s">
+        <v>610</v>
       </c>
       <c r="W103" s="66" t="s">
         <v>435</v>
       </c>
       <c r="X103" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>Key-BRASIL-SP-103</v>
       </c>
       <c r="Y103" s="75" t="s">
@@ -13739,24 +13782,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:30" s="78" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="62">
         <v>104</v>
       </c>
-      <c r="B104" s="77" t="s">
-        <v>582</v>
+      <c r="B104" s="76" t="s">
+        <v>606</v>
       </c>
       <c r="C104" s="37" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D104" s="37" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="E104" s="37" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="F104" s="37" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="G104" s="72" t="s">
         <v>1</v>
@@ -13773,51 +13816,44 @@
       <c r="K104" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="L104" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>De API</v>
-      </c>
-      <c r="M104" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Macros</v>
-      </c>
-      <c r="N104" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O104" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Função Filtro</v>
+      <c r="L104" s="73" t="s">
+        <v>607</v>
+      </c>
+      <c r="M104" s="73" t="s">
+        <v>608</v>
+      </c>
+      <c r="N104" s="73" t="s">
+        <v>610</v>
+      </c>
+      <c r="O104" s="73" t="s">
+        <v>616</v>
       </c>
       <c r="P104" s="74" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="Q104" s="74" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="R104" s="74" t="s">
-        <v>601</v>
-      </c>
-      <c r="S104" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="T104" s="74" t="str">
-        <f t="shared" si="17"/>
-        <v>De API</v>
-      </c>
-      <c r="U104" s="74" t="str">
-        <f t="shared" si="17"/>
-        <v>Macros</v>
-      </c>
-      <c r="V104" s="66" t="str">
-        <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>597</v>
+      </c>
+      <c r="S104" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="T104" s="74" t="s">
+        <v>612</v>
+      </c>
+      <c r="U104" s="74" t="s">
+        <v>613</v>
+      </c>
+      <c r="V104" s="66" t="s">
+        <v>610</v>
       </c>
       <c r="W104" s="66" t="s">
         <v>435</v>
       </c>
       <c r="X104" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>Key-BRASIL-SP-104</v>
       </c>
       <c r="Y104" s="75" t="s">
@@ -13839,24 +13875,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:30" s="78" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="62">
         <v>105</v>
       </c>
-      <c r="B105" s="77" t="s">
-        <v>582</v>
+      <c r="B105" s="76" t="s">
+        <v>606</v>
       </c>
       <c r="C105" s="37" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D105" s="37" t="s">
-        <v>585</v>
+        <v>617</v>
       </c>
       <c r="E105" s="37" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="F105" s="37" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="G105" s="72" t="s">
         <v>1</v>
@@ -13873,51 +13909,44 @@
       <c r="K105" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="L105" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>De API</v>
-      </c>
-      <c r="M105" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Macros</v>
-      </c>
-      <c r="N105" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O105" s="73" t="str">
-        <f t="shared" si="16"/>
-        <v>Bloco de Código</v>
+      <c r="L105" s="73" t="s">
+        <v>607</v>
+      </c>
+      <c r="M105" s="73" t="s">
+        <v>617</v>
+      </c>
+      <c r="N105" s="73" t="s">
+        <v>619</v>
+      </c>
+      <c r="O105" s="73" t="s">
+        <v>620</v>
       </c>
       <c r="P105" s="74" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="Q105" s="74" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="R105" s="74" t="s">
-        <v>606</v>
-      </c>
-      <c r="S105" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="T105" s="74" t="str">
-        <f t="shared" si="17"/>
-        <v>De API</v>
-      </c>
-      <c r="U105" s="74" t="str">
-        <f t="shared" si="17"/>
-        <v>Macros</v>
-      </c>
-      <c r="V105" s="66" t="str">
-        <f t="shared" si="17"/>
-        <v>Códigos Visuais</v>
+        <v>601</v>
+      </c>
+      <c r="S105" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="T105" s="74" t="s">
+        <v>612</v>
+      </c>
+      <c r="U105" s="74" t="s">
+        <v>621</v>
+      </c>
+      <c r="V105" s="66" t="s">
+        <v>619</v>
       </c>
       <c r="W105" s="66" t="s">
         <v>435</v>
       </c>
       <c r="X105" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>Key-BRASIL-SP-105</v>
       </c>
       <c r="Y105" s="75" t="s">
@@ -13941,84 +13970,82 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B105">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B100 A101:A105">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:D100 L41:Q100 T41:V100 AE41:XFD100 AE106:XFD1048576">
-    <cfRule type="cellIs" dxfId="33" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E105:F105">
-    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F1 F106:F1048576 A1:D1 T1:X1 A106:D1048576 T106:X1048576">
-    <cfRule type="cellIs" dxfId="31" priority="464" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="467" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="30" priority="1502"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="1505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AE1:XFD29 T2:V28 L7:O9 Q7:Q9 L10:Q29 T29:U29 V29:V40 O30:O40">
-    <cfRule type="cellIs" dxfId="29" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F93 F96:F100">
-    <cfRule type="duplicateValues" dxfId="28" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="26" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F40">
-    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F40">
+    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
     <cfRule type="duplicateValues" dxfId="23" priority="27"/>
     <cfRule type="duplicateValues" dxfId="22" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
-    <cfRule type="duplicateValues" dxfId="19" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F100 F2:F93">
-    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F101:F104">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="14" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="981"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="984"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="988"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="992"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="996"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1000"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="987"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="999"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L106:R1048576">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R100">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W105">
-    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F101:F105">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -14233,7 +14260,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14338,7 +14365,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A6">
-    <cfRule type="cellIs" dxfId="2" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16150,12 +16177,12 @@
   <autoFilter ref="F1:F10" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1048576 D1:F1048576 H1:XFD1048576 G2 G4:G5 G7 G9">
-    <cfRule type="cellIs" dxfId="1" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="37" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="36"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
+++ b/Versão5/BRASIL/Ontologia_Brasil_SP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7B604E-2073-430E-9DB4-03238C63CB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D9320A-E28D-470F-9D31-5D265EFBA330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="668">
   <si>
     <t>Key</t>
   </si>
@@ -194,12 +194,6 @@
     <t>Autor</t>
   </si>
   <si>
-    <t>Edição</t>
-  </si>
-  <si>
-    <t>ISBN</t>
-  </si>
-  <si>
     <t>Observações</t>
   </si>
   <si>
@@ -219,21 +213,6 @@
   </si>
   <si>
     <t>Escola Politécnica da UFRJ</t>
-  </si>
-  <si>
-    <t>NormaNúmero</t>
-  </si>
-  <si>
-    <t>NormaEscopo</t>
-  </si>
-  <si>
-    <t>NormaReferência1</t>
-  </si>
-  <si>
-    <t>NormaReferência2</t>
-  </si>
-  <si>
-    <t>NormaReferência3</t>
   </si>
   <si>
     <t>DataHora</t>
@@ -1940,13 +1919,172 @@
   </si>
   <si>
     <t>API Macros Visuais</t>
+  </si>
+  <si>
+    <t>Norma-Número</t>
+  </si>
+  <si>
+    <t>Norma-Edição</t>
+  </si>
+  <si>
+    <t>Norma-ISBN</t>
+  </si>
+  <si>
+    <t>Norma-Escopo</t>
+  </si>
+  <si>
+    <t>Norma-Referência-01</t>
+  </si>
+  <si>
+    <t>Norma-Referência-02</t>
+  </si>
+  <si>
+    <t>Norma-Referência-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-01</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-02</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-03</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-05</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-06</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-07</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-08</t>
+  </si>
+  <si>
+    <t>Fonte-SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-01</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-02</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-03</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-05</t>
+  </si>
+  <si>
+    <t>Fonte-Bombeiros-01</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>https://anvisalegis.datalegis.net</t>
+  </si>
+  <si>
+    <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
+  </si>
+  <si>
+    <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
+  </si>
+  <si>
+    <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
+  </si>
+  <si>
+    <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
+  </si>
+  <si>
+    <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
+  </si>
+  <si>
+    <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
+  </si>
+  <si>
+    <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
+  </si>
+  <si>
+    <t>Segurança contra incêndio. Varia por estado, consultar regulamento local.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2046,8 +2184,16 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2180,6 +2326,18 @@
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEAAAA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -2229,10 +2387,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2464,47 +2623,39 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="35">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2783,13 +2934,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2819,6 +2963,21 @@
       <font>
         <b val="0"/>
         <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -3138,61 +3297,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.5703125" style="6" customWidth="1"/>
     <col min="3" max="3" width="3.42578125" style="53" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="3.28515625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="79" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="C4" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B5" s="8" t="str">
@@ -3200,11 +3359,11 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>39</v>
       </c>
       <c r="B6" s="8" t="str">
@@ -3212,234 +3371,496 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>41</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>49</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>51</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>615</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>42</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>616</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>43</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>617</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>52</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>618</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>53</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>619</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>54</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>620</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>55</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>621</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>44</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>56</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46273.675280555559</v>
+        <v>46276.420959606483</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>384</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>377</v>
       </c>
       <c r="B20" s="54" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>385</v>
+        <v>372</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>378</v>
       </c>
       <c r="B21" s="54" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>57</v>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>58</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>376</v>
+        <v>372</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>369</v>
       </c>
       <c r="B26" s="12" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize concepts of elements of Urbanism of Cities in Brazil RJ.</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>380</v>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B27" s="80" t="s">
+        <v>645</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="B28" s="81" t="s">
+        <v>646</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="B29" s="81" t="s">
+        <v>647</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="B30" s="82" t="s">
+        <v>648</v>
+      </c>
+      <c r="C30" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="B31" s="83" t="s">
+        <v>649</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="B32" s="83" t="s">
+        <v>650</v>
+      </c>
+      <c r="C32" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="B33" s="83" t="s">
+        <v>651</v>
+      </c>
+      <c r="C33" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="B34" s="84" t="s">
+        <v>652</v>
+      </c>
+      <c r="C34" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="B35" s="84" t="s">
+        <v>653</v>
+      </c>
+      <c r="C35" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B36" s="83" t="s">
+        <v>654</v>
+      </c>
+      <c r="C36" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="B37" s="84" t="s">
+        <v>655</v>
+      </c>
+      <c r="C37" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="B38" s="83" t="s">
+        <v>656</v>
+      </c>
+      <c r="C38" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="B39" s="85" t="s">
+        <v>657</v>
+      </c>
+      <c r="C39" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="B40" s="85" t="s">
+        <v>658</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="B41" s="86" t="s">
+        <v>659</v>
+      </c>
+      <c r="C41" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="B42" s="87" t="s">
+        <v>660</v>
+      </c>
+      <c r="C42" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="B43" s="87" t="s">
+        <v>661</v>
+      </c>
+      <c r="C43" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="B44" s="87" t="s">
+        <v>662</v>
+      </c>
+      <c r="C44" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="B45" s="87" t="s">
+        <v>663</v>
+      </c>
+      <c r="C45" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="B46" s="87" t="s">
+        <v>664</v>
+      </c>
+      <c r="C46" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="B47" s="87" t="s">
+        <v>665</v>
+      </c>
+      <c r="C47" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B48" s="87" t="s">
+        <v>666</v>
+      </c>
+      <c r="C48" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="B49" s="87" t="s">
+        <v>667</v>
+      </c>
+      <c r="C49" s="52" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{6669C113-A26A-4DFA-8607-F2725AAA8D8D}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{101EDFAE-4EDE-449E-88DB-CD9250C3B528}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{E2B7BB62-D3A5-4E8C-8E76-AAD8626DEADF}"/>
+    <hyperlink ref="B39" r:id="rId4" location="categoria_888" xr:uid="{DF7CAD2D-8934-412B-9ED5-A0BDE12F8014}"/>
+    <hyperlink ref="B40" r:id="rId5" xr:uid="{E013878C-4856-46D4-B98B-443C89D7B540}"/>
+    <hyperlink ref="B41" r:id="rId6" xr:uid="{E52A207F-82F4-48DF-9168-AB7ADBB7270A}"/>
+    <hyperlink ref="B30" r:id="rId7" xr:uid="{C60526F3-6C22-4016-8088-1C9CD74DD3BB}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -3483,19 +3904,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G1" s="55" t="s">
         <v>24</v>
@@ -3525,49 +3946,49 @@
         <v>29</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="R1" s="51" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="S1" s="26" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="T1" s="16" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="U1" s="16" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="V1" s="17" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="W1" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="X1" s="56" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="17" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="Z1" s="26" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="AA1" s="16" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AB1" s="26" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="AC1" s="26" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="AD1" s="26" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3575,19 +3996,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G2" s="68" t="str">
         <f>_xlfn.CONCAT("é.nomeado some ",B2)</f>
@@ -3623,13 +4044,13 @@
         <v>Continente</v>
       </c>
       <c r="P2" s="69" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="Q2" s="69" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="R2" s="66" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="S2" s="77" t="s">
         <v>1</v>
@@ -3647,7 +4068,7 @@
         <v>Naturais</v>
       </c>
       <c r="W2" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X2" s="67" t="str">
         <f>CONCATENATE("Key-BRASIL-SP-",A2)</f>
@@ -3677,19 +4098,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G3" s="68" t="s">
         <v>1</v>
@@ -3723,13 +4144,13 @@
         <v>SubContinente</v>
       </c>
       <c r="P3" s="69" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="Q3" s="69" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="R3" s="66" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="S3" s="77" t="s">
         <v>1</v>
@@ -3747,7 +4168,7 @@
         <v>Naturais</v>
       </c>
       <c r="W3" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X3" s="67" t="str">
         <f t="shared" ref="X3:X66" si="3">CONCATENATE("Key-BRASIL-SP-",A3)</f>
@@ -3777,19 +4198,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G4" s="68" t="s">
         <v>1</v>
@@ -3823,13 +4244,13 @@
         <v>Bioma</v>
       </c>
       <c r="P4" s="69" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="Q4" s="69" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="R4" s="66" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="S4" s="77" t="s">
         <v>1</v>
@@ -3847,7 +4268,7 @@
         <v>Naturais</v>
       </c>
       <c r="W4" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X4" s="67" t="str">
         <f t="shared" si="3"/>
@@ -3877,19 +4298,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>1</v>
@@ -3924,13 +4345,13 @@
         <v>País</v>
       </c>
       <c r="P5" s="69" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="Q5" s="69" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="R5" s="66" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="S5" s="77" t="s">
         <v>1</v>
@@ -3948,7 +4369,7 @@
         <v>Políticas</v>
       </c>
       <c r="W5" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X5" s="67" t="str">
         <f t="shared" si="3"/>
@@ -3961,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="AA5" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB5" s="70" t="s">
         <v>1</v>
@@ -3978,19 +4399,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G6" s="68" t="s">
         <v>1</v>
@@ -4024,13 +4445,13 @@
         <v>Nação</v>
       </c>
       <c r="P6" s="69" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="Q6" s="69" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="R6" s="66" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="S6" s="77" t="s">
         <v>1</v>
@@ -4048,7 +4469,7 @@
         <v>Políticas</v>
       </c>
       <c r="W6" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X6" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4061,7 +4482,7 @@
         <v>1</v>
       </c>
       <c r="AA6" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB6" s="70" t="s">
         <v>1</v>
@@ -4078,19 +4499,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G7" s="68" t="s">
         <v>1</v>
@@ -4105,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="68" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L7" s="69" t="str">
         <f t="shared" si="0"/>
@@ -4124,13 +4545,13 @@
         <v>Região</v>
       </c>
       <c r="P7" s="71" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="Q7" s="69" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="R7" s="66" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="S7" s="77" t="s">
         <v>1</v>
@@ -4148,7 +4569,7 @@
         <v>Políticas</v>
       </c>
       <c r="W7" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X7" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4161,7 +4582,7 @@
         <v>1</v>
       </c>
       <c r="AA7" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB7" s="70" t="s">
         <v>1</v>
@@ -4178,19 +4599,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="G8" s="68" t="s">
         <v>1</v>
@@ -4205,7 +4626,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="68" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L8" s="69" t="str">
         <f t="shared" si="0"/>
@@ -4224,13 +4645,13 @@
         <v>Região Intermediária</v>
       </c>
       <c r="P8" s="71" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="Q8" s="69" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="R8" s="66" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="S8" s="77" t="s">
         <v>1</v>
@@ -4248,7 +4669,7 @@
         <v>Políticas</v>
       </c>
       <c r="W8" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X8" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4261,7 +4682,7 @@
         <v>1</v>
       </c>
       <c r="AA8" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB8" s="70" t="s">
         <v>1</v>
@@ -4278,19 +4699,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="G9" s="68" t="s">
         <v>1</v>
@@ -4305,7 +4726,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="68" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L9" s="69" t="str">
         <f t="shared" si="0"/>
@@ -4324,13 +4745,13 @@
         <v>Região Imediata</v>
       </c>
       <c r="P9" s="71" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="Q9" s="69" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="R9" s="66" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="S9" s="77" t="s">
         <v>1</v>
@@ -4348,7 +4769,7 @@
         <v>Políticas</v>
       </c>
       <c r="W9" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X9" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4361,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="AA9" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB9" s="70" t="s">
         <v>1</v>
@@ -4378,19 +4799,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G10" s="68" t="s">
         <v>1</v>
@@ -4425,13 +4846,13 @@
         <v>Estado</v>
       </c>
       <c r="P10" s="69" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="Q10" s="69" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="R10" s="66" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="S10" s="77" t="s">
         <v>1</v>
@@ -4449,7 +4870,7 @@
         <v>Políticas</v>
       </c>
       <c r="W10" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X10" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4462,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="AA10" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB10" s="70" t="s">
         <v>1</v>
@@ -4479,19 +4900,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G11" s="68" t="s">
         <v>1</v>
@@ -4525,13 +4946,13 @@
         <v>UF</v>
       </c>
       <c r="P11" s="69" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="Q11" s="69" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="R11" s="66" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="S11" s="77" t="s">
         <v>1</v>
@@ -4549,7 +4970,7 @@
         <v>Políticas</v>
       </c>
       <c r="W11" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X11" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4562,7 +4983,7 @@
         <v>1</v>
       </c>
       <c r="AA11" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB11" s="70" t="s">
         <v>1</v>
@@ -4579,19 +5000,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G12" s="68" t="s">
         <v>1</v>
@@ -4626,13 +5047,13 @@
         <v>Província</v>
       </c>
       <c r="P12" s="69" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="Q12" s="69" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="R12" s="66" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="S12" s="77" t="s">
         <v>1</v>
@@ -4650,7 +5071,7 @@
         <v>Políticas</v>
       </c>
       <c r="W12" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X12" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4663,7 +5084,7 @@
         <v>1</v>
       </c>
       <c r="AA12" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB12" s="70" t="s">
         <v>1</v>
@@ -4680,19 +5101,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G13" s="68" t="s">
         <v>1</v>
@@ -4727,13 +5148,13 @@
         <v>Capital</v>
       </c>
       <c r="P13" s="69" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="Q13" s="69" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="R13" s="66" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="S13" s="77" t="s">
         <v>1</v>
@@ -4751,7 +5172,7 @@
         <v>Políticas</v>
       </c>
       <c r="W13" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X13" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4764,7 +5185,7 @@
         <v>1</v>
       </c>
       <c r="AA13" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB13" s="70" t="s">
         <v>1</v>
@@ -4781,19 +5202,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="G14" s="68" t="s">
         <v>1</v>
@@ -4828,13 +5249,13 @@
         <v>Capital do Sul</v>
       </c>
       <c r="P14" s="69" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="Q14" s="69" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="R14" s="66" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="S14" s="77" t="s">
         <v>1</v>
@@ -4852,7 +5273,7 @@
         <v>Políticas</v>
       </c>
       <c r="W14" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X14" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4865,7 +5286,7 @@
         <v>1</v>
       </c>
       <c r="AA14" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB14" s="70" t="s">
         <v>1</v>
@@ -4882,19 +5303,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="G15" s="68" t="s">
         <v>1</v>
@@ -4929,13 +5350,13 @@
         <v>Capital do Sudeste</v>
       </c>
       <c r="P15" s="69" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="Q15" s="69" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="R15" s="66" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="S15" s="77" t="s">
         <v>1</v>
@@ -4953,7 +5374,7 @@
         <v>Políticas</v>
       </c>
       <c r="W15" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X15" s="67" t="str">
         <f t="shared" si="3"/>
@@ -4966,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="AA15" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB15" s="70" t="s">
         <v>1</v>
@@ -4983,19 +5404,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="G16" s="68" t="s">
         <v>1</v>
@@ -5030,13 +5451,13 @@
         <v>Capital do Norte</v>
       </c>
       <c r="P16" s="69" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="Q16" s="69" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="R16" s="66" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="S16" s="77" t="s">
         <v>1</v>
@@ -5054,7 +5475,7 @@
         <v>Políticas</v>
       </c>
       <c r="W16" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X16" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5067,7 +5488,7 @@
         <v>1</v>
       </c>
       <c r="AA16" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB16" s="70" t="s">
         <v>1</v>
@@ -5084,19 +5505,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="G17" s="68" t="s">
         <v>1</v>
@@ -5131,13 +5552,13 @@
         <v>Capital do Nordeste</v>
       </c>
       <c r="P17" s="69" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="Q17" s="69" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="R17" s="66" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="S17" s="77" t="s">
         <v>1</v>
@@ -5155,7 +5576,7 @@
         <v>Políticas</v>
       </c>
       <c r="W17" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X17" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5168,7 +5589,7 @@
         <v>1</v>
       </c>
       <c r="AA17" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB17" s="70" t="s">
         <v>1</v>
@@ -5185,19 +5606,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="G18" s="68" t="s">
         <v>1</v>
@@ -5232,13 +5653,13 @@
         <v>Capital do CentroOeste</v>
       </c>
       <c r="P18" s="69" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="Q18" s="69" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="R18" s="66" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="S18" s="77" t="s">
         <v>1</v>
@@ -5256,7 +5677,7 @@
         <v>Políticas</v>
       </c>
       <c r="W18" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X18" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5269,7 +5690,7 @@
         <v>1</v>
       </c>
       <c r="AA18" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB18" s="70" t="s">
         <v>1</v>
@@ -5286,19 +5707,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G19" s="68" t="s">
         <v>1</v>
@@ -5333,13 +5754,13 @@
         <v>Cidade</v>
       </c>
       <c r="P19" s="69" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="Q19" s="69" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="R19" s="66" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="S19" s="77" t="s">
         <v>1</v>
@@ -5357,7 +5778,7 @@
         <v>Políticas</v>
       </c>
       <c r="W19" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X19" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5370,7 +5791,7 @@
         <v>1</v>
       </c>
       <c r="AA19" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB19" s="70" t="s">
         <v>1</v>
@@ -5387,19 +5808,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G20" s="68" t="s">
         <v>1</v>
@@ -5434,13 +5855,13 @@
         <v>Cidade do Sul</v>
       </c>
       <c r="P20" s="69" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="Q20" s="69" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="R20" s="66" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="S20" s="77" t="s">
         <v>1</v>
@@ -5458,7 +5879,7 @@
         <v>Políticas</v>
       </c>
       <c r="W20" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X20" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5471,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="AA20" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB20" s="70" t="s">
         <v>1</v>
@@ -5488,19 +5909,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="G21" s="68" t="s">
         <v>1</v>
@@ -5535,13 +5956,13 @@
         <v>Cidade do Sudeste</v>
       </c>
       <c r="P21" s="69" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="Q21" s="69" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="R21" s="66" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="S21" s="77" t="s">
         <v>1</v>
@@ -5559,7 +5980,7 @@
         <v>Políticas</v>
       </c>
       <c r="W21" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X21" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5572,7 +5993,7 @@
         <v>1</v>
       </c>
       <c r="AA21" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB21" s="70" t="s">
         <v>1</v>
@@ -5589,19 +6010,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="G22" s="68" t="s">
         <v>1</v>
@@ -5636,13 +6057,13 @@
         <v>Cidade do Norte</v>
       </c>
       <c r="P22" s="69" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="Q22" s="69" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="R22" s="66" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="S22" s="77" t="s">
         <v>1</v>
@@ -5660,7 +6081,7 @@
         <v>Políticas</v>
       </c>
       <c r="W22" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X22" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5673,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="AA22" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB22" s="70" t="s">
         <v>1</v>
@@ -5690,19 +6111,19 @@
         <v>23</v>
       </c>
       <c r="B23" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="G23" s="68" t="s">
         <v>1</v>
@@ -5737,13 +6158,13 @@
         <v>Cidade do Nordeste</v>
       </c>
       <c r="P23" s="69" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="Q23" s="69" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="R23" s="66" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="S23" s="77" t="s">
         <v>1</v>
@@ -5761,7 +6182,7 @@
         <v>Políticas</v>
       </c>
       <c r="W23" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X23" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5774,7 +6195,7 @@
         <v>1</v>
       </c>
       <c r="AA23" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB23" s="70" t="s">
         <v>1</v>
@@ -5791,19 +6212,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="G24" s="68" t="s">
         <v>1</v>
@@ -5838,13 +6259,13 @@
         <v>Cidade do CentroOeste</v>
       </c>
       <c r="P24" s="69" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="Q24" s="69" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="R24" s="66" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="S24" s="77" t="s">
         <v>1</v>
@@ -5862,7 +6283,7 @@
         <v>Políticas</v>
       </c>
       <c r="W24" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X24" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5875,7 +6296,7 @@
         <v>1</v>
       </c>
       <c r="AA24" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB24" s="70" t="s">
         <v>1</v>
@@ -5892,19 +6313,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G25" s="68" t="s">
         <v>1</v>
@@ -5939,13 +6360,13 @@
         <v>Metrópoli</v>
       </c>
       <c r="P25" s="69" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="Q25" s="69" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="R25" s="66" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="S25" s="77" t="s">
         <v>1</v>
@@ -5963,7 +6384,7 @@
         <v>Políticas</v>
       </c>
       <c r="W25" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X25" s="67" t="str">
         <f t="shared" si="3"/>
@@ -5976,7 +6397,7 @@
         <v>1</v>
       </c>
       <c r="AA25" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB25" s="70" t="s">
         <v>1</v>
@@ -5993,19 +6414,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="G26" s="68" t="s">
         <v>1</v>
@@ -6040,13 +6461,13 @@
         <v>Município</v>
       </c>
       <c r="P26" s="69" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="Q26" s="69" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="R26" s="66" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="S26" s="77" t="s">
         <v>1</v>
@@ -6064,7 +6485,7 @@
         <v>Políticas</v>
       </c>
       <c r="W26" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X26" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6077,7 +6498,7 @@
         <v>1</v>
       </c>
       <c r="AA26" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB26" s="70" t="s">
         <v>1</v>
@@ -6094,19 +6515,19 @@
         <v>27</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G27" s="68" t="s">
         <v>1</v>
@@ -6141,13 +6562,13 @@
         <v>Região Climática</v>
       </c>
       <c r="P27" s="69" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="Q27" s="69" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="R27" s="66" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="S27" s="77" t="s">
         <v>1</v>
@@ -6165,20 +6586,20 @@
         <v>Bioclimáticas</v>
       </c>
       <c r="W27" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X27" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-27</v>
       </c>
       <c r="Y27" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z27" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA27" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB27" s="70" t="s">
         <v>1</v>
@@ -6195,19 +6616,19 @@
         <v>28</v>
       </c>
       <c r="B28" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G28" s="68" t="s">
         <v>1</v>
@@ -6242,13 +6663,13 @@
         <v>Zona Climática</v>
       </c>
       <c r="P28" s="69" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="Q28" s="69" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="R28" s="66" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="S28" s="77" t="s">
         <v>1</v>
@@ -6266,20 +6687,20 @@
         <v>Bioclimáticas</v>
       </c>
       <c r="W28" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X28" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-28</v>
       </c>
       <c r="Y28" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z28" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA28" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB28" s="70" t="s">
         <v>1</v>
@@ -6296,19 +6717,19 @@
         <v>29</v>
       </c>
       <c r="B29" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G29" s="68" t="s">
         <v>1</v>
@@ -6343,13 +6764,13 @@
         <v>Zona Climática Local</v>
       </c>
       <c r="P29" s="69" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="Q29" s="69" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="R29" s="66" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="S29" s="77" t="s">
         <v>1</v>
@@ -6367,20 +6788,20 @@
         <v>Ilhas de Calor</v>
       </c>
       <c r="W29" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X29" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-29</v>
       </c>
       <c r="Y29" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z29" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA29" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB29" s="70" t="s">
         <v>1</v>
@@ -6397,19 +6818,19 @@
         <v>30</v>
       </c>
       <c r="B30" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E30" s="63" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F30" s="64" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G30" s="68" t="s">
         <v>1</v>
@@ -6443,13 +6864,13 @@
         <v>Marco.Referencial</v>
       </c>
       <c r="P30" s="66" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="Q30" s="66" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="R30" s="66" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="S30" s="77" t="s">
         <v>1</v>
@@ -6467,7 +6888,7 @@
         <v>Marcos</v>
       </c>
       <c r="W30" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X30" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6480,7 +6901,7 @@
         <v>1</v>
       </c>
       <c r="AA30" s="70" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="AB30" s="70" t="s">
         <v>1</v>
@@ -6497,19 +6918,19 @@
         <v>31</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E31" s="63" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F31" s="64" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G31" s="68" t="s">
         <v>1</v>
@@ -6543,13 +6964,13 @@
         <v>Marco.de.Fronteira</v>
       </c>
       <c r="P31" s="66" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="Q31" s="66" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="R31" s="66" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="S31" s="77" t="s">
         <v>1</v>
@@ -6567,7 +6988,7 @@
         <v>Marcos</v>
       </c>
       <c r="W31" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X31" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6580,7 +7001,7 @@
         <v>1</v>
       </c>
       <c r="AA31" s="70" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="AB31" s="70" t="s">
         <v>1</v>
@@ -6597,19 +7018,19 @@
         <v>32</v>
       </c>
       <c r="B32" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E32" s="63" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F32" s="64" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="G32" s="68" t="s">
         <v>1</v>
@@ -6643,13 +7064,13 @@
         <v>Marco.de.Cruzamento</v>
       </c>
       <c r="P32" s="66" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="Q32" s="66" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="R32" s="66" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="S32" s="77" t="s">
         <v>1</v>
@@ -6667,7 +7088,7 @@
         <v>Marcos</v>
       </c>
       <c r="W32" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X32" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6680,7 +7101,7 @@
         <v>1</v>
       </c>
       <c r="AA32" s="70" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="AB32" s="70" t="s">
         <v>1</v>
@@ -6697,19 +7118,19 @@
         <v>33</v>
       </c>
       <c r="B33" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E33" s="63" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F33" s="64" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="G33" s="68" t="s">
         <v>1</v>
@@ -6743,13 +7164,13 @@
         <v>Marco.de.Localização</v>
       </c>
       <c r="P33" s="66" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="Q33" s="66" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="R33" s="66" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="S33" s="77" t="s">
         <v>1</v>
@@ -6767,7 +7188,7 @@
         <v>Marcos</v>
       </c>
       <c r="W33" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X33" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6780,7 +7201,7 @@
         <v>1</v>
       </c>
       <c r="AA33" s="70" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="AB33" s="70" t="s">
         <v>1</v>
@@ -6797,19 +7218,19 @@
         <v>34</v>
       </c>
       <c r="B34" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E34" s="63" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F34" s="64" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="G34" s="68" t="s">
         <v>1</v>
@@ -6843,13 +7264,13 @@
         <v>Marco.Quilométrico</v>
       </c>
       <c r="P34" s="66" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="Q34" s="66" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="R34" s="66" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="S34" s="77" t="s">
         <v>1</v>
@@ -6867,7 +7288,7 @@
         <v>Marcos</v>
       </c>
       <c r="W34" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X34" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6880,7 +7301,7 @@
         <v>1</v>
       </c>
       <c r="AA34" s="70" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="AB34" s="70" t="s">
         <v>1</v>
@@ -6897,19 +7318,19 @@
         <v>35</v>
       </c>
       <c r="B35" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E35" s="63" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F35" s="64" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="G35" s="68" t="s">
         <v>1</v>
@@ -6943,13 +7364,13 @@
         <v>Marco.Geográfico</v>
       </c>
       <c r="P35" s="66" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="Q35" s="66" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="R35" s="66" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="S35" s="77" t="s">
         <v>1</v>
@@ -6967,7 +7388,7 @@
         <v>Marcos</v>
       </c>
       <c r="W35" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X35" s="67" t="str">
         <f t="shared" si="3"/>
@@ -6980,7 +7401,7 @@
         <v>1</v>
       </c>
       <c r="AA35" s="70" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="AB35" s="70" t="s">
         <v>1</v>
@@ -6997,19 +7418,19 @@
         <v>36</v>
       </c>
       <c r="B36" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E36" s="63" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F36" s="64" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="G36" s="68" t="s">
         <v>1</v>
@@ -7043,13 +7464,13 @@
         <v>Marco.de.Milha</v>
       </c>
       <c r="P36" s="66" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="Q36" s="66" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="R36" s="66" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="S36" s="77" t="s">
         <v>1</v>
@@ -7067,7 +7488,7 @@
         <v>Marcos</v>
       </c>
       <c r="W36" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X36" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7080,7 +7501,7 @@
         <v>1</v>
       </c>
       <c r="AA36" s="70" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="AB36" s="70" t="s">
         <v>1</v>
@@ -7097,19 +7518,19 @@
         <v>37</v>
       </c>
       <c r="B37" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C37" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="D37" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="E37" s="63" t="s">
+        <v>281</v>
+      </c>
+      <c r="F37" s="64" t="s">
         <v>255</v>
-      </c>
-      <c r="D37" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="E37" s="63" t="s">
-        <v>288</v>
-      </c>
-      <c r="F37" s="64" t="s">
-        <v>262</v>
       </c>
       <c r="G37" s="68" t="s">
         <v>1</v>
@@ -7143,13 +7564,13 @@
         <v>Estaca.de.Controle</v>
       </c>
       <c r="P37" s="66" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="Q37" s="66" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="R37" s="66" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="S37" s="77" t="s">
         <v>1</v>
@@ -7167,7 +7588,7 @@
         <v>Marcos</v>
       </c>
       <c r="W37" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X37" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7180,7 +7601,7 @@
         <v>1</v>
       </c>
       <c r="AA37" s="70" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="AB37" s="70" t="s">
         <v>1</v>
@@ -7197,19 +7618,19 @@
         <v>38</v>
       </c>
       <c r="B38" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E38" s="63" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F38" s="64" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="G38" s="68" t="s">
         <v>1</v>
@@ -7243,13 +7664,13 @@
         <v>Estação.de.Medição</v>
       </c>
       <c r="P38" s="66" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="Q38" s="66" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="R38" s="66" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="S38" s="77" t="s">
         <v>1</v>
@@ -7267,7 +7688,7 @@
         <v>Marcos</v>
       </c>
       <c r="W38" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X38" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7280,7 +7701,7 @@
         <v>1</v>
       </c>
       <c r="AA38" s="70" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="AB38" s="70" t="s">
         <v>1</v>
@@ -7297,19 +7718,19 @@
         <v>39</v>
       </c>
       <c r="B39" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E39" s="63" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F39" s="64" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="G39" s="68" t="s">
         <v>1</v>
@@ -7343,13 +7764,13 @@
         <v xml:space="preserve">Superelevação </v>
       </c>
       <c r="P39" s="66" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="Q39" s="66" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="R39" s="66" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="S39" s="77" t="s">
         <v>1</v>
@@ -7367,7 +7788,7 @@
         <v>Marcos</v>
       </c>
       <c r="W39" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X39" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7380,7 +7801,7 @@
         <v>1</v>
       </c>
       <c r="AA39" s="70" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="AB39" s="70" t="s">
         <v>1</v>
@@ -7397,19 +7818,19 @@
         <v>40</v>
       </c>
       <c r="B40" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E40" s="63" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F40" s="64" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="G40" s="68" t="s">
         <v>1</v>
@@ -7443,13 +7864,13 @@
         <v>Largura.de.Pista</v>
       </c>
       <c r="P40" s="66" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="Q40" s="66" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="R40" s="66" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="S40" s="77" t="s">
         <v>1</v>
@@ -7467,7 +7888,7 @@
         <v>Marcos</v>
       </c>
       <c r="W40" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X40" s="67" t="str">
         <f t="shared" si="3"/>
@@ -7480,7 +7901,7 @@
         <v>1</v>
       </c>
       <c r="AA40" s="70" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AB40" s="70" t="s">
         <v>1</v>
@@ -7497,19 +7918,19 @@
         <v>41</v>
       </c>
       <c r="B41" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="G41" s="68" t="s">
         <v>1</v>
@@ -7543,13 +7964,13 @@
         <v>Ponto Interno</v>
       </c>
       <c r="P41" s="69" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="Q41" s="69" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="R41" s="66" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="S41" s="77" t="s">
         <v>1</v>
@@ -7567,20 +7988,20 @@
         <v>Pontos Cotados</v>
       </c>
       <c r="W41" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X41" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-41</v>
       </c>
       <c r="Y41" s="66" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="Z41" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA41" s="66" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AB41" s="70" t="s">
         <v>1</v>
@@ -7597,19 +8018,19 @@
         <v>42</v>
       </c>
       <c r="B42" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="G42" s="68" t="s">
         <v>1</v>
@@ -7643,13 +8064,13 @@
         <v>Ponto Perimetral</v>
       </c>
       <c r="P42" s="69" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="Q42" s="69" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="R42" s="66" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="S42" s="77" t="s">
         <v>1</v>
@@ -7667,20 +8088,20 @@
         <v>Pontos Cotados</v>
       </c>
       <c r="W42" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X42" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-42</v>
       </c>
       <c r="Y42" s="66" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="Z42" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA42" s="66" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AB42" s="70" t="s">
         <v>1</v>
@@ -7697,19 +8118,19 @@
         <v>43</v>
       </c>
       <c r="B43" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="G43" s="68" t="s">
         <v>1</v>
@@ -7743,13 +8164,13 @@
         <v>Terreno 3D Sólido</v>
       </c>
       <c r="P43" s="69" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="Q43" s="69" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="R43" s="66" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="S43" s="77" t="s">
         <v>1</v>
@@ -7767,20 +8188,20 @@
         <v>Terrenos</v>
       </c>
       <c r="W43" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X43" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-43</v>
       </c>
       <c r="Y43" s="66" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="Z43" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA43" s="66" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AB43" s="70" t="s">
         <v>1</v>
@@ -7797,19 +8218,19 @@
         <v>44</v>
       </c>
       <c r="B44" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D44" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="G44" s="68" t="s">
         <v>1</v>
@@ -7843,13 +8264,13 @@
         <v>Terreno 3D Superficial</v>
       </c>
       <c r="P44" s="69" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="Q44" s="69" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="R44" s="66" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="S44" s="77" t="s">
         <v>1</v>
@@ -7867,20 +8288,20 @@
         <v>Terrenos</v>
       </c>
       <c r="W44" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X44" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-44</v>
       </c>
       <c r="Y44" s="66" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="Z44" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA44" s="66" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AB44" s="70" t="s">
         <v>1</v>
@@ -7897,19 +8318,19 @@
         <v>45</v>
       </c>
       <c r="B45" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D45" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="G45" s="68" t="s">
         <v>1</v>
@@ -7943,13 +8364,13 @@
         <v>MDT Camada Núcleo</v>
       </c>
       <c r="P45" s="69" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="Q45" s="69" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="R45" s="66" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="S45" s="77" t="s">
         <v>1</v>
@@ -7967,20 +8388,20 @@
         <v>Terrenos</v>
       </c>
       <c r="W45" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X45" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-45</v>
       </c>
       <c r="Y45" s="66" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="Z45" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA45" s="66" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AB45" s="70" t="s">
         <v>1</v>
@@ -7997,19 +8418,19 @@
         <v>46</v>
       </c>
       <c r="B46" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="G46" s="68" t="s">
         <v>1</v>
@@ -8043,13 +8464,13 @@
         <v>MDT Camada Substrato</v>
       </c>
       <c r="P46" s="69" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="Q46" s="69" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="R46" s="66" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="S46" s="77" t="s">
         <v>1</v>
@@ -8067,20 +8488,20 @@
         <v>Terrenos</v>
       </c>
       <c r="W46" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X46" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-46</v>
       </c>
       <c r="Y46" s="66" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="Z46" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA46" s="66" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AB46" s="70" t="s">
         <v>1</v>
@@ -8097,19 +8518,19 @@
         <v>47</v>
       </c>
       <c r="B47" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="G47" s="68" t="s">
         <v>1</v>
@@ -8143,13 +8564,13 @@
         <v>MDT Camada Membrana</v>
       </c>
       <c r="P47" s="69" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="Q47" s="69" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="R47" s="66" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="S47" s="77" t="s">
         <v>1</v>
@@ -8167,20 +8588,20 @@
         <v>Terrenos</v>
       </c>
       <c r="W47" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X47" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-47</v>
       </c>
       <c r="Y47" s="66" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="Z47" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA47" s="66" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AB47" s="70" t="s">
         <v>1</v>
@@ -8197,19 +8618,19 @@
         <v>48</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C48" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G48" s="68" t="s">
         <v>1</v>
@@ -8243,13 +8664,13 @@
         <v>MDT Camada Isolamento</v>
       </c>
       <c r="P48" s="69" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="Q48" s="69" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="R48" s="66" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="S48" s="77" t="s">
         <v>1</v>
@@ -8267,20 +8688,20 @@
         <v>Terrenos</v>
       </c>
       <c r="W48" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X48" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-48</v>
       </c>
       <c r="Y48" s="66" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="Z48" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA48" s="66" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AB48" s="70" t="s">
         <v>1</v>
@@ -8297,19 +8718,19 @@
         <v>49</v>
       </c>
       <c r="B49" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C49" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D49" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E49" s="31" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="F49" s="31" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="G49" s="68" t="s">
         <v>1</v>
@@ -8343,13 +8764,13 @@
         <v>MDT Camada Superficial</v>
       </c>
       <c r="P49" s="69" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="Q49" s="69" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="R49" s="66" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="S49" s="77" t="s">
         <v>1</v>
@@ -8367,20 +8788,20 @@
         <v>Terrenos</v>
       </c>
       <c r="W49" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X49" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-49</v>
       </c>
       <c r="Y49" s="66" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="Z49" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA49" s="66" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="AB49" s="70" t="s">
         <v>1</v>
@@ -8397,19 +8818,19 @@
         <v>50</v>
       </c>
       <c r="B50" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C50" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D50" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E50" s="31" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F50" s="31" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="G50" s="68" t="s">
         <v>1</v>
@@ -8443,13 +8864,13 @@
         <v>Curva de Nível 10m</v>
       </c>
       <c r="P50" s="69" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="Q50" s="69" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="R50" s="66" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="S50" s="77" t="s">
         <v>1</v>
@@ -8467,20 +8888,20 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W50" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X50" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-50</v>
       </c>
       <c r="Y50" s="66" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="Z50" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA50" s="66" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="AB50" s="70" t="s">
         <v>1</v>
@@ -8497,19 +8918,19 @@
         <v>51</v>
       </c>
       <c r="B51" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D51" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E51" s="31" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F51" s="31" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="G51" s="68" t="s">
         <v>1</v>
@@ -8543,13 +8964,13 @@
         <v>Curva de Nível 05m</v>
       </c>
       <c r="P51" s="69" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="Q51" s="69" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="R51" s="66" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="S51" s="77" t="s">
         <v>1</v>
@@ -8567,20 +8988,20 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W51" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X51" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-51</v>
       </c>
       <c r="Y51" s="66" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="Z51" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA51" s="66" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="AB51" s="70" t="s">
         <v>1</v>
@@ -8597,19 +9018,19 @@
         <v>52</v>
       </c>
       <c r="B52" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C52" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D52" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E52" s="31" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F52" s="31" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="G52" s="68" t="s">
         <v>1</v>
@@ -8643,13 +9064,13 @@
         <v>Curva de Nível 01m</v>
       </c>
       <c r="P52" s="69" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="Q52" s="69" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="R52" s="66" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="S52" s="77" t="s">
         <v>1</v>
@@ -8667,20 +9088,20 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W52" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X52" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-52</v>
       </c>
       <c r="Y52" s="66" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="Z52" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA52" s="66" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="AB52" s="70" t="s">
         <v>1</v>
@@ -8697,19 +9118,19 @@
         <v>53</v>
       </c>
       <c r="B53" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C53" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D53" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="E53" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="F53" s="31" t="s">
         <v>275</v>
-      </c>
-      <c r="E53" s="31" t="s">
-        <v>276</v>
-      </c>
-      <c r="F53" s="31" t="s">
-        <v>282</v>
       </c>
       <c r="G53" s="68" t="s">
         <v>1</v>
@@ -8743,13 +9164,13 @@
         <v>Curva de Nível Submétrica</v>
       </c>
       <c r="P53" s="69" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="Q53" s="69" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="R53" s="66" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="S53" s="77" t="s">
         <v>1</v>
@@ -8767,20 +9188,20 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W53" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X53" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-53</v>
       </c>
       <c r="Y53" s="66" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="Z53" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA53" s="66" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AB53" s="70" t="s">
         <v>1</v>
@@ -8797,19 +9218,19 @@
         <v>54</v>
       </c>
       <c r="B54" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C54" s="31" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D54" s="31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E54" s="31" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="G54" s="68" t="s">
         <v>1</v>
@@ -8843,13 +9264,13 @@
         <v>Ponto de Sondagem</v>
       </c>
       <c r="P54" s="69" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="Q54" s="69" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="R54" s="66" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="S54" s="77" t="s">
         <v>1</v>
@@ -8867,20 +9288,20 @@
         <v>Sondagens</v>
       </c>
       <c r="W54" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X54" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-54</v>
       </c>
       <c r="Y54" s="66" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="Z54" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA54" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB54" s="70" t="s">
         <v>1</v>
@@ -8897,19 +9318,19 @@
         <v>55</v>
       </c>
       <c r="B55" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C55" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="D55" s="31" t="s">
+        <v>456</v>
+      </c>
+      <c r="E55" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="D55" s="31" t="s">
-        <v>463</v>
-      </c>
-      <c r="E55" s="31" t="s">
-        <v>272</v>
-      </c>
       <c r="F55" s="31" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G55" s="68" t="s">
         <v>1</v>
@@ -8946,13 +9367,13 @@
         <v>Area de Planejamento</v>
       </c>
       <c r="P55" s="69" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="Q55" s="69" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="R55" s="66" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="S55" s="77" t="s">
         <v>1</v>
@@ -8970,20 +9391,20 @@
         <v>Zonificações</v>
       </c>
       <c r="W55" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X55" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-55</v>
       </c>
       <c r="Y55" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z55" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA55" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB55" s="70" t="s">
         <v>1</v>
@@ -9000,19 +9421,19 @@
         <v>56</v>
       </c>
       <c r="B56" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C56" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="D56" s="31" t="s">
+        <v>456</v>
+      </c>
+      <c r="E56" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="D56" s="31" t="s">
-        <v>463</v>
-      </c>
-      <c r="E56" s="31" t="s">
-        <v>272</v>
-      </c>
       <c r="F56" s="31" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G56" s="68" t="s">
         <v>1</v>
@@ -9048,13 +9469,13 @@
         <v>Região Administrativa</v>
       </c>
       <c r="P56" s="69" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="Q56" s="69" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="R56" s="66" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="S56" s="77" t="s">
         <v>1</v>
@@ -9072,20 +9493,20 @@
         <v>Zonificações</v>
       </c>
       <c r="W56" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X56" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-56</v>
       </c>
       <c r="Y56" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z56" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA56" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB56" s="70" t="s">
         <v>1</v>
@@ -9102,19 +9523,19 @@
         <v>57</v>
       </c>
       <c r="B57" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C57" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="D57" s="31" t="s">
+        <v>456</v>
+      </c>
+      <c r="E57" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="D57" s="31" t="s">
-        <v>463</v>
-      </c>
-      <c r="E57" s="31" t="s">
-        <v>272</v>
-      </c>
       <c r="F57" s="31" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="G57" s="68" t="s">
         <v>1</v>
@@ -9148,13 +9569,13 @@
         <v>Area de Interesse Especial</v>
       </c>
       <c r="P57" s="69" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="Q57" s="69" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="R57" s="66" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="S57" s="77" t="s">
         <v>1</v>
@@ -9172,20 +9593,20 @@
         <v>Zonificações</v>
       </c>
       <c r="W57" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X57" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-57</v>
       </c>
       <c r="Y57" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z57" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA57" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB57" s="70" t="s">
         <v>1</v>
@@ -9202,19 +9623,19 @@
         <v>58</v>
       </c>
       <c r="B58" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C58" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="D58" s="31" t="s">
+        <v>456</v>
+      </c>
+      <c r="E58" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="D58" s="31" t="s">
-        <v>463</v>
-      </c>
-      <c r="E58" s="31" t="s">
-        <v>272</v>
-      </c>
       <c r="F58" s="31" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G58" s="68" t="s">
         <v>1</v>
@@ -9248,13 +9669,13 @@
         <v>Area Restringida</v>
       </c>
       <c r="P58" s="69" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q58" s="69" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="R58" s="66" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="S58" s="77" t="s">
         <v>1</v>
@@ -9272,20 +9693,20 @@
         <v>Zonificações</v>
       </c>
       <c r="W58" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X58" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-58</v>
       </c>
       <c r="Y58" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z58" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA58" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB58" s="70" t="s">
         <v>1</v>
@@ -9302,19 +9723,19 @@
         <v>59</v>
       </c>
       <c r="B59" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C59" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="D59" s="31" t="s">
+        <v>456</v>
+      </c>
+      <c r="E59" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="D59" s="31" t="s">
-        <v>463</v>
-      </c>
-      <c r="E59" s="31" t="s">
-        <v>272</v>
-      </c>
       <c r="F59" s="31" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G59" s="68" t="s">
         <v>1</v>
@@ -9329,7 +9750,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="68" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L59" s="69" t="str">
         <f t="shared" si="0"/>
@@ -9348,13 +9769,13 @@
         <v>Zona</v>
       </c>
       <c r="P59" s="69" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="Q59" s="69" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="R59" s="66" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="S59" s="77" t="s">
         <v>1</v>
@@ -9372,20 +9793,20 @@
         <v>Zonificações</v>
       </c>
       <c r="W59" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X59" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-59</v>
       </c>
       <c r="Y59" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z59" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA59" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB59" s="70" t="s">
         <v>1</v>
@@ -9402,19 +9823,19 @@
         <v>60</v>
       </c>
       <c r="B60" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C60" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="D60" s="31" t="s">
+        <v>456</v>
+      </c>
+      <c r="E60" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="D60" s="31" t="s">
-        <v>463</v>
-      </c>
-      <c r="E60" s="31" t="s">
-        <v>272</v>
-      </c>
       <c r="F60" s="31" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G60" s="68" t="s">
         <v>1</v>
@@ -9429,7 +9850,7 @@
         <v>1</v>
       </c>
       <c r="K60" s="68" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L60" s="69" t="str">
         <f t="shared" si="0"/>
@@ -9448,13 +9869,13 @@
         <v>Bairro</v>
       </c>
       <c r="P60" s="69" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="Q60" s="69" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="R60" s="66" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="S60" s="77" t="s">
         <v>1</v>
@@ -9472,20 +9893,20 @@
         <v>Zonificações</v>
       </c>
       <c r="W60" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X60" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-60</v>
       </c>
       <c r="Y60" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z60" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA60" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB60" s="70" t="s">
         <v>1</v>
@@ -9502,19 +9923,19 @@
         <v>61</v>
       </c>
       <c r="B61" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C61" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="D61" s="31" t="s">
+        <v>456</v>
+      </c>
+      <c r="E61" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="D61" s="31" t="s">
-        <v>463</v>
-      </c>
-      <c r="E61" s="31" t="s">
-        <v>272</v>
-      </c>
       <c r="F61" s="31" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="G61" s="68" t="s">
         <v>1</v>
@@ -9529,7 +9950,7 @@
         <v>1</v>
       </c>
       <c r="K61" s="68" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L61" s="69" t="str">
         <f t="shared" si="0"/>
@@ -9548,13 +9969,13 @@
         <v>Zona de Uso</v>
       </c>
       <c r="P61" s="69" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="Q61" s="69" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="R61" s="66" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="S61" s="77" t="s">
         <v>1</v>
@@ -9572,20 +9993,20 @@
         <v>Zonificações</v>
       </c>
       <c r="W61" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X61" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-61</v>
       </c>
       <c r="Y61" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z61" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA61" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB61" s="70" t="s">
         <v>1</v>
@@ -9602,19 +10023,19 @@
         <v>62</v>
       </c>
       <c r="B62" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C62" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="D62" s="31" t="s">
+        <v>456</v>
+      </c>
+      <c r="E62" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="D62" s="31" t="s">
-        <v>463</v>
-      </c>
-      <c r="E62" s="31" t="s">
-        <v>272</v>
-      </c>
       <c r="F62" s="31" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="G62" s="68" t="s">
         <v>1</v>
@@ -9629,7 +10050,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="68" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L62" s="69" t="str">
         <f t="shared" si="0"/>
@@ -9648,13 +10069,13 @@
         <v>Macrozona</v>
       </c>
       <c r="P62" s="69" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="Q62" s="69" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="R62" s="66" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="S62" s="77" t="s">
         <v>1</v>
@@ -9672,20 +10093,20 @@
         <v>Zonificações</v>
       </c>
       <c r="W62" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X62" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-62</v>
       </c>
       <c r="Y62" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z62" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA62" s="66" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="AB62" s="70" t="s">
         <v>1</v>
@@ -9702,19 +10123,19 @@
         <v>63</v>
       </c>
       <c r="B63" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C63" s="31" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="E63" s="31" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F63" s="31" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G63" s="68" t="s">
         <v>1</v>
@@ -9729,7 +10150,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="68" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="L63" s="69" t="str">
         <f t="shared" si="0"/>
@@ -9748,13 +10169,13 @@
         <v>Quadra</v>
       </c>
       <c r="P63" s="69" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="Q63" s="69" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="R63" s="66" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="S63" s="77" t="s">
         <v>1</v>
@@ -9772,20 +10193,20 @@
         <v>Frações</v>
       </c>
       <c r="W63" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X63" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-63</v>
       </c>
       <c r="Y63" s="66" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="Z63" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA63" s="66" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="AB63" s="70" t="s">
         <v>1</v>
@@ -9802,19 +10223,19 @@
         <v>64</v>
       </c>
       <c r="B64" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C64" s="31" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="E64" s="31" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F64" s="31" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G64" s="68" t="s">
         <v>1</v>
@@ -9848,13 +10269,13 @@
         <v>Gleba</v>
       </c>
       <c r="P64" s="69" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="Q64" s="69" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="R64" s="66" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="S64" s="77" t="s">
         <v>1</v>
@@ -9872,20 +10293,20 @@
         <v>Frações</v>
       </c>
       <c r="W64" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X64" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-64</v>
       </c>
       <c r="Y64" s="66" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="Z64" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA64" s="66" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AB64" s="70" t="s">
         <v>1</v>
@@ -9902,19 +10323,19 @@
         <v>65</v>
       </c>
       <c r="B65" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C65" s="31" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="E65" s="31" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F65" s="31" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="G65" s="68" t="s">
         <v>1</v>
@@ -9948,13 +10369,13 @@
         <v>Loteamento</v>
       </c>
       <c r="P65" s="69" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="Q65" s="69" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="R65" s="66" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="S65" s="77" t="s">
         <v>1</v>
@@ -9972,20 +10393,20 @@
         <v>Frações</v>
       </c>
       <c r="W65" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X65" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-65</v>
       </c>
       <c r="Y65" s="66" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="Z65" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA65" s="66" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AB65" s="70" t="s">
         <v>1</v>
@@ -10002,19 +10423,19 @@
         <v>66</v>
       </c>
       <c r="B66" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C66" s="31" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="E66" s="31" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F66" s="31" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G66" s="68" t="s">
         <v>1</v>
@@ -10048,13 +10469,13 @@
         <v>Parcela</v>
       </c>
       <c r="P66" s="69" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="Q66" s="69" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="R66" s="66" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="S66" s="77" t="s">
         <v>1</v>
@@ -10072,20 +10493,20 @@
         <v>Frações</v>
       </c>
       <c r="W66" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X66" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL-SP-66</v>
       </c>
       <c r="Y66" s="66" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="Z66" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA66" s="66" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AB66" s="70" t="s">
         <v>1</v>
@@ -10102,19 +10523,19 @@
         <v>67</v>
       </c>
       <c r="B67" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C67" s="31" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D67" s="31" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="E67" s="31" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F67" s="31" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G67" s="68" t="s">
         <v>1</v>
@@ -10148,13 +10569,13 @@
         <v>Lote</v>
       </c>
       <c r="P67" s="69" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="Q67" s="69" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="R67" s="66" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="S67" s="77" t="s">
         <v>1</v>
@@ -10172,20 +10593,20 @@
         <v>Frações</v>
       </c>
       <c r="W67" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X67" s="67" t="str">
-        <f t="shared" ref="X67:X105" si="13">CONCATENATE("Key-BRASIL-SP-",A67)</f>
+        <f t="shared" ref="X67:X100" si="13">CONCATENATE("Key-BRASIL-SP-",A67)</f>
         <v>Key-BRASIL-SP-67</v>
       </c>
       <c r="Y67" s="66" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="Z67" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA67" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB67" s="70" t="s">
         <v>1</v>
@@ -10202,19 +10623,19 @@
         <v>68</v>
       </c>
       <c r="B68" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C68" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D68" s="31" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E68" s="31" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G68" s="68" t="s">
         <v>1</v>
@@ -10249,13 +10670,13 @@
         <v>Prédio</v>
       </c>
       <c r="P68" s="69" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Q68" s="69" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="R68" s="66" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="S68" s="77" t="s">
         <v>1</v>
@@ -10273,20 +10694,20 @@
         <v>Construídas</v>
       </c>
       <c r="W68" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X68" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-68</v>
       </c>
       <c r="Y68" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z68" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA68" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB68" s="70" t="s">
         <v>1</v>
@@ -10303,19 +10724,19 @@
         <v>69</v>
       </c>
       <c r="B69" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C69" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D69" s="31" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E69" s="31" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F69" s="31" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G69" s="68" t="s">
         <v>1</v>
@@ -10350,13 +10771,13 @@
         <v>Bloco</v>
       </c>
       <c r="P69" s="69" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="Q69" s="69" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="R69" s="66" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="S69" s="77" t="s">
         <v>1</v>
@@ -10374,20 +10795,20 @@
         <v>Construídas</v>
       </c>
       <c r="W69" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X69" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-69</v>
       </c>
       <c r="Y69" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z69" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA69" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB69" s="70" t="s">
         <v>1</v>
@@ -10404,19 +10825,19 @@
         <v>70</v>
       </c>
       <c r="B70" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C70" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D70" s="31" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E70" s="31" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F70" s="31" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G70" s="68" t="s">
         <v>1</v>
@@ -10451,13 +10872,13 @@
         <v>Edifício</v>
       </c>
       <c r="P70" s="69" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="Q70" s="69" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="R70" s="66" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="S70" s="77" t="s">
         <v>1</v>
@@ -10475,20 +10896,20 @@
         <v>Construídas</v>
       </c>
       <c r="W70" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X70" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-70</v>
       </c>
       <c r="Y70" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z70" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA70" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB70" s="70" t="s">
         <v>1</v>
@@ -10505,19 +10926,19 @@
         <v>71</v>
       </c>
       <c r="B71" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C71" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D71" s="31" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E71" s="31" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F71" s="31" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="G71" s="68" t="s">
         <v>1</v>
@@ -10552,13 +10973,13 @@
         <v>Casa</v>
       </c>
       <c r="P71" s="69" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="Q71" s="69" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="R71" s="66" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="S71" s="77" t="s">
         <v>1</v>
@@ -10576,20 +10997,20 @@
         <v>Construídas</v>
       </c>
       <c r="W71" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X71" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-71</v>
       </c>
       <c r="Y71" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z71" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA71" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB71" s="70" t="s">
         <v>1</v>
@@ -10606,19 +11027,19 @@
         <v>72</v>
       </c>
       <c r="B72" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C72" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D72" s="31" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E72" s="31" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F72" s="31" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G72" s="68" t="s">
         <v>1</v>
@@ -10653,13 +11074,13 @@
         <v>HIS</v>
       </c>
       <c r="P72" s="69" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="Q72" s="69" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="R72" s="66" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="S72" s="77" t="s">
         <v>1</v>
@@ -10677,20 +11098,20 @@
         <v>Construídas</v>
       </c>
       <c r="W72" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X72" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-72</v>
       </c>
       <c r="Y72" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z72" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA72" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB72" s="70" t="s">
         <v>1</v>
@@ -10707,19 +11128,19 @@
         <v>73</v>
       </c>
       <c r="B73" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C73" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D73" s="31" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E73" s="31" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F73" s="31" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G73" s="68" t="s">
         <v>1</v>
@@ -10734,7 +11155,7 @@
         <v>1</v>
       </c>
       <c r="K73" s="68" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="L73" s="69" t="str">
         <f t="shared" si="0"/>
@@ -10753,13 +11174,13 @@
         <v>Galpão</v>
       </c>
       <c r="P73" s="69" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="Q73" s="69" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="R73" s="66" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="S73" s="77" t="s">
         <v>1</v>
@@ -10777,20 +11198,20 @@
         <v>Construídas</v>
       </c>
       <c r="W73" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X73" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-73</v>
       </c>
       <c r="Y73" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z73" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA73" s="66" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AB73" s="70" t="s">
         <v>1</v>
@@ -10807,19 +11228,19 @@
         <v>74</v>
       </c>
       <c r="B74" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C74" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D74" s="31" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E74" s="31" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F74" s="31" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G74" s="68" t="s">
         <v>1</v>
@@ -10834,7 +11255,7 @@
         <v>1</v>
       </c>
       <c r="K74" s="68" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="L74" s="69" t="str">
         <f t="shared" si="0"/>
@@ -10853,13 +11274,13 @@
         <v>Edícula</v>
       </c>
       <c r="P74" s="69" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="Q74" s="69" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="R74" s="66" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="S74" s="77" t="s">
         <v>1</v>
@@ -10877,20 +11298,20 @@
         <v>Construídas</v>
       </c>
       <c r="W74" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X74" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-74</v>
       </c>
       <c r="Y74" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z74" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA74" s="66" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AB74" s="70" t="s">
         <v>1</v>
@@ -10907,19 +11328,19 @@
         <v>75</v>
       </c>
       <c r="B75" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C75" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D75" s="31" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E75" s="31" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F75" s="31" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G75" s="68" t="s">
         <v>1</v>
@@ -10935,7 +11356,7 @@
         <v>1</v>
       </c>
       <c r="K75" s="68" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L75" s="69" t="str">
         <f t="shared" si="0"/>
@@ -10954,13 +11375,13 @@
         <v>Unidade</v>
       </c>
       <c r="P75" s="69" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="Q75" s="69" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="R75" s="66" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="S75" s="77" t="s">
         <v>1</v>
@@ -10978,20 +11399,20 @@
         <v>Organizativas</v>
       </c>
       <c r="W75" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X75" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-75</v>
       </c>
       <c r="Y75" s="66" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Z75" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA75" s="66" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AB75" s="70" t="s">
         <v>1</v>
@@ -11008,19 +11429,19 @@
         <v>76</v>
       </c>
       <c r="B76" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C76" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D76" s="31" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E76" s="31" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F76" s="31" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="G76" s="68" t="s">
         <v>1</v>
@@ -11035,7 +11456,7 @@
         <v>1</v>
       </c>
       <c r="K76" s="68" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L76" s="69" t="str">
         <f t="shared" si="0"/>
@@ -11054,13 +11475,13 @@
         <v>Setor Urbano</v>
       </c>
       <c r="P76" s="69" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="Q76" s="69" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="R76" s="66" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="S76" s="77" t="s">
         <v>1</v>
@@ -11078,20 +11499,20 @@
         <v>Organizativas</v>
       </c>
       <c r="W76" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X76" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-76</v>
       </c>
       <c r="Y76" s="66" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="Z76" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA76" s="66" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AB76" s="70" t="s">
         <v>1</v>
@@ -11108,19 +11529,19 @@
         <v>77</v>
       </c>
       <c r="B77" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C77" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D77" s="31" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E77" s="31" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F77" s="31" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G77" s="68" t="s">
         <v>1</v>
@@ -11135,7 +11556,7 @@
         <v>1</v>
       </c>
       <c r="K77" s="68" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L77" s="69" t="str">
         <f t="shared" si="0"/>
@@ -11154,13 +11575,13 @@
         <v>Divisão</v>
       </c>
       <c r="P77" s="69" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="Q77" s="69" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="R77" s="66" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="S77" s="77" t="s">
         <v>1</v>
@@ -11178,20 +11599,20 @@
         <v>Organizativas</v>
       </c>
       <c r="W77" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X77" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-77</v>
       </c>
       <c r="Y77" s="66" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="Z77" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA77" s="66" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AB77" s="70" t="s">
         <v>1</v>
@@ -11208,19 +11629,19 @@
         <v>78</v>
       </c>
       <c r="B78" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C78" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D78" s="31" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E78" s="31" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F78" s="31" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G78" s="68" t="s">
         <v>1</v>
@@ -11235,7 +11656,7 @@
         <v>1</v>
       </c>
       <c r="K78" s="68" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L78" s="69" t="str">
         <f t="shared" si="0"/>
@@ -11254,13 +11675,13 @@
         <v>Departamento</v>
       </c>
       <c r="P78" s="69" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="Q78" s="69" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="R78" s="66" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="S78" s="77" t="s">
         <v>1</v>
@@ -11278,20 +11699,20 @@
         <v>Organizativas</v>
       </c>
       <c r="W78" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X78" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-78</v>
       </c>
       <c r="Y78" s="66" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="Z78" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA78" s="66" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="AB78" s="70" t="s">
         <v>1</v>
@@ -11308,19 +11729,19 @@
         <v>79</v>
       </c>
       <c r="B79" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C79" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D79" s="31" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E79" s="31" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="F79" s="31" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G79" s="68" t="s">
         <v>1</v>
@@ -11335,7 +11756,7 @@
         <v>1</v>
       </c>
       <c r="K79" s="68" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L79" s="69" t="str">
         <f t="shared" si="0"/>
@@ -11354,13 +11775,13 @@
         <v>Ambiente</v>
       </c>
       <c r="P79" s="69" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="Q79" s="69" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="R79" s="66" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="S79" s="77" t="s">
         <v>1</v>
@@ -11378,20 +11799,20 @@
         <v>Distribuição</v>
       </c>
       <c r="W79" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X79" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-79</v>
       </c>
       <c r="Y79" s="66" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="Z79" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA79" s="66" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AB79" s="70" t="s">
         <v>1</v>
@@ -11408,19 +11829,19 @@
         <v>80</v>
       </c>
       <c r="B80" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C80" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D80" s="31" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E80" s="31" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="F80" s="31" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G80" s="68" t="s">
         <v>1</v>
@@ -11435,7 +11856,7 @@
         <v>1</v>
       </c>
       <c r="K80" s="68" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L80" s="69" t="str">
         <f t="shared" si="0"/>
@@ -11454,13 +11875,13 @@
         <v>Apartamento</v>
       </c>
       <c r="P80" s="69" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="Q80" s="69" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="R80" s="66" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="S80" s="77" t="s">
         <v>1</v>
@@ -11478,20 +11899,20 @@
         <v>Distribuição</v>
       </c>
       <c r="W80" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X80" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-80</v>
       </c>
       <c r="Y80" s="66" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="Z80" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA80" s="66" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AB80" s="70" t="s">
         <v>1</v>
@@ -11508,19 +11929,19 @@
         <v>81</v>
       </c>
       <c r="B81" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C81" s="31" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D81" s="31" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E81" s="31" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="F81" s="31" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G81" s="68" t="s">
         <v>1</v>
@@ -11535,7 +11956,7 @@
         <v>1</v>
       </c>
       <c r="K81" s="68" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L81" s="69" t="str">
         <f t="shared" si="0"/>
@@ -11554,13 +11975,13 @@
         <v>Núcleo de Circulação</v>
       </c>
       <c r="P81" s="69" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="Q81" s="69" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="R81" s="66" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="S81" s="77" t="s">
         <v>1</v>
@@ -11578,20 +11999,20 @@
         <v>Distribuição</v>
       </c>
       <c r="W81" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X81" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-81</v>
       </c>
       <c r="Y81" s="66" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="Z81" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA81" s="66" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AB81" s="70" t="s">
         <v>1</v>
@@ -11608,19 +12029,19 @@
         <v>82</v>
       </c>
       <c r="B82" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C82" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D82" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E82" s="31" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F82" s="31" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G82" s="68" t="s">
         <v>1</v>
@@ -11654,13 +12075,13 @@
         <v>Hospital Federal</v>
       </c>
       <c r="P82" s="69" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="Q82" s="69" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="R82" s="66" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="S82" s="77" t="s">
         <v>1</v>
@@ -11678,20 +12099,20 @@
         <v>Saúde</v>
       </c>
       <c r="W82" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X82" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-82</v>
       </c>
       <c r="Y82" s="66" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z82" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA82" s="66" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AB82" s="70" t="s">
         <v>1</v>
@@ -11708,19 +12129,19 @@
         <v>83</v>
       </c>
       <c r="B83" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C83" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D83" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E83" s="31" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F83" s="31" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G83" s="68" t="s">
         <v>1</v>
@@ -11754,13 +12175,13 @@
         <v>Hospital Estadual</v>
       </c>
       <c r="P83" s="69" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="Q83" s="69" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="R83" s="66" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="S83" s="77" t="s">
         <v>1</v>
@@ -11778,20 +12199,20 @@
         <v>Saúde</v>
       </c>
       <c r="W83" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X83" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-83</v>
       </c>
       <c r="Y83" s="66" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z83" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA83" s="66" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AB83" s="70" t="s">
         <v>1</v>
@@ -11808,19 +12229,19 @@
         <v>84</v>
       </c>
       <c r="B84" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C84" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D84" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E84" s="31" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F84" s="31" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G84" s="68" t="s">
         <v>1</v>
@@ -11854,13 +12275,13 @@
         <v>Hospital Municipal</v>
       </c>
       <c r="P84" s="69" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="Q84" s="69" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="R84" s="66" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="S84" s="77" t="s">
         <v>1</v>
@@ -11878,20 +12299,20 @@
         <v>Saúde</v>
       </c>
       <c r="W84" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X84" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-84</v>
       </c>
       <c r="Y84" s="66" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z84" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA84" s="66" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AB84" s="70" t="s">
         <v>1</v>
@@ -11908,19 +12329,19 @@
         <v>85</v>
       </c>
       <c r="B85" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C85" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D85" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E85" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="F85" s="31" t="s">
         <v>154</v>
-      </c>
-      <c r="F85" s="31" t="s">
-        <v>161</v>
       </c>
       <c r="G85" s="68" t="s">
         <v>1</v>
@@ -11954,13 +12375,13 @@
         <v>UBS</v>
       </c>
       <c r="P85" s="69" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="Q85" s="69" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="R85" s="66" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="S85" s="77" t="s">
         <v>1</v>
@@ -11978,20 +12399,20 @@
         <v>Saúde</v>
       </c>
       <c r="W85" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X85" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-85</v>
       </c>
       <c r="Y85" s="66" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z85" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA85" s="66" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AB85" s="70" t="s">
         <v>1</v>
@@ -12008,19 +12429,19 @@
         <v>86</v>
       </c>
       <c r="B86" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C86" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D86" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E86" s="31" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F86" s="31" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G86" s="68" t="s">
         <v>1</v>
@@ -12054,13 +12475,13 @@
         <v>UPA</v>
       </c>
       <c r="P86" s="69" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="Q86" s="69" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="R86" s="66" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="S86" s="77" t="s">
         <v>1</v>
@@ -12078,20 +12499,20 @@
         <v>Saúde</v>
       </c>
       <c r="W86" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X86" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-86</v>
       </c>
       <c r="Y86" s="66" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z86" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA86" s="66" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AB86" s="70" t="s">
         <v>1</v>
@@ -12108,19 +12529,19 @@
         <v>87</v>
       </c>
       <c r="B87" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C87" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D87" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E87" s="31" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F87" s="31" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G87" s="68" t="s">
         <v>1</v>
@@ -12154,13 +12575,13 @@
         <v>Universidade Federal</v>
       </c>
       <c r="P87" s="69" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="Q87" s="69" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="R87" s="66" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="S87" s="77" t="s">
         <v>1</v>
@@ -12178,20 +12599,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W87" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X87" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-87</v>
       </c>
       <c r="Y87" s="66" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z87" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA87" s="66" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AB87" s="70" t="s">
         <v>1</v>
@@ -12208,19 +12629,19 @@
         <v>88</v>
       </c>
       <c r="B88" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C88" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D88" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E88" s="31" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F88" s="31" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G88" s="68" t="s">
         <v>1</v>
@@ -12254,13 +12675,13 @@
         <v>Universidade Estadual</v>
       </c>
       <c r="P88" s="69" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="Q88" s="69" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="R88" s="66" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="S88" s="77" t="s">
         <v>1</v>
@@ -12278,20 +12699,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W88" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X88" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-88</v>
       </c>
       <c r="Y88" s="66" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z88" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA88" s="66" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AB88" s="70" t="s">
         <v>1</v>
@@ -12308,19 +12729,19 @@
         <v>89</v>
       </c>
       <c r="B89" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C89" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D89" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E89" s="31" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F89" s="31" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G89" s="68" t="s">
         <v>1</v>
@@ -12354,13 +12775,13 @@
         <v>Escola Estadual</v>
       </c>
       <c r="P89" s="69" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="Q89" s="69" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="R89" s="66" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="S89" s="77" t="s">
         <v>1</v>
@@ -12378,20 +12799,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W89" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X89" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-89</v>
       </c>
       <c r="Y89" s="66" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z89" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA89" s="66" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AB89" s="70" t="s">
         <v>1</v>
@@ -12408,19 +12829,19 @@
         <v>90</v>
       </c>
       <c r="B90" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C90" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D90" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E90" s="31" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F90" s="31" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="G90" s="68" t="s">
         <v>1</v>
@@ -12454,13 +12875,13 @@
         <v>Escola Municipal</v>
       </c>
       <c r="P90" s="69" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="Q90" s="69" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="R90" s="66" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="S90" s="77" t="s">
         <v>1</v>
@@ -12478,20 +12899,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W90" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X90" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-90</v>
       </c>
       <c r="Y90" s="66" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z90" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA90" s="66" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AB90" s="70" t="s">
         <v>1</v>
@@ -12508,19 +12929,19 @@
         <v>91</v>
       </c>
       <c r="B91" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C91" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D91" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E91" s="31" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F91" s="31" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="G91" s="68" t="s">
         <v>1</v>
@@ -12554,13 +12975,13 @@
         <v>Colégio de Aplicação</v>
       </c>
       <c r="P91" s="69" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="Q91" s="69" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="R91" s="66" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="S91" s="77" t="s">
         <v>1</v>
@@ -12578,20 +12999,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W91" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X91" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-91</v>
       </c>
       <c r="Y91" s="66" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z91" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA91" s="66" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AB91" s="70" t="s">
         <v>1</v>
@@ -12608,19 +13029,19 @@
         <v>92</v>
       </c>
       <c r="B92" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C92" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D92" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E92" s="31" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F92" s="31" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="G92" s="68" t="s">
         <v>1</v>
@@ -12654,13 +13075,13 @@
         <v>Instituiçao de Ensino Militar</v>
       </c>
       <c r="P92" s="69" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="Q92" s="69" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="R92" s="66" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="S92" s="77" t="s">
         <v>1</v>
@@ -12678,20 +13099,20 @@
         <v>Educacionais</v>
       </c>
       <c r="W92" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X92" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-92</v>
       </c>
       <c r="Y92" s="66" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z92" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA92" s="66" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AB92" s="70" t="s">
         <v>1</v>
@@ -12708,19 +13129,19 @@
         <v>93</v>
       </c>
       <c r="B93" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C93" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D93" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E93" s="31" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F93" s="31" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="G93" s="68" t="s">
         <v>1</v>
@@ -12754,13 +13175,13 @@
         <v>Estação Meteorológica</v>
       </c>
       <c r="P93" s="69" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="Q93" s="69" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="R93" s="66" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="S93" s="77" t="s">
         <v>1</v>
@@ -12778,20 +13199,20 @@
         <v>INMET</v>
       </c>
       <c r="W93" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X93" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-93</v>
       </c>
       <c r="Y93" s="66" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="Z93" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA93" s="66" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AB93" s="70" t="s">
         <v>1</v>
@@ -12808,19 +13229,19 @@
         <v>94</v>
       </c>
       <c r="B94" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C94" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D94" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E94" s="31" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F94" s="37" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="G94" s="68" t="s">
         <v>1</v>
@@ -12854,13 +13275,13 @@
         <v>Estação Meteorológica Automática</v>
       </c>
       <c r="P94" s="69" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="Q94" s="69" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="R94" s="66" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="S94" s="77" t="s">
         <v>1</v>
@@ -12878,20 +13299,20 @@
         <v>INMET</v>
       </c>
       <c r="W94" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X94" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-94</v>
       </c>
       <c r="Y94" s="66" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="Z94" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA94" s="66" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AB94" s="70" t="s">
         <v>1</v>
@@ -12908,19 +13329,19 @@
         <v>95</v>
       </c>
       <c r="B95" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C95" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D95" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E95" s="31" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F95" s="37" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="G95" s="68" t="s">
         <v>1</v>
@@ -12954,13 +13375,13 @@
         <v>Estação Meteorológica Convencional</v>
       </c>
       <c r="P95" s="69" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="Q95" s="69" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="R95" s="66" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="S95" s="77" t="s">
         <v>1</v>
@@ -12978,20 +13399,20 @@
         <v>INMET</v>
       </c>
       <c r="W95" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X95" s="67" t="str">
         <f t="shared" si="13"/>
         <v>Key-BRASIL-SP-95</v>
       </c>
       <c r="Y95" s="66" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="Z95" s="75" t="s">
         <v>1</v>
       </c>
       <c r="AA95" s="66" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AB95" s="70" t="s">
         <v>1</v>
@@ -13008,19 +13429,19 @@
         <v>96</v>
       </c>
       <c r="B96" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C96" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D96" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E96" s="31" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F96" s="31" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="G96" s="68" t="s">
         <v>1</v>
@@ -13054,13 +13475,13 @@
         <v>Area Densa</v>
       </c>
       <c r="P96" s="69" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="Q96" s="69" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="R96" s="66" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="S96" s="77" t="s">
         <v>1</v>
@@ -13078,7 +13499,7 @@
         <v>IBGE</v>
       </c>
       <c r="W96" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X96" s="67" t="str">
         <f t="shared" si="13"/>
@@ -13108,19 +13529,19 @@
         <v>97</v>
       </c>
       <c r="B97" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C97" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D97" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E97" s="31" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F97" s="31" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G97" s="68" t="s">
         <v>1</v>
@@ -13154,13 +13575,13 @@
         <v>Area Pouco Densa</v>
       </c>
       <c r="P97" s="69" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="Q97" s="69" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="R97" s="66" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="S97" s="77" t="s">
         <v>1</v>
@@ -13178,7 +13599,7 @@
         <v>IBGE</v>
       </c>
       <c r="W97" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X97" s="67" t="str">
         <f t="shared" si="13"/>
@@ -13208,19 +13629,19 @@
         <v>98</v>
       </c>
       <c r="B98" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C98" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D98" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E98" s="31" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F98" s="31" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G98" s="68" t="s">
         <v>1</v>
@@ -13254,13 +13675,13 @@
         <v>IDU</v>
       </c>
       <c r="P98" s="69" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="Q98" s="69" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="R98" s="66" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="S98" s="77" t="s">
         <v>1</v>
@@ -13278,7 +13699,7 @@
         <v>IBGE</v>
       </c>
       <c r="W98" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X98" s="67" t="str">
         <f t="shared" si="13"/>
@@ -13308,19 +13729,19 @@
         <v>99</v>
       </c>
       <c r="B99" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C99" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D99" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F99" s="31" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G99" s="68" t="s">
         <v>1</v>
@@ -13354,13 +13775,13 @@
         <v>Taxa Urbanização</v>
       </c>
       <c r="P99" s="69" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="Q99" s="69" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="R99" s="66" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="S99" s="77" t="s">
         <v>1</v>
@@ -13378,7 +13799,7 @@
         <v>IBGE</v>
       </c>
       <c r="W99" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X99" s="67" t="str">
         <f t="shared" si="13"/>
@@ -13408,19 +13829,19 @@
         <v>100</v>
       </c>
       <c r="B100" s="63" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D100" s="31" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E100" s="31" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F100" s="31" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="G100" s="68" t="s">
         <v>1</v>
@@ -13454,13 +13875,13 @@
         <v>Expansão Urbana</v>
       </c>
       <c r="P100" s="69" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="Q100" s="69" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="R100" s="66" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="S100" s="77" t="s">
         <v>1</v>
@@ -13478,7 +13899,7 @@
         <v>IBGE</v>
       </c>
       <c r="W100" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X100" s="67" t="str">
         <f t="shared" si="13"/>
@@ -13508,70 +13929,70 @@
         <v>101</v>
       </c>
       <c r="B101" s="76" t="s">
+        <v>599</v>
+      </c>
+      <c r="C101" s="37" t="s">
+        <v>600</v>
+      </c>
+      <c r="D101" s="37" t="s">
+        <v>601</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>602</v>
+      </c>
+      <c r="F101" s="37" t="s">
+        <v>575</v>
+      </c>
+      <c r="G101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="I101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="J101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="L101" s="73" t="s">
+        <v>600</v>
+      </c>
+      <c r="M101" s="73" t="s">
+        <v>601</v>
+      </c>
+      <c r="N101" s="73" t="s">
+        <v>603</v>
+      </c>
+      <c r="O101" s="73" t="s">
+        <v>604</v>
+      </c>
+      <c r="P101" s="74" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q101" s="74" t="s">
+        <v>577</v>
+      </c>
+      <c r="R101" s="74" t="s">
+        <v>578</v>
+      </c>
+      <c r="S101" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="T101" s="74" t="s">
+        <v>605</v>
+      </c>
+      <c r="U101" s="74" t="s">
         <v>606</v>
       </c>
-      <c r="C101" s="37" t="s">
-        <v>607</v>
-      </c>
-      <c r="D101" s="37" t="s">
-        <v>608</v>
-      </c>
-      <c r="E101" s="37" t="s">
-        <v>609</v>
-      </c>
-      <c r="F101" s="37" t="s">
-        <v>582</v>
-      </c>
-      <c r="G101" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="H101" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="I101" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="J101" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="K101" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="L101" s="73" t="s">
-        <v>607</v>
-      </c>
-      <c r="M101" s="73" t="s">
-        <v>608</v>
-      </c>
-      <c r="N101" s="73" t="s">
-        <v>610</v>
-      </c>
-      <c r="O101" s="73" t="s">
-        <v>611</v>
-      </c>
-      <c r="P101" s="74" t="s">
-        <v>583</v>
-      </c>
-      <c r="Q101" s="74" t="s">
-        <v>584</v>
-      </c>
-      <c r="R101" s="74" t="s">
-        <v>585</v>
-      </c>
-      <c r="S101" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="T101" s="74" t="s">
-        <v>612</v>
-      </c>
-      <c r="U101" s="74" t="s">
-        <v>613</v>
-      </c>
       <c r="V101" s="66" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="W101" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X101" s="67" t="str">
         <f t="shared" ref="X101:X105" si="16">CONCATENATE("Key-BRASIL-SP-",A101)</f>
@@ -13601,70 +14022,70 @@
         <v>102</v>
       </c>
       <c r="B102" s="76" t="s">
+        <v>599</v>
+      </c>
+      <c r="C102" s="37" t="s">
+        <v>600</v>
+      </c>
+      <c r="D102" s="37" t="s">
+        <v>601</v>
+      </c>
+      <c r="E102" s="37" t="s">
+        <v>602</v>
+      </c>
+      <c r="F102" s="37" t="s">
+        <v>579</v>
+      </c>
+      <c r="G102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="H102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="I102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="J102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="L102" s="73" t="s">
+        <v>600</v>
+      </c>
+      <c r="M102" s="73" t="s">
+        <v>601</v>
+      </c>
+      <c r="N102" s="73" t="s">
+        <v>603</v>
+      </c>
+      <c r="O102" s="73" t="s">
+        <v>607</v>
+      </c>
+      <c r="P102" s="74" t="s">
+        <v>580</v>
+      </c>
+      <c r="Q102" s="74" t="s">
+        <v>581</v>
+      </c>
+      <c r="R102" s="74" t="s">
+        <v>582</v>
+      </c>
+      <c r="S102" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="T102" s="74" t="s">
+        <v>605</v>
+      </c>
+      <c r="U102" s="74" t="s">
         <v>606</v>
       </c>
-      <c r="C102" s="37" t="s">
-        <v>607</v>
-      </c>
-      <c r="D102" s="37" t="s">
-        <v>608</v>
-      </c>
-      <c r="E102" s="37" t="s">
-        <v>609</v>
-      </c>
-      <c r="F102" s="37" t="s">
-        <v>586</v>
-      </c>
-      <c r="G102" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="H102" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="I102" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="J102" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="K102" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="L102" s="73" t="s">
-        <v>607</v>
-      </c>
-      <c r="M102" s="73" t="s">
-        <v>608</v>
-      </c>
-      <c r="N102" s="73" t="s">
-        <v>610</v>
-      </c>
-      <c r="O102" s="73" t="s">
-        <v>614</v>
-      </c>
-      <c r="P102" s="74" t="s">
-        <v>587</v>
-      </c>
-      <c r="Q102" s="74" t="s">
-        <v>588</v>
-      </c>
-      <c r="R102" s="74" t="s">
-        <v>589</v>
-      </c>
-      <c r="S102" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="T102" s="74" t="s">
-        <v>612</v>
-      </c>
-      <c r="U102" s="74" t="s">
-        <v>613</v>
-      </c>
       <c r="V102" s="66" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="W102" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X102" s="67" t="str">
         <f t="shared" si="16"/>
@@ -13694,70 +14115,70 @@
         <v>103</v>
       </c>
       <c r="B103" s="76" t="s">
+        <v>599</v>
+      </c>
+      <c r="C103" s="37" t="s">
+        <v>600</v>
+      </c>
+      <c r="D103" s="37" t="s">
+        <v>601</v>
+      </c>
+      <c r="E103" s="37" t="s">
+        <v>602</v>
+      </c>
+      <c r="F103" s="37" t="s">
+        <v>583</v>
+      </c>
+      <c r="G103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="H103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="I103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="J103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="L103" s="73" t="s">
+        <v>600</v>
+      </c>
+      <c r="M103" s="73" t="s">
+        <v>601</v>
+      </c>
+      <c r="N103" s="73" t="s">
+        <v>603</v>
+      </c>
+      <c r="O103" s="73" t="s">
+        <v>608</v>
+      </c>
+      <c r="P103" s="74" t="s">
+        <v>584</v>
+      </c>
+      <c r="Q103" s="74" t="s">
+        <v>585</v>
+      </c>
+      <c r="R103" s="74" t="s">
+        <v>586</v>
+      </c>
+      <c r="S103" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="T103" s="74" t="s">
+        <v>605</v>
+      </c>
+      <c r="U103" s="74" t="s">
         <v>606</v>
       </c>
-      <c r="C103" s="37" t="s">
-        <v>607</v>
-      </c>
-      <c r="D103" s="37" t="s">
-        <v>608</v>
-      </c>
-      <c r="E103" s="37" t="s">
-        <v>609</v>
-      </c>
-      <c r="F103" s="37" t="s">
-        <v>590</v>
-      </c>
-      <c r="G103" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="H103" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="I103" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="J103" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="K103" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="L103" s="73" t="s">
-        <v>607</v>
-      </c>
-      <c r="M103" s="73" t="s">
-        <v>608</v>
-      </c>
-      <c r="N103" s="73" t="s">
-        <v>610</v>
-      </c>
-      <c r="O103" s="73" t="s">
-        <v>615</v>
-      </c>
-      <c r="P103" s="74" t="s">
-        <v>591</v>
-      </c>
-      <c r="Q103" s="74" t="s">
-        <v>592</v>
-      </c>
-      <c r="R103" s="74" t="s">
-        <v>593</v>
-      </c>
-      <c r="S103" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="T103" s="74" t="s">
-        <v>612</v>
-      </c>
-      <c r="U103" s="74" t="s">
-        <v>613</v>
-      </c>
       <c r="V103" s="66" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="W103" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X103" s="67" t="str">
         <f t="shared" si="16"/>
@@ -13787,70 +14208,70 @@
         <v>104</v>
       </c>
       <c r="B104" s="76" t="s">
+        <v>599</v>
+      </c>
+      <c r="C104" s="37" t="s">
+        <v>600</v>
+      </c>
+      <c r="D104" s="37" t="s">
+        <v>601</v>
+      </c>
+      <c r="E104" s="37" t="s">
+        <v>602</v>
+      </c>
+      <c r="F104" s="37" t="s">
+        <v>587</v>
+      </c>
+      <c r="G104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="H104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="I104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="J104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="L104" s="73" t="s">
+        <v>600</v>
+      </c>
+      <c r="M104" s="73" t="s">
+        <v>601</v>
+      </c>
+      <c r="N104" s="73" t="s">
+        <v>603</v>
+      </c>
+      <c r="O104" s="73" t="s">
+        <v>609</v>
+      </c>
+      <c r="P104" s="74" t="s">
+        <v>588</v>
+      </c>
+      <c r="Q104" s="74" t="s">
+        <v>589</v>
+      </c>
+      <c r="R104" s="74" t="s">
+        <v>590</v>
+      </c>
+      <c r="S104" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="T104" s="74" t="s">
+        <v>605</v>
+      </c>
+      <c r="U104" s="74" t="s">
         <v>606</v>
       </c>
-      <c r="C104" s="37" t="s">
-        <v>607</v>
-      </c>
-      <c r="D104" s="37" t="s">
-        <v>608</v>
-      </c>
-      <c r="E104" s="37" t="s">
-        <v>609</v>
-      </c>
-      <c r="F104" s="37" t="s">
-        <v>594</v>
-      </c>
-      <c r="G104" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="H104" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="I104" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="J104" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="K104" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="L104" s="73" t="s">
-        <v>607</v>
-      </c>
-      <c r="M104" s="73" t="s">
-        <v>608</v>
-      </c>
-      <c r="N104" s="73" t="s">
-        <v>610</v>
-      </c>
-      <c r="O104" s="73" t="s">
-        <v>616</v>
-      </c>
-      <c r="P104" s="74" t="s">
-        <v>595</v>
-      </c>
-      <c r="Q104" s="74" t="s">
-        <v>596</v>
-      </c>
-      <c r="R104" s="74" t="s">
-        <v>597</v>
-      </c>
-      <c r="S104" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="T104" s="74" t="s">
-        <v>612</v>
-      </c>
-      <c r="U104" s="74" t="s">
-        <v>613</v>
-      </c>
       <c r="V104" s="66" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="W104" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X104" s="67" t="str">
         <f t="shared" si="16"/>
@@ -13880,19 +14301,19 @@
         <v>105</v>
       </c>
       <c r="B105" s="76" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="C105" s="37" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="D105" s="37" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="E105" s="37" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="F105" s="37" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="G105" s="72" t="s">
         <v>1</v>
@@ -13910,40 +14331,40 @@
         <v>1</v>
       </c>
       <c r="L105" s="73" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="M105" s="73" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="N105" s="73" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="O105" s="73" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="P105" s="74" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="Q105" s="74" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="R105" s="74" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="S105" s="77" t="s">
         <v>1</v>
       </c>
       <c r="T105" s="74" t="s">
+        <v>605</v>
+      </c>
+      <c r="U105" s="74" t="s">
+        <v>614</v>
+      </c>
+      <c r="V105" s="66" t="s">
         <v>612</v>
       </c>
-      <c r="U105" s="74" t="s">
-        <v>621</v>
-      </c>
-      <c r="V105" s="66" t="s">
-        <v>619</v>
-      </c>
       <c r="W105" s="66" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="X105" s="67" t="str">
         <f t="shared" si="16"/>
@@ -13971,81 +14392,81 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B100 A101:A105">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:D100 L41:Q100 T41:V100 AE41:XFD100 AE106:XFD1048576">
-    <cfRule type="cellIs" dxfId="37" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1 F106:F1048576 A1:D1 T1:X1 A106:D1048576 T106:X1048576">
-    <cfRule type="cellIs" dxfId="35" priority="467" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="467" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="34" priority="1505"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AE1:XFD29 T2:V28 L7:O9 Q7:Q9 L10:Q29 T29:U29 V29:V40 O30:O40">
-    <cfRule type="cellIs" dxfId="33" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F93 F96:F100">
-    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="30" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F40">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F40">
-    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
-    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F100 F2:F93">
-    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F101:F105">
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="18" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="984"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="987"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="991"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="995"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="999"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="987"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="999"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L106:R1048576">
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R100">
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W105">
-    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F101:F105">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -14260,7 +14681,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14284,13 +14705,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
@@ -14298,10 +14719,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D2" s="50" t="s">
         <v>1</v>
@@ -14312,10 +14733,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>1</v>
@@ -14326,13 +14747,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
@@ -14340,13 +14761,13 @@
         <v>5</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="36" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
@@ -14354,10 +14775,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D6" s="50" t="s">
         <v>1</v>
@@ -14365,7 +14786,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A6">
-    <cfRule type="cellIs" dxfId="6" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14439,49 +14860,49 @@
   <sheetData>
     <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>34</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="D1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="N1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="P1" s="19"/>
       <c r="Q1" s="19"/>
@@ -14489,121 +14910,121 @@
         <v>33</v>
       </c>
       <c r="S1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="T1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="U1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="V1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="W1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="X1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="Y1" s="35" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Z1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AA1" s="35" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AB1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AC1" s="35" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AD1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AE1" s="34" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AF1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AG1" s="34" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AH1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AI1" s="34" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AJ1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AK1" s="34" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AL1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AM1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AN1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AO1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AP1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AQ1" s="34" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AR1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AS1" s="35" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AT1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AU1" s="35" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AV1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AW1" s="35" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AX1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AY1" s="35" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AZ1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="BA1" s="35" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="BB1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="BC1" s="35" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="BD1" s="19" t="s">
         <v>33</v>
       </c>
       <c r="BE1" s="35" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -14611,10 +15032,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>1</v>
@@ -14647,10 +15068,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="39" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O2" s="30" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="P2" s="39" t="s">
         <v>1</v>
@@ -14755,25 +15176,25 @@
         <v>1</v>
       </c>
       <c r="AX2" s="32" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AY2" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="AZ2" s="32" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="BA2" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="BB2" s="32" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="BC2" s="40" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="BD2" s="32" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="BE2" s="40" t="str">
         <f t="shared" ref="BE2" si="0">_xlfn.CONCAT("""",C2,"""")</f>
@@ -14785,22 +15206,22 @@
         <v>3</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H3" s="18" t="s">
         <v>1</v>
@@ -14821,10 +15242,10 @@
         <v>1</v>
       </c>
       <c r="N3" s="39" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O3" s="30" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="P3" s="39" t="s">
         <v>1</v>
@@ -14929,25 +15350,25 @@
         <v>1</v>
       </c>
       <c r="AX3" s="32" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AY3" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="AZ3" s="32" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="BA3" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="BB3" s="32" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="BC3" s="40" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="BD3" s="32" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="BE3" s="40" t="str">
         <f t="shared" ref="BE3" si="1">_xlfn.CONCAT("""",C3,"""")</f>
@@ -14959,16 +15380,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>1</v>
@@ -14995,10 +15416,10 @@
         <v>1</v>
       </c>
       <c r="N4" s="39" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O4" s="30" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="P4" s="39" t="s">
         <v>1</v>
@@ -15103,25 +15524,25 @@
         <v>1</v>
       </c>
       <c r="AX4" s="32" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AY4" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="AZ4" s="32" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="BA4" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="BB4" s="32" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="BC4" s="40" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="BD4" s="32" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="BE4" s="40" t="str">
         <f t="shared" ref="BE4:BE5" si="2">_xlfn.CONCAT("""",C4,"""")</f>
@@ -15133,16 +15554,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>1</v>
@@ -15169,10 +15590,10 @@
         <v>1</v>
       </c>
       <c r="N5" s="39" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O5" s="28" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="P5" s="39" t="s">
         <v>1</v>
@@ -15181,10 +15602,10 @@
         <v>1</v>
       </c>
       <c r="R5" s="39" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="S5" s="28" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="T5" s="39" t="s">
         <v>1</v>
@@ -15277,25 +15698,25 @@
         <v>1</v>
       </c>
       <c r="AX5" s="32" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AY5" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="AZ5" s="32" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="BA5" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="BB5" s="32" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="BC5" s="40" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="BD5" s="32" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="BE5" s="40" t="str">
         <f t="shared" si="2"/>
@@ -15307,28 +15728,28 @@
         <v>6</v>
       </c>
       <c r="B6" s="61" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="C6" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="45" t="s">
-        <v>196</v>
-      </c>
-      <c r="E6" s="46" t="s">
+      <c r="G6" s="46" t="s">
         <v>199</v>
       </c>
-      <c r="F6" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="G6" s="46" t="s">
+      <c r="H6" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="H6" s="45" t="s">
-        <v>213</v>
-      </c>
       <c r="I6" s="46" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="J6" s="18" t="s">
         <v>1</v>
@@ -15343,10 +15764,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="39" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O6" s="28" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="P6" s="39" t="s">
         <v>1</v>
@@ -15451,25 +15872,25 @@
         <v>1</v>
       </c>
       <c r="AX6" s="32" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AY6" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="AZ6" s="32" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="BA6" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="BB6" s="32" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="BC6" s="40" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="BD6" s="32" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="BE6" s="40" t="str">
         <f t="shared" ref="BE6:BE9" si="3">_xlfn.CONCAT("""",C6,"""")</f>
@@ -15481,16 +15902,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>1</v>
@@ -15517,10 +15938,10 @@
         <v>1</v>
       </c>
       <c r="N7" s="39" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O7" s="30" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="P7" s="39" t="s">
         <v>1</v>
@@ -15625,25 +16046,25 @@
         <v>1</v>
       </c>
       <c r="AX7" s="32" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AY7" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="AZ7" s="32" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="BA7" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="BB7" s="32" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="BC7" s="40" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="BD7" s="32" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="BE7" s="40" t="str">
         <f t="shared" si="3"/>
@@ -15655,34 +16076,34 @@
         <v>8</v>
       </c>
       <c r="B8" s="61" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D8" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="H8" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="E8" s="46" t="s">
-        <v>208</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>196</v>
-      </c>
-      <c r="G8" s="46" t="s">
-        <v>205</v>
-      </c>
-      <c r="H8" s="45" t="s">
-        <v>203</v>
-      </c>
       <c r="I8" s="46" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="K8" s="41" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="L8" s="18" t="s">
         <v>1</v>
@@ -15691,7 +16112,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="39" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O8" s="28" t="str">
         <f t="shared" ref="O8" si="4">_xlfn.CONCAT("""É a cidade capital do Estado de ",K8," do Brasil """)</f>
@@ -15794,31 +16215,31 @@
         <v>1</v>
       </c>
       <c r="AV8" s="32" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="AW8" s="40" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="AX8" s="32" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AY8" s="40" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="AZ8" s="32" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="BA8" s="40" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="BB8" s="32" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="BC8" s="40" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="BD8" s="32" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="BE8" s="40" t="str">
         <f t="shared" si="3"/>
@@ -15830,16 +16251,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="61" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>1</v>
@@ -15866,10 +16287,10 @@
         <v>1</v>
       </c>
       <c r="N9" s="39" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="P9" s="39" t="s">
         <v>1</v>
@@ -15878,121 +16299,121 @@
         <v>1</v>
       </c>
       <c r="R9" s="39" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="S9" s="47" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="T9" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="U9" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="V9" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="W9" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="X9" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP9" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ9" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR9" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV9" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="AY9" s="40" t="s">
+        <v>414</v>
+      </c>
+      <c r="AZ9" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="U9" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="V9" s="39" t="s">
-        <v>217</v>
-      </c>
-      <c r="W9" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="X9" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF9" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ9" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL9" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM9" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN9" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO9" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="AP9" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AR9" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AS9" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT9" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AU9" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AV9" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AW9" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX9" s="32" t="s">
-        <v>381</v>
-      </c>
-      <c r="AY9" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="AZ9" s="32" t="s">
-        <v>223</v>
-      </c>
       <c r="BA9" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="BB9" s="32" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="BC9" s="40" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="BD9" s="32" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="BE9" s="40" t="str">
         <f t="shared" si="3"/>
@@ -16004,169 +16425,169 @@
         <v>10</v>
       </c>
       <c r="B10" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="H10" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="I10" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="J10" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="K10" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="O10" s="30" t="s">
+        <v>425</v>
+      </c>
+      <c r="P10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="C10" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>199</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>222</v>
-      </c>
-      <c r="G10" s="46" t="s">
-        <v>218</v>
-      </c>
-      <c r="H10" s="45" t="s">
-        <v>222</v>
-      </c>
-      <c r="I10" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="J10" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="K10" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="L10" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="O10" s="30" t="s">
-        <v>432</v>
-      </c>
-      <c r="P10" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="39" t="s">
-        <v>215</v>
-      </c>
       <c r="S10" s="47" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="T10" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="U10" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="V10" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="W10" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="X10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ10" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU10" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW10" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX10" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="AY10" s="40" t="s">
+        <v>414</v>
+      </c>
+      <c r="AZ10" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="U10" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="V10" s="39" t="s">
-        <v>217</v>
-      </c>
-      <c r="W10" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="X10" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ10" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL10" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN10" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="AP10" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AR10" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AS10" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT10" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AU10" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AV10" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AW10" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX10" s="32" t="s">
-        <v>381</v>
-      </c>
-      <c r="AY10" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="AZ10" s="32" t="s">
-        <v>223</v>
-      </c>
       <c r="BA10" s="40" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="BB10" s="32" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="BC10" s="40" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="BD10" s="32" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="BE10" s="40" t="str">
         <f t="shared" ref="BE10" si="5">_xlfn.CONCAT("""",C10,"""")</f>
@@ -16177,12 +16598,12 @@
   <autoFilter ref="F1:F10" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1048576 D1:F1048576 H1:XFD1048576 G2 G4:G5 G7 G9">
-    <cfRule type="cellIs" dxfId="5" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="37" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
